--- a/RR_fuelflow.xlsx
+++ b/RR_fuelflow.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\RationalResources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\GitHub\RationalResources\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -994,7 +994,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="239">
   <si>
     <t>name</t>
   </si>
@@ -1738,32 +1738,38 @@
   <si>
     <t>m</t>
   </si>
+  <si>
+    <t>Engine 1</t>
+  </si>
+  <si>
+    <t>Engine 2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="18">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="General\ &quot;J/mol-1 /K-1&quot;"/>
-    <numFmt numFmtId="170" formatCode="0\ &quot;K&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0.00\ &quot;g/mol&quot;"/>
-    <numFmt numFmtId="172" formatCode="0\ &quot;atm&quot;"/>
-    <numFmt numFmtId="173" formatCode="0.00\ &quot;g/mol&quot;"/>
-    <numFmt numFmtId="174" formatCode="0.000\ &quot;kg/mol&quot;"/>
-    <numFmt numFmtId="175" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.00000\ &quot;m/s^2&quot;"/>
-    <numFmt numFmtId="177" formatCode="#,###\ &quot;m/s&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0.00\ &quot;Pa&quot;"/>
-    <numFmt numFmtId="179" formatCode="#,###\ &quot;kW&quot;"/>
-    <numFmt numFmtId="180" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="General\ &quot;J/mol-1 /K-1&quot;"/>
+    <numFmt numFmtId="171" formatCode="0\ &quot;K&quot;"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00\ &quot;g/mol&quot;"/>
+    <numFmt numFmtId="173" formatCode="0\ &quot;atm&quot;"/>
+    <numFmt numFmtId="174" formatCode="0.00\ &quot;g/mol&quot;"/>
+    <numFmt numFmtId="175" formatCode="0.000\ &quot;kg/mol&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.00000\ &quot;m/s^2&quot;"/>
+    <numFmt numFmtId="178" formatCode="#,###\ &quot;m/s&quot;"/>
+    <numFmt numFmtId="179" formatCode="#,##0.00\ &quot;Pa&quot;"/>
+    <numFmt numFmtId="180" formatCode="#,###\ &quot;kW&quot;"/>
+    <numFmt numFmtId="181" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="10"/>
       <color indexed="8"/>
@@ -2069,18 +2075,17 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="4" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="5" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2090,60 +2095,60 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="5"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="8" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="4" fillId="3" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="4"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="3"/>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="3" fillId="2" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="11" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="4" fillId="3" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="11"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="6" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="11" applyFont="1"/>
-    <xf numFmtId="173" fontId="5" fillId="0" borderId="4" xfId="5" applyNumberFormat="1"/>
     <xf numFmtId="174" fontId="5" fillId="0" borderId="4" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="5" fillId="0" borderId="4" xfId="5" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2"/>
-    <xf numFmtId="176" fontId="17" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="177" fontId="17" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="4" fillId="3" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="13" fillId="3" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="17" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="5" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="4" xfId="5" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="4" xfId="5" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="12"/>
-    <xf numFmtId="175" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="5" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="3" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="179" fontId="3" fillId="2" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="180" fontId="3" fillId="2" borderId="3" xfId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2153,19 +2158,19 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="3" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="4" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="7" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="9" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="8" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="8"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="180" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2536,7 +2541,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IQ80"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="3" width="19.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="21.140625" style="2" customWidth="1"/>
@@ -2553,27 +2558,27 @@
     <col min="252" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="84" t="s">
+    <row r="1" spans="1:28" ht="20.25" thickBot="1">
+      <c r="A1" s="83" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-    </row>
-    <row r="2" spans="1:28" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+    </row>
+    <row r="2" spans="1:28" ht="16.5" thickTop="1">
+      <c r="A2" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
       <c r="L2" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="M2" s="68">
+      <c r="M2" s="67">
         <v>60</v>
       </c>
       <c r="V2" s="2" t="s">
@@ -2586,21 +2591,21 @@
         <v>235</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="66" t="s">
+    <row r="3" spans="1:28">
+      <c r="A3" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
       <c r="L3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="M3" s="68">
+      <c r="M3" s="67">
         <v>800</v>
       </c>
-      <c r="N3" s="69"/>
+      <c r="N3" s="68"/>
       <c r="W3" s="2" t="s">
         <v>236</v>
       </c>
@@ -2614,21 +2619,21 @@
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A4" s="66" t="s">
+    <row r="4" spans="1:28">
+      <c r="A4" s="65" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="66"/>
+      <c r="E4" s="66"/>
       <c r="L4" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="M4" s="68">
+      <c r="M4" s="67">
         <v>380</v>
       </c>
-      <c r="N4" s="69"/>
+      <c r="N4" s="68"/>
       <c r="X4" s="2" t="s">
         <v>198</v>
       </c>
@@ -2636,20 +2641,22 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="67"/>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
+    <row r="5" spans="1:28" ht="18" thickBot="1">
+      <c r="A5" s="48" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
       <c r="L5" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="M5" s="70">
+      <c r="M5" s="69">
         <f>M4/M3</f>
         <v>0.47499999999999998</v>
       </c>
-      <c r="N5" s="69"/>
+      <c r="N5" s="68"/>
       <c r="V5" s="2">
         <v>1</v>
       </c>
@@ -2666,7 +2673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="16.5" thickTop="1">
       <c r="A6" s="5" t="s">
         <v>35</v>
       </c>
@@ -2682,11 +2689,11 @@
       <c r="L6" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="M6" s="71">
+      <c r="M6" s="70">
         <f>M5^-0.75</f>
         <v>1.7477519396551873</v>
       </c>
-      <c r="N6" s="69" t="s">
+      <c r="N6" s="68" t="s">
         <v>227</v>
       </c>
       <c r="V6" s="2">
@@ -2706,15 +2713,15 @@
       </c>
       <c r="AB6" s="5"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="72" t="s">
+    <row r="7" spans="1:28">
+      <c r="A7" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="23">
-        <v>35000</v>
-      </c>
-      <c r="C7" s="23">
-        <v>343.3</v>
+      <c r="B7" s="22">
+        <v>289</v>
+      </c>
+      <c r="C7" s="22">
+        <v>90</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2722,11 +2729,11 @@
       <c r="L7" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="72">
         <f>60*M6</f>
         <v>104.86511637931123</v>
       </c>
-      <c r="N7" s="69"/>
+      <c r="N7" s="68"/>
       <c r="V7" s="2">
         <v>3</v>
       </c>
@@ -2744,7 +2751,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" ht="18" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>36</v>
       </c>
@@ -2760,10 +2767,10 @@
       <c r="E8" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="74"/>
+      <c r="H8" s="73"/>
       <c r="V8" s="5">
         <v>4</v>
       </c>
@@ -2780,28 +2787,28 @@
         <v>16.86</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="20">
+    <row r="9" spans="1:28" ht="16.5" thickTop="1">
+      <c r="B9" s="19">
         <f>B7*9.80665</f>
-        <v>343232.75</v>
-      </c>
-      <c r="C9" s="71">
+        <v>2834.12185</v>
+      </c>
+      <c r="C9" s="70">
         <f>IFERROR(C7*1000/B9,0)</f>
-        <v>1.0001959311866364</v>
-      </c>
-      <c r="D9" s="20">
+        <v>31.755868224226138</v>
+      </c>
+      <c r="D9" s="19">
         <f>C7*1000*B9</f>
-        <v>117831803075</v>
-      </c>
-      <c r="E9" s="20">
+        <v>255070966.5</v>
+      </c>
+      <c r="E9" s="19">
         <f>IFERROR(D9/C9,0)</f>
-        <v>117808720672.5625</v>
-      </c>
-      <c r="G9" s="75">
+        <v>8032246.660647423</v>
+      </c>
+      <c r="G9" s="74">
         <f>SUM(B16:E16)</f>
-        <v>1.0001959311866364</v>
-      </c>
-      <c r="H9" s="70" t="str">
+        <v>31.755868224226141</v>
+      </c>
+      <c r="H9" s="69" t="str">
         <f>IF($C$9&gt;$G$9,"Input excesive",IF($C$9&lt;$G$9,"Output excessive","Equal"))</f>
         <v>Equal</v>
       </c>
@@ -2811,9 +2818,9 @@
       <c r="M9" s="2">
         <v>1.5</v>
       </c>
-      <c r="N9" s="71">
+      <c r="N9" s="70">
         <f>IFERROR(C7*1000/M9/B9,0)</f>
-        <v>0.66679728745775757</v>
+        <v>21.170578816150758</v>
       </c>
       <c r="V9" s="2">
         <v>5</v>
@@ -2831,16 +2838,16 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="67" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" s="66" customFormat="1">
       <c r="L10" s="2" t="s">
         <v>30</v>
       </c>
       <c r="M10" s="2">
         <v>1.2</v>
       </c>
-      <c r="N10" s="71">
+      <c r="N10" s="70">
         <f>IFERROR(C7*1000/M10/B9,0)</f>
-        <v>0.83349660932219716</v>
+        <v>26.46322352018845</v>
       </c>
       <c r="O10" s="2"/>
       <c r="T10" s="5"/>
@@ -2862,24 +2869,24 @@
       </c>
       <c r="AB10" s="2"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="67"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
+    <row r="11" spans="1:28">
+      <c r="A11" s="66"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="66"/>
+      <c r="D11" s="66"/>
+      <c r="E11" s="66"/>
+      <c r="G11" s="66"/>
+      <c r="H11" s="66"/>
+      <c r="I11" s="66"/>
       <c r="L11" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M11" s="2">
         <v>3.7</v>
       </c>
-      <c r="N11" s="71">
+      <c r="N11" s="70">
         <f>IFERROR(C7*1000/M11/B9,0)</f>
-        <v>0.27032322464503683</v>
+        <v>8.5826670876286855</v>
       </c>
       <c r="V11" s="2">
         <v>7</v>
@@ -2897,23 +2904,27 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="72" t="s">
+    <row r="12" spans="1:28" ht="16.5" thickBot="1">
+      <c r="A12" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17">
-        <v>1</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17"/>
-      <c r="G12" s="76" t="s">
+      <c r="B12" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="C12" s="16">
+        <v>0.1</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16">
+        <v>1.8527</v>
+      </c>
+      <c r="G12" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="H12" s="76" t="s">
+      <c r="H12" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="I12" s="76" t="s">
+      <c r="I12" s="75" t="s">
         <v>92</v>
       </c>
       <c r="L12" s="2" t="s">
@@ -2922,9 +2933,9 @@
       <c r="M12" s="2">
         <v>1.33</v>
       </c>
-      <c r="N12" s="71">
+      <c r="N12" s="70">
         <f>IFERROR(C7*1000/M12/B9,0)</f>
-        <v>0.75202701592980181</v>
+        <v>23.876592649794087</v>
       </c>
       <c r="V12" s="2">
         <v>8</v>
@@ -2942,103 +2953,103 @@
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28">
       <c r="A13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="66" t="s">
+      <c r="B13" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="13"/>
+      <c r="E13" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="77">
+      <c r="G13" s="76">
         <f>IFERROR(E15/I13,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="78" t="str">
+        <v>0.37673593219496804</v>
+      </c>
+      <c r="H13" s="77">
         <f>IFERROR(E12/G13,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I13" s="79">
+        <v>4.9177682341200004</v>
+      </c>
+      <c r="I13" s="78">
         <v>200</v>
       </c>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-    </row>
-    <row r="14" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="30"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="30"/>
+    </row>
+    <row r="14" spans="1:28" ht="16.5" thickBot="1">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <f>IFERROR(VLOOKUP(B13,Database!$A$2:$B$56,2,0),"-")</f>
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="C14" s="9">
+        <v>0.70209999999999995</v>
+      </c>
+      <c r="C14" s="8">
         <f>IFERROR(VLOOKUP(C13,Database!$A$2:$B$56,2,0),"-")</f>
-        <v>0.216</v>
-      </c>
-      <c r="D14" s="9" t="str">
+        <v>5</v>
+      </c>
+      <c r="D14" s="8" t="str">
         <f>IFERROR(VLOOKUP(D13,Database!$A$2:$B$56,2,0),"-")</f>
         <v>-</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="9">
         <v>0</v>
       </c>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31" t="s">
+      <c r="L14" s="30"/>
+      <c r="M14" s="30" t="s">
         <v>230</v>
       </c>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="31" t="s">
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31" t="s">
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="72" t="s">
+    <row r="15" spans="1:28" ht="16.5" thickTop="1">
+      <c r="A15" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="75">
+      <c r="B15" s="74">
         <f>IFERROR(C9*B12/SUM(B17:D17),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="75">
+        <v>16.267541736707209</v>
+      </c>
+      <c r="C15" s="74">
         <f>IFERROR(C9*C12/SUM(B17:D17),"-")</f>
-        <v>4.6305367184566499</v>
-      </c>
-      <c r="D15" s="75">
+        <v>4.0668854341768021</v>
+      </c>
+      <c r="D15" s="74">
         <f>IFERROR(C9*D12/SUM(B17:D17),"-")</f>
         <v>0</v>
       </c>
-      <c r="E15" s="75">
+      <c r="E15" s="74">
         <f>IFERROR(C9*E12/SUM(B17:D17),0)</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="31"/>
-      <c r="M15" s="22">
+        <v>75.347186438993603</v>
+      </c>
+      <c r="L15" s="30"/>
+      <c r="M15" s="21">
         <v>2080</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
-      <c r="P15" s="22">
+      <c r="P15" s="21">
         <v>2100</v>
       </c>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="30"/>
       <c r="W15" s="2" t="s">
         <v>236</v>
       </c>
@@ -3052,38 +3063,34 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28">
       <c r="A16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B16" s="70">
+      <c r="B16" s="69">
         <f>IFERROR($B$14*$B$15,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="70">
+        <v>11.42144105334213</v>
+      </c>
+      <c r="C16" s="69">
         <f t="shared" ref="C16:D16" si="0">IFERROR(C14*C15,"-")</f>
-        <v>1.0001959311866364</v>
-      </c>
-      <c r="D16" s="70" t="str">
+        <v>20.334427170884013</v>
+      </c>
+      <c r="D16" s="69" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="E16" s="70">
+      <c r="E16" s="69">
         <f>E14*E15</f>
         <v>0</v>
       </c>
-      <c r="F16" s="2">
-        <f>SUM(B16:D16)</f>
-        <v>1.0001959311866364</v>
-      </c>
-      <c r="L16" s="31"/>
+      <c r="L16" s="30"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="65">
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="64">
         <v>0.1</v>
       </c>
       <c r="X16" s="2" t="s">
@@ -3093,52 +3100,48 @@
         <v>198</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28">
       <c r="A17" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="70">
+      <c r="B17" s="69">
         <f>IFERROR(B12*B14,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="70">
+        <v>0.28083999999999998</v>
+      </c>
+      <c r="C17" s="69">
         <f t="shared" ref="C17:D17" si="1">IFERROR(C12*C14,"-")</f>
-        <v>0.216</v>
-      </c>
-      <c r="D17" s="70" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="69" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="E17" s="70"/>
-      <c r="F17" s="2">
-        <f>B16/C16</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="31" t="s">
+      <c r="E17" s="69"/>
+      <c r="L17" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="M17" s="80">
+      <c r="M17" s="79">
         <f t="shared" ref="M17:M23" si="2">N17*$O$17</f>
         <v>2080</v>
       </c>
-      <c r="N17" s="31">
+      <c r="N17" s="30">
         <v>800</v>
       </c>
-      <c r="O17" s="21">
+      <c r="O17" s="20">
         <f>($M$15/N17)</f>
         <v>2.6</v>
       </c>
-      <c r="P17" s="80">
+      <c r="P17" s="79">
         <f t="shared" ref="P17:P23" si="3">$P$15*Q17</f>
         <v>2100</v>
       </c>
-      <c r="Q17" s="31">
-        <v>1</v>
-      </c>
-      <c r="R17" s="31">
+      <c r="Q17" s="30">
+        <v>1</v>
+      </c>
+      <c r="R17" s="30">
         <v>1E-4</v>
       </c>
-      <c r="S17" s="19">
+      <c r="S17" s="18">
         <f t="shared" ref="S17:S23" si="4">$S$16*R17</f>
         <v>1.0000000000000001E-5</v>
       </c>
@@ -3158,37 +3161,33 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28">
       <c r="A18" s="5"/>
-      <c r="F18" s="2" t="e">
-        <f>B12/F17</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="L18" s="31" t="s">
+      <c r="G18" s="66"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="66"/>
+      <c r="L18" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="M18" s="80">
+      <c r="M18" s="79">
         <f t="shared" si="2"/>
         <v>657.80000000000007</v>
       </c>
-      <c r="N18" s="31">
+      <c r="N18" s="30">
         <v>253</v>
       </c>
       <c r="O18" s="5"/>
-      <c r="P18" s="80">
+      <c r="P18" s="79">
         <f t="shared" si="3"/>
         <v>4977</v>
       </c>
-      <c r="Q18" s="31">
+      <c r="Q18" s="30">
         <v>2.37</v>
       </c>
-      <c r="R18" s="31">
+      <c r="R18" s="30">
         <v>1.4672099999999999E-4</v>
       </c>
-      <c r="S18" s="19">
+      <c r="S18" s="18">
         <f t="shared" si="4"/>
         <v>1.46721E-5</v>
       </c>
@@ -3198,39 +3197,39 @@
       <c r="W18" s="2">
         <v>1</v>
       </c>
-      <c r="X18" s="81">
+      <c r="X18" s="80">
         <v>0.61019999999999996</v>
       </c>
       <c r="Z18" s="2">
         <v>1</v>
       </c>
-      <c r="AA18" s="81">
+      <c r="AA18" s="80">
         <v>4.3200000000000002E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="L19" s="31" t="s">
+    <row r="19" spans="1:28">
+      <c r="L19" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="M19" s="80">
+      <c r="M19" s="79">
         <f t="shared" si="2"/>
         <v>1040</v>
       </c>
-      <c r="N19" s="31">
+      <c r="N19" s="30">
         <v>400</v>
       </c>
       <c r="O19" s="5"/>
-      <c r="P19" s="80">
+      <c r="P19" s="79">
         <f t="shared" si="3"/>
         <v>3528</v>
       </c>
-      <c r="Q19" s="31">
+      <c r="Q19" s="30">
         <v>1.68</v>
       </c>
-      <c r="R19" s="31">
+      <c r="R19" s="30">
         <v>2.9090700000000003E-4</v>
       </c>
-      <c r="S19" s="19">
+      <c r="S19" s="18">
         <f t="shared" si="4"/>
         <v>2.9090700000000003E-5</v>
       </c>
@@ -3240,63 +3239,70 @@
       <c r="W19" s="2">
         <v>2.95</v>
       </c>
-      <c r="X19" s="81">
+      <c r="X19" s="80">
         <f t="shared" ref="X19:X24" si="5">$X$18*W19</f>
         <v>1.80009</v>
       </c>
       <c r="Z19" s="2">
         <v>2.95</v>
       </c>
-      <c r="AA19" s="81">
+      <c r="AA19" s="80">
         <f t="shared" ref="AA19:AA24" si="6">$AA$18*W19</f>
         <v>0.12744000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="L20" s="31" t="s">
+    <row r="20" spans="1:28" ht="18" thickBot="1">
+      <c r="A20" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="L20" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="M20" s="80">
+      <c r="M20" s="79">
         <f t="shared" si="2"/>
         <v>657.80000000000007</v>
       </c>
-      <c r="N20" s="31">
+      <c r="N20" s="30">
         <v>253</v>
       </c>
       <c r="O20" s="5"/>
-      <c r="P20" s="80">
+      <c r="P20" s="79">
         <f t="shared" si="3"/>
         <v>4977</v>
       </c>
-      <c r="Q20" s="31">
+      <c r="Q20" s="30">
         <v>2.37</v>
       </c>
-      <c r="R20" s="31">
+      <c r="R20" s="30">
         <v>1.53485E-4</v>
       </c>
-      <c r="S20" s="19">
+      <c r="S20" s="18">
         <f t="shared" si="4"/>
         <v>1.5348500000000001E-5</v>
       </c>
       <c r="V20" s="5">
         <v>4</v>
       </c>
-      <c r="W20" s="39">
+      <c r="W20" s="38">
         <v>5.53</v>
       </c>
-      <c r="X20" s="81">
+      <c r="X20" s="80">
         <f t="shared" si="5"/>
         <v>3.374406</v>
       </c>
-      <c r="Y20" s="39"/>
-      <c r="Z20" s="39"/>
-      <c r="AA20" s="81">
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="38"/>
+      <c r="AA20" s="80">
         <f t="shared" si="6"/>
         <v>0.23889600000000002</v>
       </c>
-      <c r="AB20" s="39"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AB20" s="38"/>
+    </row>
+    <row r="21" spans="1:28" ht="16.5" thickTop="1">
       <c r="A21" s="5" t="s">
         <v>35</v>
       </c>
@@ -3309,106 +3315,106 @@
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-      <c r="L21" s="31" t="s">
+      <c r="L21" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="M21" s="80">
+      <c r="M21" s="79">
         <f t="shared" si="2"/>
         <v>1575.6000000000001</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="30">
         <v>606</v>
       </c>
       <c r="O21" s="5"/>
-      <c r="P21" s="80">
+      <c r="P21" s="79">
         <f t="shared" si="3"/>
         <v>2583</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="30">
         <v>1.23</v>
       </c>
-      <c r="R21" s="31">
+      <c r="R21" s="30">
         <v>3.6680399999999998E-4</v>
       </c>
-      <c r="S21" s="19">
+      <c r="S21" s="18">
         <f t="shared" si="4"/>
         <v>3.6680400000000002E-5</v>
       </c>
       <c r="V21" s="2">
         <v>5</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="30">
         <v>8.86</v>
       </c>
-      <c r="X21" s="81">
+      <c r="X21" s="80">
         <f t="shared" si="5"/>
         <v>5.4063719999999993</v>
       </c>
-      <c r="Y21" s="31"/>
-      <c r="Z21" s="31"/>
-      <c r="AA21" s="81">
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="30"/>
+      <c r="AA21" s="80">
         <f t="shared" si="6"/>
         <v>0.38275199999999998</v>
       </c>
-      <c r="AB21" s="31"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="72" t="s">
+      <c r="AB21" s="30"/>
+    </row>
+    <row r="22" spans="1:28">
+      <c r="A22" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="B22" s="23">
-        <v>35000</v>
-      </c>
-      <c r="C22" s="23">
-        <v>350</v>
+      <c r="B22" s="22">
+        <v>800</v>
+      </c>
+      <c r="C22" s="22">
+        <v>60</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-      <c r="L22" s="31" t="s">
+      <c r="L22" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="M22" s="80">
+      <c r="M22" s="79">
         <f t="shared" si="2"/>
         <v>735.80000000000007</v>
       </c>
-      <c r="N22" s="31">
+      <c r="N22" s="30">
         <v>283</v>
       </c>
       <c r="O22" s="5"/>
-      <c r="P22" s="80">
+      <c r="P22" s="79">
         <f t="shared" si="3"/>
         <v>4578</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="30">
         <v>2.1800000000000002</v>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="30">
         <v>2.6534900000000001E-4</v>
       </c>
-      <c r="S22" s="19">
+      <c r="S22" s="18">
         <f t="shared" si="4"/>
         <v>2.6534900000000002E-5</v>
       </c>
       <c r="V22" s="2">
         <v>6</v>
       </c>
-      <c r="W22" s="31">
+      <c r="W22" s="30">
         <v>12.92</v>
       </c>
-      <c r="X22" s="81">
+      <c r="X22" s="80">
         <f t="shared" si="5"/>
         <v>7.8837839999999995</v>
       </c>
-      <c r="Y22" s="31"/>
-      <c r="Z22" s="31"/>
-      <c r="AA22" s="81">
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="80">
         <f t="shared" si="6"/>
         <v>0.55814399999999997</v>
       </c>
-      <c r="AB22" s="31"/>
-    </row>
-    <row r="23" spans="1:28" ht="18" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="AB22" s="30"/>
+    </row>
+    <row r="23" spans="1:28" ht="18" thickBot="1">
       <c r="A23" s="2" t="s">
         <v>36</v>
       </c>
@@ -3424,75 +3430,75 @@
       <c r="E23" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="G23" s="74" t="s">
+      <c r="G23" s="73" t="s">
         <v>72</v>
       </c>
-      <c r="H23" s="74"/>
-      <c r="L23" s="31" t="s">
+      <c r="H23" s="73"/>
+      <c r="L23" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="M23" s="80">
+      <c r="M23" s="79">
         <f t="shared" si="2"/>
         <v>962</v>
       </c>
-      <c r="N23" s="31">
+      <c r="N23" s="30">
         <v>370</v>
       </c>
       <c r="O23" s="5"/>
-      <c r="P23" s="80">
+      <c r="P23" s="79">
         <f t="shared" si="3"/>
         <v>3738</v>
       </c>
-      <c r="Q23" s="31">
+      <c r="Q23" s="30">
         <v>1.78</v>
       </c>
-      <c r="R23" s="31">
+      <c r="R23" s="30">
         <v>3.6195500000000001E-4</v>
       </c>
-      <c r="S23" s="19">
+      <c r="S23" s="18">
         <f t="shared" si="4"/>
         <v>3.6195500000000003E-5</v>
       </c>
       <c r="V23" s="2">
         <v>7</v>
       </c>
-      <c r="W23" s="31">
+      <c r="W23" s="30">
         <v>17.7</v>
       </c>
-      <c r="X23" s="81">
+      <c r="X23" s="80">
         <f t="shared" si="5"/>
         <v>10.80054</v>
       </c>
-      <c r="Y23" s="31"/>
-      <c r="Z23" s="31"/>
-      <c r="AA23" s="81">
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
+      <c r="AA23" s="80">
         <f t="shared" si="6"/>
         <v>0.76463999999999999</v>
       </c>
-      <c r="AB23" s="31"/>
-    </row>
-    <row r="24" spans="1:28" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="20">
+      <c r="AB23" s="30"/>
+    </row>
+    <row r="24" spans="1:28" ht="16.5" thickTop="1">
+      <c r="B24" s="19">
         <f>B22*9.80665</f>
-        <v>343232.75</v>
-      </c>
-      <c r="C24" s="71">
+        <v>7845.32</v>
+      </c>
+      <c r="C24" s="70">
         <f>IFERROR(C22*1000/B24,0)</f>
-        <v>1.0197162129779282</v>
-      </c>
-      <c r="D24" s="20">
+        <v>7.6478715973344622</v>
+      </c>
+      <c r="D24" s="19">
         <f>C22*1000*B24</f>
-        <v>120131462500</v>
-      </c>
-      <c r="E24" s="20">
+        <v>470719200</v>
+      </c>
+      <c r="E24" s="19">
         <f>IFERROR(D24/C24,0)</f>
-        <v>117808720672.5625</v>
-      </c>
-      <c r="G24" s="75">
+        <v>61549045.902399994</v>
+      </c>
+      <c r="G24" s="74">
         <f>SUM(B31:E31)</f>
-        <v>1.0197162129779282</v>
-      </c>
-      <c r="H24" s="70" t="str">
+        <v>7.6478715973344622</v>
+      </c>
+      <c r="H24" s="69" t="str">
         <f>IF($C$9&gt;$G$9,"Input excesive",IF($C$9&lt;$G$9,"Output excessive","Equal"))</f>
         <v>Equal</v>
       </c>
@@ -3502,744 +3508,722 @@
       <c r="W24" s="5">
         <v>23.25</v>
       </c>
-      <c r="X24" s="81">
+      <c r="X24" s="80">
         <f t="shared" si="5"/>
         <v>14.187149999999999</v>
       </c>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
-      <c r="AA24" s="81">
+      <c r="AA24" s="80">
         <f t="shared" si="6"/>
         <v>1.0044</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="67"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="67"/>
-      <c r="G25" s="67"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="67"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="67"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="67"/>
-      <c r="I26" s="67"/>
-      <c r="J26" s="67"/>
-    </row>
-    <row r="27" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="72" t="s">
+    <row r="25" spans="1:28">
+      <c r="A25" s="66"/>
+      <c r="B25" s="66"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66"/>
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="66"/>
+    </row>
+    <row r="26" spans="1:28">
+      <c r="A26" s="66"/>
+      <c r="B26" s="66"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66"/>
+    </row>
+    <row r="27" spans="1:28" ht="16.5" thickBot="1">
+      <c r="A27" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17">
-        <v>0.90949999999999998</v>
-      </c>
-      <c r="D27" s="83">
-        <f>C27/10</f>
-        <v>9.0950000000000003E-2</v>
-      </c>
-      <c r="E27" s="17"/>
-      <c r="G27" s="76" t="s">
+      <c r="B27" s="16">
+        <v>1</v>
+      </c>
+      <c r="C27" s="16">
+        <v>0</v>
+      </c>
+      <c r="D27" s="82"/>
+      <c r="E27" s="16">
+        <v>4.5380000000000003</v>
+      </c>
+      <c r="G27" s="75" t="s">
         <v>88</v>
       </c>
-      <c r="H27" s="76" t="s">
+      <c r="H27" s="75" t="s">
         <v>91</v>
       </c>
-      <c r="I27" s="76" t="s">
+      <c r="I27" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="J27" s="67"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="J27" s="66"/>
+    </row>
+    <row r="28" spans="1:28">
       <c r="A28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="66" t="s">
+      <c r="B28" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="G28" s="77">
+      <c r="G28" s="76">
         <f>IFERROR(E30/I28,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="78" t="str">
+        <v>2.4492619131054192</v>
+      </c>
+      <c r="H28" s="77">
         <f>IFERROR(E27/G28,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I28" s="79">
+        <v>1.8528030733333334</v>
+      </c>
+      <c r="I28" s="78">
         <v>200</v>
       </c>
-      <c r="J28" s="67"/>
-    </row>
-    <row r="29" spans="1:28" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J28" s="66"/>
+    </row>
+    <row r="29" spans="1:28" ht="16.5" thickBot="1">
       <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="9">
+      <c r="B29" s="8">
         <f>IFERROR(VLOOKUP(B28,Database!$A$2:$B$56,2,0),"-")</f>
+        <v>7.0849999999999996E-2</v>
+      </c>
+      <c r="C29" s="8">
+        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$56,2,0),"-")</f>
         <v>5</v>
       </c>
-      <c r="C29" s="9">
-        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$56,2,0),"-")</f>
-        <v>0.35399999999999998</v>
-      </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8" t="str">
         <f>IFERROR(VLOOKUP(D28,Database!$A$2:$B$56,2,0),"-")</f>
-        <v>5</v>
-      </c>
-      <c r="E29" s="10">
+        <v>-</v>
+      </c>
+      <c r="E29" s="9">
         <v>0</v>
       </c>
-      <c r="J29" s="67"/>
-    </row>
-    <row r="30" spans="1:28" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="72" t="s">
+      <c r="J29" s="66"/>
+    </row>
+    <row r="30" spans="1:28" ht="16.5" thickTop="1">
+      <c r="A30" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="75">
+      <c r="B30" s="74">
         <f>IFERROR(C24*B27/SUM(B32:D32),"-")</f>
+        <v>107.94455324395854</v>
+      </c>
+      <c r="C30" s="74">
+        <f>IFERROR(C24*C27/SUM(B32:D32),"-")</f>
         <v>0</v>
       </c>
-      <c r="C30" s="75">
-        <f>IFERROR(C24*C27/SUM(B32:D32),"-")</f>
-        <v>1.1940470877961689</v>
-      </c>
-      <c r="D30" s="75">
+      <c r="D30" s="74">
         <f>IFERROR(C24*D27/SUM(B32:D32),"-")</f>
-        <v>0.1194047087796169</v>
-      </c>
-      <c r="E30" s="75">
+        <v>0</v>
+      </c>
+      <c r="E30" s="74">
         <f>IFERROR(C24*E27/SUM(B32:D32),0)</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="67"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+        <v>489.85238262108385</v>
+      </c>
+      <c r="J30" s="66"/>
+    </row>
+    <row r="31" spans="1:28">
       <c r="A31" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="70">
+      <c r="B31" s="69">
         <f>IFERROR($B$29*$B$30,"-")</f>
+        <v>7.6478715973344622</v>
+      </c>
+      <c r="C31" s="69">
+        <f t="shared" ref="C31:D31" si="7">IFERROR(C29*C30,"-")</f>
         <v>0</v>
       </c>
-      <c r="C31" s="70">
-        <f t="shared" ref="C31:D31" si="7">IFERROR(C29*C30,"-")</f>
-        <v>0.42269266907984376</v>
-      </c>
-      <c r="D31" s="70">
+      <c r="D31" s="69" t="str">
         <f t="shared" si="7"/>
-        <v>0.59702354389808443</v>
-      </c>
-      <c r="E31" s="70">
+        <v>-</v>
+      </c>
+      <c r="E31" s="69">
         <f>E29*E30</f>
         <v>0</v>
       </c>
-      <c r="F31" s="2">
-        <f>SUM(B31:D31)</f>
-        <v>1.0197162129779282</v>
-      </c>
-      <c r="J31" s="67"/>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="J31" s="66"/>
+    </row>
+    <row r="32" spans="1:28">
       <c r="A32" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="70">
+      <c r="B32" s="69">
         <f>IFERROR(B27*B29,"-")</f>
+        <v>7.0849999999999996E-2</v>
+      </c>
+      <c r="C32" s="69">
+        <f t="shared" ref="C32:D32" si="8">IFERROR(C27*C29,"-")</f>
         <v>0</v>
       </c>
-      <c r="C32" s="70">
-        <f t="shared" ref="C32:D32" si="8">IFERROR(C27*C29,"-")</f>
-        <v>0.321963</v>
-      </c>
-      <c r="D32" s="70">
+      <c r="D32" s="69" t="str">
         <f t="shared" si="8"/>
-        <v>0.45474999999999999</v>
-      </c>
-      <c r="E32" s="70"/>
-      <c r="F32" s="2">
-        <f>B31/C31</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="82">
-        <f>C27+D27</f>
-        <v>1.0004500000000001</v>
-      </c>
-      <c r="J32" s="67"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-</v>
+      </c>
+      <c r="E32" s="69"/>
+      <c r="H32" s="81"/>
+      <c r="J32" s="66"/>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" s="5"/>
-      <c r="F33" s="2" t="e">
-        <f>B27/F32</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G33" s="67"/>
-      <c r="H33" s="67"/>
-      <c r="I33" s="67"/>
-      <c r="J33" s="67"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D34" s="2">
-        <f>0.143/C30</f>
-        <v>0.11976077113</v>
-      </c>
-      <c r="J34" s="67"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="D35" s="6">
-        <f>C27*D34</f>
-        <v>0.108922421342735</v>
-      </c>
-      <c r="J35" s="67"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="J36" s="67"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="67"/>
-      <c r="B37" s="67"/>
-      <c r="C37" s="67"/>
-      <c r="D37" s="67"/>
-      <c r="E37" s="67"/>
-      <c r="F37" s="67"/>
-      <c r="G37" s="67"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="67"/>
-      <c r="J37" s="67"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="67"/>
-      <c r="B38" s="67"/>
-      <c r="C38" s="67"/>
-      <c r="D38" s="67"/>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="67"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="67"/>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="67"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="67"/>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
-      <c r="J40" s="67"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="67"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="67"/>
-      <c r="F41" s="67"/>
-      <c r="G41" s="67"/>
-      <c r="H41" s="67"/>
-      <c r="I41" s="67"/>
-      <c r="J41" s="67"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="67"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="67"/>
-      <c r="F42" s="67"/>
-      <c r="G42" s="67"/>
-      <c r="H42" s="67"/>
-      <c r="I42" s="67"/>
-      <c r="J42" s="67"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="67"/>
-      <c r="B43" s="67"/>
-      <c r="C43" s="67"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="67"/>
-      <c r="F43" s="67"/>
-      <c r="G43" s="67"/>
-      <c r="H43" s="67"/>
-      <c r="I43" s="67"/>
-      <c r="J43" s="67"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="67"/>
-      <c r="B44" s="67"/>
-      <c r="C44" s="67"/>
-      <c r="D44" s="67"/>
-      <c r="E44" s="67"/>
-      <c r="F44" s="67"/>
-      <c r="G44" s="67"/>
-      <c r="H44" s="67"/>
-      <c r="I44" s="67"/>
-      <c r="J44" s="67"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="67"/>
-      <c r="B45" s="67"/>
-      <c r="C45" s="67"/>
-      <c r="D45" s="67"/>
-      <c r="E45" s="67"/>
-      <c r="F45" s="67"/>
-      <c r="G45" s="67"/>
-      <c r="H45" s="67"/>
-      <c r="I45" s="67"/>
-      <c r="J45" s="67"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="67"/>
-      <c r="B46" s="67"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
-      <c r="H46" s="67"/>
-      <c r="I46" s="67"/>
-      <c r="J46" s="67"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="67"/>
-      <c r="B47" s="67"/>
-      <c r="C47" s="67"/>
-      <c r="D47" s="67"/>
-      <c r="E47" s="67"/>
-      <c r="F47" s="67"/>
-      <c r="G47" s="67"/>
-      <c r="H47" s="67"/>
-      <c r="I47" s="67"/>
-      <c r="J47" s="67"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="67"/>
-      <c r="B48" s="67"/>
-      <c r="C48" s="67"/>
-      <c r="D48" s="67"/>
-      <c r="E48" s="67"/>
-      <c r="F48" s="67"/>
-      <c r="G48" s="67"/>
-      <c r="H48" s="67"/>
-      <c r="I48" s="67"/>
-      <c r="J48" s="67"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="67"/>
-      <c r="B49" s="67"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
-      <c r="E49" s="67"/>
-      <c r="F49" s="67"/>
-      <c r="G49" s="67"/>
-      <c r="H49" s="67"/>
-      <c r="I49" s="67"/>
-      <c r="J49" s="67"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="67"/>
-      <c r="B50" s="67"/>
-      <c r="C50" s="67"/>
-      <c r="D50" s="67"/>
-      <c r="E50" s="67"/>
-      <c r="F50" s="67"/>
-      <c r="G50" s="67"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="67"/>
-      <c r="J50" s="67"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="67"/>
-      <c r="B51" s="67"/>
-      <c r="C51" s="67"/>
-      <c r="D51" s="67"/>
-      <c r="E51" s="67"/>
-      <c r="F51" s="67"/>
-      <c r="G51" s="67"/>
-      <c r="H51" s="67"/>
-      <c r="I51" s="67"/>
-      <c r="J51" s="67"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="67"/>
-      <c r="B52" s="67"/>
-      <c r="C52" s="67"/>
-      <c r="D52" s="67"/>
-      <c r="E52" s="67"/>
-      <c r="F52" s="67"/>
-      <c r="G52" s="67"/>
-      <c r="H52" s="67"/>
-      <c r="I52" s="67"/>
-      <c r="J52" s="67"/>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="67"/>
-      <c r="B53" s="67"/>
-      <c r="C53" s="67"/>
-      <c r="D53" s="67"/>
-      <c r="E53" s="67"/>
-      <c r="F53" s="67"/>
-      <c r="G53" s="67"/>
-      <c r="H53" s="67"/>
-      <c r="I53" s="67"/>
-      <c r="J53" s="67"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="67"/>
-      <c r="B54" s="67"/>
-      <c r="C54" s="67"/>
-      <c r="D54" s="67"/>
-      <c r="E54" s="67"/>
-      <c r="F54" s="67"/>
-      <c r="G54" s="67"/>
-      <c r="H54" s="67"/>
-      <c r="I54" s="67"/>
-      <c r="J54" s="67"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="67"/>
-      <c r="B55" s="67"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
-      <c r="E55" s="67"/>
-      <c r="F55" s="67"/>
-      <c r="G55" s="67"/>
-      <c r="H55" s="67"/>
-      <c r="I55" s="67"/>
-      <c r="J55" s="67"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="67"/>
-      <c r="B56" s="67"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="67"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="67"/>
-      <c r="I56" s="67"/>
-      <c r="J56" s="67"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="67"/>
-      <c r="B57" s="67"/>
-      <c r="C57" s="67"/>
-      <c r="D57" s="67"/>
-      <c r="E57" s="67"/>
-      <c r="F57" s="67"/>
-      <c r="G57" s="67"/>
-      <c r="H57" s="67"/>
-      <c r="I57" s="67"/>
-      <c r="J57" s="67"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="67"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="67"/>
-      <c r="D58" s="67"/>
-      <c r="E58" s="67"/>
-      <c r="F58" s="67"/>
-      <c r="G58" s="67"/>
-      <c r="H58" s="67"/>
-      <c r="I58" s="67"/>
-      <c r="J58" s="67"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="67"/>
-      <c r="B59" s="67"/>
-      <c r="C59" s="67"/>
-      <c r="D59" s="67"/>
-      <c r="E59" s="67"/>
-      <c r="F59" s="67"/>
-      <c r="G59" s="67"/>
-      <c r="H59" s="67"/>
-      <c r="I59" s="67"/>
-      <c r="J59" s="67"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="67"/>
-      <c r="B60" s="67"/>
-      <c r="C60" s="67"/>
-      <c r="D60" s="67"/>
-      <c r="E60" s="67"/>
-      <c r="F60" s="67"/>
-      <c r="G60" s="67"/>
-      <c r="H60" s="67"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="67"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="67"/>
-      <c r="B61" s="67"/>
-      <c r="C61" s="67"/>
-      <c r="D61" s="67"/>
-      <c r="E61" s="67"/>
-      <c r="F61" s="67"/>
-      <c r="G61" s="67"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="67"/>
-      <c r="J61" s="67"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="67"/>
-      <c r="B62" s="67"/>
-      <c r="C62" s="67"/>
-      <c r="D62" s="67"/>
-      <c r="E62" s="67"/>
-      <c r="F62" s="67"/>
-      <c r="G62" s="67"/>
-      <c r="H62" s="67"/>
-      <c r="I62" s="67"/>
-      <c r="J62" s="67"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="67"/>
-      <c r="B63" s="67"/>
-      <c r="C63" s="67"/>
-      <c r="D63" s="67"/>
-      <c r="E63" s="67"/>
-      <c r="F63" s="67"/>
-      <c r="G63" s="67"/>
-      <c r="H63" s="67"/>
-      <c r="I63" s="67"/>
-      <c r="J63" s="67"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="67"/>
-      <c r="B64" s="67"/>
-      <c r="C64" s="67"/>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
-      <c r="H64" s="67"/>
-      <c r="I64" s="67"/>
-      <c r="J64" s="67"/>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="67"/>
-      <c r="B65" s="67"/>
-      <c r="C65" s="67"/>
-      <c r="D65" s="67"/>
-      <c r="E65" s="67"/>
-      <c r="F65" s="67"/>
-      <c r="G65" s="67"/>
-      <c r="H65" s="67"/>
-      <c r="I65" s="67"/>
-      <c r="J65" s="67"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="67"/>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67"/>
-      <c r="D66" s="67"/>
-      <c r="E66" s="67"/>
-      <c r="F66" s="67"/>
-      <c r="G66" s="67"/>
-      <c r="H66" s="67"/>
-      <c r="I66" s="67"/>
-      <c r="J66" s="67"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="67"/>
-      <c r="B67" s="67"/>
-      <c r="C67" s="67"/>
-      <c r="D67" s="67"/>
-      <c r="E67" s="67"/>
-      <c r="F67" s="67"/>
-      <c r="G67" s="67"/>
-      <c r="H67" s="67"/>
-      <c r="I67" s="67"/>
-      <c r="J67" s="67"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="67"/>
-      <c r="B68" s="67"/>
-      <c r="C68" s="67"/>
-      <c r="D68" s="67"/>
-      <c r="E68" s="67"/>
-      <c r="F68" s="67"/>
-      <c r="G68" s="67"/>
-      <c r="H68" s="67"/>
-      <c r="I68" s="67"/>
-      <c r="J68" s="67"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="67"/>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67"/>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="67"/>
-      <c r="G69" s="67"/>
-      <c r="H69" s="67"/>
-      <c r="I69" s="67"/>
-      <c r="J69" s="67"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="67"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="67"/>
-      <c r="E70" s="67"/>
-      <c r="F70" s="67"/>
-      <c r="G70" s="67"/>
-      <c r="H70" s="67"/>
-      <c r="I70" s="67"/>
-      <c r="J70" s="67"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="67"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="67"/>
-      <c r="D71" s="67"/>
-      <c r="E71" s="67"/>
-      <c r="F71" s="67"/>
-      <c r="G71" s="67"/>
-      <c r="H71" s="67"/>
-      <c r="I71" s="67"/>
-      <c r="J71" s="67"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="67"/>
-      <c r="B72" s="67"/>
-      <c r="C72" s="67"/>
-      <c r="D72" s="67"/>
-      <c r="E72" s="67"/>
-      <c r="F72" s="67"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="67"/>
-      <c r="I72" s="67"/>
-      <c r="J72" s="67"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="67"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="67"/>
-      <c r="D73" s="67"/>
-      <c r="E73" s="67"/>
-      <c r="F73" s="67"/>
-      <c r="G73" s="67"/>
-      <c r="H73" s="67"/>
-      <c r="I73" s="67"/>
-      <c r="J73" s="67"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="67"/>
-      <c r="B74" s="67"/>
-      <c r="C74" s="67"/>
-      <c r="D74" s="67"/>
-      <c r="E74" s="67"/>
-      <c r="F74" s="67"/>
-      <c r="G74" s="67"/>
-      <c r="H74" s="67"/>
-      <c r="I74" s="67"/>
-      <c r="J74" s="67"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="67"/>
-      <c r="B75" s="67"/>
-      <c r="C75" s="67"/>
-      <c r="D75" s="67"/>
-      <c r="E75" s="67"/>
-      <c r="F75" s="67"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="67"/>
-      <c r="I75" s="67"/>
-      <c r="J75" s="67"/>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="67"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="67"/>
-      <c r="D76" s="67"/>
-      <c r="E76" s="67"/>
-      <c r="F76" s="67"/>
-      <c r="G76" s="67"/>
-      <c r="H76" s="67"/>
-      <c r="I76" s="67"/>
-      <c r="J76" s="67"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="67"/>
-      <c r="B77" s="67"/>
-      <c r="C77" s="67"/>
-      <c r="D77" s="67"/>
-      <c r="E77" s="67"/>
-      <c r="F77" s="67"/>
-      <c r="G77" s="67"/>
-      <c r="H77" s="67"/>
-      <c r="I77" s="67"/>
-      <c r="J77" s="67"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="67"/>
-      <c r="B78" s="67"/>
-      <c r="C78" s="67"/>
-      <c r="D78" s="67"/>
-      <c r="E78" s="67"/>
-      <c r="F78" s="67"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="67"/>
-      <c r="I78" s="67"/>
-      <c r="J78" s="67"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="67"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="67"/>
-      <c r="D79" s="67"/>
-      <c r="E79" s="67"/>
-      <c r="F79" s="67"/>
-      <c r="G79" s="67"/>
-      <c r="H79" s="67"/>
-      <c r="I79" s="67"/>
-      <c r="J79" s="67"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="67"/>
-      <c r="B80" s="67"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="67"/>
-      <c r="E80" s="67"/>
-      <c r="F80" s="67"/>
-      <c r="G80" s="67"/>
-      <c r="H80" s="67"/>
-      <c r="I80" s="67"/>
-      <c r="J80" s="67"/>
+      <c r="G33" s="66"/>
+      <c r="H33" s="66"/>
+      <c r="I33" s="66"/>
+      <c r="J33" s="66"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="D34"/>
+      <c r="J34" s="66"/>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="D35"/>
+      <c r="J35" s="66"/>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="J36" s="66"/>
+    </row>
+    <row r="37" spans="1:10">
+      <c r="A37" s="66"/>
+      <c r="B37" s="66"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="66"/>
+      <c r="E37" s="66"/>
+      <c r="F37" s="66"/>
+      <c r="G37" s="66"/>
+      <c r="H37" s="66"/>
+      <c r="I37" s="66"/>
+      <c r="J37" s="66"/>
+    </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="66"/>
+      <c r="B38" s="66"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="66"/>
+      <c r="E38" s="66"/>
+      <c r="F38" s="66"/>
+      <c r="G38" s="66"/>
+      <c r="H38" s="66"/>
+      <c r="I38" s="66"/>
+      <c r="J38" s="66"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="66"/>
+      <c r="B39" s="66"/>
+      <c r="C39" s="66"/>
+      <c r="D39" s="66"/>
+      <c r="E39" s="66"/>
+      <c r="F39" s="66"/>
+      <c r="G39" s="66"/>
+      <c r="H39" s="66"/>
+      <c r="I39" s="66"/>
+      <c r="J39" s="66"/>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="66"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="66"/>
+      <c r="D40" s="66"/>
+      <c r="E40" s="66"/>
+      <c r="F40" s="66"/>
+      <c r="G40" s="66"/>
+      <c r="H40" s="66"/>
+      <c r="I40" s="66"/>
+      <c r="J40" s="66"/>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="66"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+      <c r="F41" s="66"/>
+      <c r="G41" s="66"/>
+      <c r="H41" s="66"/>
+      <c r="I41" s="66"/>
+      <c r="J41" s="66"/>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="66"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
+      <c r="D42" s="66"/>
+      <c r="E42" s="66"/>
+      <c r="F42" s="66"/>
+      <c r="G42" s="66"/>
+      <c r="H42" s="66"/>
+      <c r="I42" s="66"/>
+      <c r="J42" s="66"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="66"/>
+      <c r="B43" s="66"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="66"/>
+      <c r="F43" s="66"/>
+      <c r="G43" s="66"/>
+      <c r="H43" s="66"/>
+      <c r="I43" s="66"/>
+      <c r="J43" s="66"/>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="66"/>
+      <c r="B44" s="66"/>
+      <c r="C44" s="66"/>
+      <c r="D44" s="66"/>
+      <c r="E44" s="66"/>
+      <c r="F44" s="66"/>
+      <c r="G44" s="66"/>
+      <c r="H44" s="66"/>
+      <c r="I44" s="66"/>
+      <c r="J44" s="66"/>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="66"/>
+      <c r="B45" s="66"/>
+      <c r="C45" s="66"/>
+      <c r="D45" s="66"/>
+      <c r="E45" s="66"/>
+      <c r="F45" s="66"/>
+      <c r="G45" s="66"/>
+      <c r="H45" s="66"/>
+      <c r="I45" s="66"/>
+      <c r="J45" s="66"/>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="66"/>
+      <c r="B46" s="66"/>
+      <c r="C46" s="66"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="66"/>
+      <c r="G46" s="66"/>
+      <c r="H46" s="66"/>
+      <c r="I46" s="66"/>
+      <c r="J46" s="66"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="66"/>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
+      <c r="G47" s="66"/>
+      <c r="H47" s="66"/>
+      <c r="I47" s="66"/>
+      <c r="J47" s="66"/>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="66"/>
+      <c r="B48" s="66"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
+      <c r="G48" s="66"/>
+      <c r="H48" s="66"/>
+      <c r="I48" s="66"/>
+      <c r="J48" s="66"/>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="66"/>
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="66"/>
+      <c r="H49" s="66"/>
+      <c r="I49" s="66"/>
+      <c r="J49" s="66"/>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="66"/>
+      <c r="B50" s="66"/>
+      <c r="C50" s="66"/>
+      <c r="D50" s="66"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="66"/>
+      <c r="G50" s="66"/>
+      <c r="H50" s="66"/>
+      <c r="I50" s="66"/>
+      <c r="J50" s="66"/>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="66"/>
+      <c r="B51" s="66"/>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
+      <c r="G51" s="66"/>
+      <c r="H51" s="66"/>
+      <c r="I51" s="66"/>
+      <c r="J51" s="66"/>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="66"/>
+      <c r="B52" s="66"/>
+      <c r="C52" s="66"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="66"/>
+      <c r="G52" s="66"/>
+      <c r="H52" s="66"/>
+      <c r="I52" s="66"/>
+      <c r="J52" s="66"/>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="66"/>
+      <c r="B53" s="66"/>
+      <c r="C53" s="66"/>
+      <c r="D53" s="66"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="66"/>
+      <c r="G53" s="66"/>
+      <c r="H53" s="66"/>
+      <c r="I53" s="66"/>
+      <c r="J53" s="66"/>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="66"/>
+      <c r="B54" s="66"/>
+      <c r="C54" s="66"/>
+      <c r="D54" s="66"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="66"/>
+      <c r="G54" s="66"/>
+      <c r="H54" s="66"/>
+      <c r="I54" s="66"/>
+      <c r="J54" s="66"/>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="66"/>
+      <c r="B55" s="66"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="66"/>
+      <c r="E55" s="66"/>
+      <c r="F55" s="66"/>
+      <c r="G55" s="66"/>
+      <c r="H55" s="66"/>
+      <c r="I55" s="66"/>
+      <c r="J55" s="66"/>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="66"/>
+      <c r="B56" s="66"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="66"/>
+      <c r="F56" s="66"/>
+      <c r="G56" s="66"/>
+      <c r="H56" s="66"/>
+      <c r="I56" s="66"/>
+      <c r="J56" s="66"/>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="66"/>
+      <c r="B57" s="66"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="66"/>
+      <c r="F57" s="66"/>
+      <c r="G57" s="66"/>
+      <c r="H57" s="66"/>
+      <c r="I57" s="66"/>
+      <c r="J57" s="66"/>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="66"/>
+      <c r="B58" s="66"/>
+      <c r="C58" s="66"/>
+      <c r="D58" s="66"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="66"/>
+      <c r="G58" s="66"/>
+      <c r="H58" s="66"/>
+      <c r="I58" s="66"/>
+      <c r="J58" s="66"/>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="66"/>
+      <c r="B59" s="66"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="66"/>
+      <c r="G59" s="66"/>
+      <c r="H59" s="66"/>
+      <c r="I59" s="66"/>
+      <c r="J59" s="66"/>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="66"/>
+      <c r="B60" s="66"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="66"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="66"/>
+      <c r="G60" s="66"/>
+      <c r="H60" s="66"/>
+      <c r="I60" s="66"/>
+      <c r="J60" s="66"/>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="66"/>
+      <c r="B61" s="66"/>
+      <c r="C61" s="66"/>
+      <c r="D61" s="66"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="66"/>
+      <c r="G61" s="66"/>
+      <c r="H61" s="66"/>
+      <c r="I61" s="66"/>
+      <c r="J61" s="66"/>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="66"/>
+      <c r="B62" s="66"/>
+      <c r="C62" s="66"/>
+      <c r="D62" s="66"/>
+      <c r="E62" s="66"/>
+      <c r="F62" s="66"/>
+      <c r="G62" s="66"/>
+      <c r="H62" s="66"/>
+      <c r="I62" s="66"/>
+      <c r="J62" s="66"/>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="66"/>
+      <c r="B63" s="66"/>
+      <c r="C63" s="66"/>
+      <c r="D63" s="66"/>
+      <c r="E63" s="66"/>
+      <c r="F63" s="66"/>
+      <c r="G63" s="66"/>
+      <c r="H63" s="66"/>
+      <c r="I63" s="66"/>
+      <c r="J63" s="66"/>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="66"/>
+      <c r="B64" s="66"/>
+      <c r="C64" s="66"/>
+      <c r="D64" s="66"/>
+      <c r="E64" s="66"/>
+      <c r="F64" s="66"/>
+      <c r="G64" s="66"/>
+      <c r="H64" s="66"/>
+      <c r="I64" s="66"/>
+      <c r="J64" s="66"/>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="66"/>
+      <c r="B65" s="66"/>
+      <c r="C65" s="66"/>
+      <c r="D65" s="66"/>
+      <c r="E65" s="66"/>
+      <c r="F65" s="66"/>
+      <c r="G65" s="66"/>
+      <c r="H65" s="66"/>
+      <c r="I65" s="66"/>
+      <c r="J65" s="66"/>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="66"/>
+      <c r="B66" s="66"/>
+      <c r="C66" s="66"/>
+      <c r="D66" s="66"/>
+      <c r="E66" s="66"/>
+      <c r="F66" s="66"/>
+      <c r="G66" s="66"/>
+      <c r="H66" s="66"/>
+      <c r="I66" s="66"/>
+      <c r="J66" s="66"/>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="66"/>
+      <c r="B67" s="66"/>
+      <c r="C67" s="66"/>
+      <c r="D67" s="66"/>
+      <c r="E67" s="66"/>
+      <c r="F67" s="66"/>
+      <c r="G67" s="66"/>
+      <c r="H67" s="66"/>
+      <c r="I67" s="66"/>
+      <c r="J67" s="66"/>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="66"/>
+      <c r="B68" s="66"/>
+      <c r="C68" s="66"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="66"/>
+      <c r="F68" s="66"/>
+      <c r="G68" s="66"/>
+      <c r="H68" s="66"/>
+      <c r="I68" s="66"/>
+      <c r="J68" s="66"/>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="66"/>
+      <c r="B69" s="66"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="66"/>
+      <c r="F69" s="66"/>
+      <c r="G69" s="66"/>
+      <c r="H69" s="66"/>
+      <c r="I69" s="66"/>
+      <c r="J69" s="66"/>
+    </row>
+    <row r="70" spans="1:10">
+      <c r="A70" s="66"/>
+      <c r="B70" s="66"/>
+      <c r="C70" s="66"/>
+      <c r="D70" s="66"/>
+      <c r="E70" s="66"/>
+      <c r="F70" s="66"/>
+      <c r="G70" s="66"/>
+      <c r="H70" s="66"/>
+      <c r="I70" s="66"/>
+      <c r="J70" s="66"/>
+    </row>
+    <row r="71" spans="1:10">
+      <c r="A71" s="66"/>
+      <c r="B71" s="66"/>
+      <c r="C71" s="66"/>
+      <c r="D71" s="66"/>
+      <c r="E71" s="66"/>
+      <c r="F71" s="66"/>
+      <c r="G71" s="66"/>
+      <c r="H71" s="66"/>
+      <c r="I71" s="66"/>
+      <c r="J71" s="66"/>
+    </row>
+    <row r="72" spans="1:10">
+      <c r="A72" s="66"/>
+      <c r="B72" s="66"/>
+      <c r="C72" s="66"/>
+      <c r="D72" s="66"/>
+      <c r="E72" s="66"/>
+      <c r="F72" s="66"/>
+      <c r="G72" s="66"/>
+      <c r="H72" s="66"/>
+      <c r="I72" s="66"/>
+      <c r="J72" s="66"/>
+    </row>
+    <row r="73" spans="1:10">
+      <c r="A73" s="66"/>
+      <c r="B73" s="66"/>
+      <c r="C73" s="66"/>
+      <c r="D73" s="66"/>
+      <c r="E73" s="66"/>
+      <c r="F73" s="66"/>
+      <c r="G73" s="66"/>
+      <c r="H73" s="66"/>
+      <c r="I73" s="66"/>
+      <c r="J73" s="66"/>
+    </row>
+    <row r="74" spans="1:10">
+      <c r="A74" s="66"/>
+      <c r="B74" s="66"/>
+      <c r="C74" s="66"/>
+      <c r="D74" s="66"/>
+      <c r="E74" s="66"/>
+      <c r="F74" s="66"/>
+      <c r="G74" s="66"/>
+      <c r="H74" s="66"/>
+      <c r="I74" s="66"/>
+      <c r="J74" s="66"/>
+    </row>
+    <row r="75" spans="1:10">
+      <c r="A75" s="66"/>
+      <c r="B75" s="66"/>
+      <c r="C75" s="66"/>
+      <c r="D75" s="66"/>
+      <c r="E75" s="66"/>
+      <c r="F75" s="66"/>
+      <c r="G75" s="66"/>
+      <c r="H75" s="66"/>
+      <c r="I75" s="66"/>
+      <c r="J75" s="66"/>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="66"/>
+      <c r="B76" s="66"/>
+      <c r="C76" s="66"/>
+      <c r="D76" s="66"/>
+      <c r="E76" s="66"/>
+      <c r="F76" s="66"/>
+      <c r="G76" s="66"/>
+      <c r="H76" s="66"/>
+      <c r="I76" s="66"/>
+      <c r="J76" s="66"/>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="66"/>
+      <c r="B77" s="66"/>
+      <c r="C77" s="66"/>
+      <c r="D77" s="66"/>
+      <c r="E77" s="66"/>
+      <c r="F77" s="66"/>
+      <c r="G77" s="66"/>
+      <c r="H77" s="66"/>
+      <c r="I77" s="66"/>
+      <c r="J77" s="66"/>
+    </row>
+    <row r="78" spans="1:10">
+      <c r="A78" s="66"/>
+      <c r="B78" s="66"/>
+      <c r="C78" s="66"/>
+      <c r="D78" s="66"/>
+      <c r="E78" s="66"/>
+      <c r="F78" s="66"/>
+      <c r="G78" s="66"/>
+      <c r="H78" s="66"/>
+      <c r="I78" s="66"/>
+      <c r="J78" s="66"/>
+    </row>
+    <row r="79" spans="1:10">
+      <c r="A79" s="66"/>
+      <c r="B79" s="66"/>
+      <c r="C79" s="66"/>
+      <c r="D79" s="66"/>
+      <c r="E79" s="66"/>
+      <c r="F79" s="66"/>
+      <c r="G79" s="66"/>
+      <c r="H79" s="66"/>
+      <c r="I79" s="66"/>
+      <c r="J79" s="66"/>
+    </row>
+    <row r="80" spans="1:10">
+      <c r="A80" s="66"/>
+      <c r="B80" s="66"/>
+      <c r="C80" s="66"/>
+      <c r="D80" s="66"/>
+      <c r="E80" s="66"/>
+      <c r="F80" s="66"/>
+      <c r="G80" s="66"/>
+      <c r="H80" s="66"/>
+      <c r="I80" s="66"/>
+      <c r="J80" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4254,7 +4238,7 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>Database!$A$2:$A$56</xm:f>
@@ -4270,7 +4254,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV78"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="3" width="23.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="2"/>
@@ -4284,1344 +4268,1344 @@
     <col min="257" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:10" ht="20.25" thickBot="1">
+      <c r="A1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="16.5" thickTop="1">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="31" t="s">
         <v>116</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="I2" s="32">
-        <v>1</v>
-      </c>
-      <c r="J2" s="33">
+      <c r="I2" s="31">
+        <v>1</v>
+      </c>
+      <c r="J2" s="32">
         <v>101.96</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B3" s="2">
         <v>5</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="I3" s="32">
-        <v>1</v>
-      </c>
-      <c r="J3" s="33">
+      <c r="I3" s="31">
+        <v>1</v>
+      </c>
+      <c r="J3" s="32">
         <v>26.98</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
         <v>63</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="I4" s="32">
-        <v>1</v>
-      </c>
-      <c r="J4" s="33">
+      <c r="I4" s="31">
+        <v>1</v>
+      </c>
+      <c r="J4" s="32">
         <v>17.03</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="I5" s="32">
-        <v>1</v>
-      </c>
-      <c r="J5" s="33">
+      <c r="I5" s="31">
+        <v>1</v>
+      </c>
+      <c r="J5" s="32">
         <v>39.950000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
         <v>75</v>
       </c>
       <c r="B6" s="2">
         <v>10</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="31" t="s">
         <v>221</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="31" t="s">
         <v>222</v>
       </c>
-      <c r="I6" s="32">
-        <v>1</v>
-      </c>
-      <c r="J6" s="33">
+      <c r="I6" s="31">
+        <v>1</v>
+      </c>
+      <c r="J6" s="32">
         <v>39.950000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="2">
         <v>7.5</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="I7" s="32">
-        <v>1</v>
-      </c>
-      <c r="J7" s="33">
+      <c r="I7" s="31">
+        <v>1</v>
+      </c>
+      <c r="J7" s="32">
         <v>12.01</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B8" s="2">
         <v>0.1</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="I8" s="32">
-        <v>1</v>
-      </c>
-      <c r="J8" s="33">
+      <c r="I8" s="31">
+        <v>1</v>
+      </c>
+      <c r="J8" s="32">
         <v>44.01</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="A9"/>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="I9" s="32">
-        <v>1</v>
-      </c>
-      <c r="J9" s="33">
+      <c r="I9" s="31">
+        <v>1</v>
+      </c>
+      <c r="J9" s="32">
         <v>28.01</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:10" ht="18" thickBot="1">
+      <c r="A10" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="I10" s="32">
-        <v>1</v>
-      </c>
-      <c r="J10" s="33">
+      <c r="I10" s="31">
+        <v>1</v>
+      </c>
+      <c r="J10" s="32">
         <v>35.450000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="16.5" thickTop="1">
       <c r="A11" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <f>C11*1000</f>
         <v>1.0000000000000002E-6</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="11">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="I11" s="32">
-        <v>1</v>
-      </c>
-      <c r="J11" s="33">
+      <c r="I11" s="31">
+        <v>1</v>
+      </c>
+      <c r="J11" s="32">
         <v>238.03</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <f t="shared" ref="B12:B13" si="0">C12*1000</f>
         <v>1.784E-3</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>1.784E-6</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="I12" s="32">
-        <v>1</v>
-      </c>
-      <c r="J12" s="33">
+      <c r="I12" s="31">
+        <v>1</v>
+      </c>
+      <c r="J12" s="32">
         <v>2.0139999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <f t="shared" si="0"/>
         <v>0.9</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="I13" s="32">
-        <v>1</v>
-      </c>
-      <c r="J13" s="33">
+      <c r="I13" s="31">
+        <v>1</v>
+      </c>
+      <c r="J13" s="32">
         <v>60.08</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="10">
         <f t="shared" ref="B14" si="1">C14*1000</f>
         <v>2.46</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>2.4599999999999999E-3</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="I14" s="32">
-        <v>1</v>
-      </c>
-      <c r="J14" s="33">
+      <c r="I14" s="31">
+        <v>1</v>
+      </c>
+      <c r="J14" s="32">
         <v>238.03</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <f t="shared" ref="B15:B25" si="2">C15*1000</f>
         <v>10.97</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <v>1.0970000000000001E-2</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="H15" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="I15" s="32">
-        <v>1</v>
-      </c>
-      <c r="J15" s="33">
+      <c r="I15" s="31">
+        <v>1</v>
+      </c>
+      <c r="J15" s="32">
         <v>46.07</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="10">
         <f t="shared" si="2"/>
         <v>0.78900000000000003</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>7.8899999999999999E-4</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="31" t="s">
         <v>138</v>
       </c>
-      <c r="I16" s="32">
-        <v>1</v>
-      </c>
-      <c r="J16" s="33">
+      <c r="I16" s="31">
+        <v>1</v>
+      </c>
+      <c r="J16" s="32">
         <v>61.206800000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <f t="shared" si="2"/>
         <v>0.84175</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <v>8.4175000000000005E-4</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="31" t="s">
         <v>140</v>
       </c>
-      <c r="I17" s="32">
-        <v>1</v>
-      </c>
-      <c r="J17" s="33">
+      <c r="I17" s="31">
+        <v>1</v>
+      </c>
+      <c r="J17" s="32">
         <v>183.88</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="11">
+      <c r="B18" s="10">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>1E-3</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="31" t="s">
         <v>141</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="31" t="s">
         <v>142</v>
       </c>
-      <c r="I18" s="32">
-        <v>1</v>
-      </c>
-      <c r="J18" s="33">
+      <c r="I18" s="31">
+        <v>1</v>
+      </c>
+      <c r="J18" s="32">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <f t="shared" si="2"/>
         <v>0.216</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <v>2.1599999999999999E-4</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="H19" s="32" t="s">
+      <c r="H19" s="31" t="s">
         <v>143</v>
       </c>
-      <c r="I19" s="32">
-        <v>1</v>
-      </c>
-      <c r="J19" s="33">
+      <c r="I19" s="31">
+        <v>1</v>
+      </c>
+      <c r="J19" s="32">
         <f>5.03</f>
         <v>5.03</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="11">
+      <c r="B20" s="10">
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="31" t="s">
         <v>144</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="31" t="s">
         <v>145</v>
       </c>
-      <c r="I20" s="32">
-        <v>1</v>
-      </c>
-      <c r="J20" s="33">
+      <c r="I20" s="31">
+        <v>1</v>
+      </c>
+      <c r="J20" s="32">
         <v>92.09</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <f t="shared" si="2"/>
         <v>5.8</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="G21" s="32" t="s">
+      <c r="G21" s="31" t="s">
         <v>146</v>
       </c>
-      <c r="H21" s="32" t="s">
+      <c r="H21" s="31" t="s">
         <v>147</v>
       </c>
-      <c r="I21" s="32">
-        <v>1</v>
-      </c>
-      <c r="J21" s="33">
+      <c r="I21" s="31">
+        <v>1</v>
+      </c>
+      <c r="J21" s="32">
         <v>172.14</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="10">
         <f t="shared" si="2"/>
         <v>0.82</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <v>8.1999999999999998E-4</v>
       </c>
-      <c r="G22" s="32" t="s">
+      <c r="G22" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H22" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="I22" s="32">
-        <v>1</v>
-      </c>
-      <c r="J22" s="33">
+      <c r="I22" s="31">
+        <v>1</v>
+      </c>
+      <c r="J22" s="32">
         <v>3.016</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <f t="shared" si="2"/>
         <v>0.53399999999999992</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <v>5.3399999999999997E-4</v>
       </c>
-      <c r="G23" s="32" t="s">
+      <c r="G23" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="H23" s="32" t="s">
+      <c r="H23" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="I23" s="32">
-        <v>1</v>
-      </c>
-      <c r="J23" s="33">
+      <c r="I23" s="31">
+        <v>1</v>
+      </c>
+      <c r="J23" s="32">
         <v>4.0019999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="11">
+      <c r="B24" s="10">
         <f t="shared" si="2"/>
         <v>0.70209999999999995</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <v>7.0209999999999999E-4</v>
       </c>
-      <c r="G24" s="32" t="s">
+      <c r="G24" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="I24" s="32">
-        <v>1</v>
-      </c>
-      <c r="J24" s="33">
+      <c r="I24" s="31">
+        <v>1</v>
+      </c>
+      <c r="J24" s="32">
         <v>34.01</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <f t="shared" si="2"/>
         <v>0.79</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="G25" s="32" t="s">
+      <c r="G25" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="H25" s="32" t="s">
+      <c r="H25" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="I25" s="32">
-        <v>1</v>
-      </c>
-      <c r="J25" s="33">
+      <c r="I25" s="31">
+        <v>1</v>
+      </c>
+      <c r="J25" s="32">
         <v>168.69</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="11">
+      <c r="B26" s="10">
         <f t="shared" ref="B26:B40" si="3">C26*1000</f>
         <v>1.1732500000000001</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="11">
         <v>1.17325E-3</v>
       </c>
-      <c r="G26" s="32" t="s">
+      <c r="G26" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="H26" s="32" t="s">
+      <c r="H26" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="I26" s="32">
-        <v>1</v>
-      </c>
-      <c r="J26" s="33">
+      <c r="I26" s="31">
+        <v>1</v>
+      </c>
+      <c r="J26" s="32">
         <f>(14.007*2)+(1.008*4)</f>
         <v>32.045999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <f t="shared" si="3"/>
         <v>0.16239999999999999</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <v>1.6239999999999999E-4</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="G27" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="H27" s="32" t="s">
+      <c r="H27" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="I27" s="32">
-        <v>1</v>
-      </c>
-      <c r="J27" s="33">
+      <c r="I27" s="31">
+        <v>1</v>
+      </c>
+      <c r="J27" s="32">
         <v>2.02</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B28" s="11">
+      <c r="B28" s="10">
         <f t="shared" si="3"/>
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <v>5.8999999999999998E-5</v>
       </c>
-      <c r="G28" s="32" t="s">
+      <c r="G28" s="31" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="32" t="s">
+      <c r="H28" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="I28" s="32">
-        <v>1</v>
-      </c>
-      <c r="J28" s="33">
+      <c r="I28" s="31">
+        <v>1</v>
+      </c>
+      <c r="J28" s="32">
         <v>170.34</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="10">
         <f t="shared" si="3"/>
         <v>7.0849999999999996E-2</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <v>7.0850000000000001E-5</v>
       </c>
-      <c r="G29" s="32" t="s">
+      <c r="G29" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="H29" s="32" t="s">
+      <c r="H29" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="I29" s="32">
-        <v>1</v>
-      </c>
-      <c r="J29" s="33">
+      <c r="I29" s="31">
+        <v>1</v>
+      </c>
+      <c r="J29" s="32">
         <v>6.94</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="11">
+      <c r="B30" s="10">
         <f t="shared" si="3"/>
         <v>0.42560999999999999</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="11">
         <v>4.2560999999999999E-4</v>
       </c>
-      <c r="G30" s="32" t="s">
+      <c r="G30" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="H30" s="32" t="s">
+      <c r="H30" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="I30" s="32">
-        <v>1</v>
-      </c>
-      <c r="J30" s="33">
+      <c r="I30" s="31">
+        <v>1</v>
+      </c>
+      <c r="J30" s="32">
         <v>17.03</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="10">
         <f t="shared" si="3"/>
         <v>1.141</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <v>1.1410000000000001E-3</v>
       </c>
-      <c r="G31" s="32" t="s">
+      <c r="G31" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="H31" s="32" t="s">
+      <c r="H31" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="I31" s="32">
-        <v>1</v>
-      </c>
-      <c r="J31" s="33">
+      <c r="I31" s="31">
+        <v>1</v>
+      </c>
+      <c r="J31" s="32">
         <v>28.01</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B32" s="11">
+      <c r="B32" s="10">
         <f t="shared" si="3"/>
         <v>0.82490700000000006</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <v>8.2490700000000005E-4</v>
       </c>
-      <c r="G32" s="32" t="s">
+      <c r="G32" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="H32" s="32" t="s">
+      <c r="H32" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="I32" s="32">
-        <v>1</v>
-      </c>
-      <c r="J32" s="33">
+      <c r="I32" s="31">
+        <v>1</v>
+      </c>
+      <c r="J32" s="32">
         <v>44.01</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="10">
         <f t="shared" si="3"/>
         <v>7.8</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="G33" s="32" t="s">
+      <c r="G33" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="H33" s="32" t="s">
+      <c r="H33" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="I33" s="32">
-        <v>1</v>
-      </c>
-      <c r="J33" s="33">
+      <c r="I33" s="31">
+        <v>1</v>
+      </c>
+      <c r="J33" s="32">
         <v>2.0139999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B34" s="11">
+      <c r="B34" s="10">
         <f t="shared" si="3"/>
         <v>7.085</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="11">
         <v>7.0850000000000002E-3</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="H34" s="32" t="s">
+      <c r="H34" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="I34" s="32">
-        <v>1</v>
-      </c>
-      <c r="J34" s="33">
+      <c r="I34" s="31">
+        <v>1</v>
+      </c>
+      <c r="J34" s="32">
         <v>3.016</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="10">
         <f t="shared" si="3"/>
         <v>0.88</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="11">
         <v>8.8000000000000003E-4</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="H35" s="32" t="s">
+      <c r="H35" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="I35" s="32">
-        <v>1</v>
-      </c>
-      <c r="J35" s="33">
+      <c r="I35" s="31">
+        <v>1</v>
+      </c>
+      <c r="J35" s="32">
         <v>4.0019999999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B36" s="11">
+      <c r="B36" s="10">
         <f t="shared" si="3"/>
         <v>1.45</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="11">
         <v>1.4499999999999999E-3</v>
       </c>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="H36" s="32" t="s">
+      <c r="H36" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="I36" s="32">
-        <v>1</v>
-      </c>
-      <c r="J36" s="33">
+      <c r="I36" s="31">
+        <v>1</v>
+      </c>
+      <c r="J36" s="32">
         <v>2.02</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="10">
         <f t="shared" si="3"/>
         <v>1.05</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="11">
         <v>1.0499999999999999E-3</v>
       </c>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="H37" s="32" t="s">
+      <c r="H37" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="I37" s="32">
-        <v>1</v>
-      </c>
-      <c r="J37" s="33">
+      <c r="I37" s="31">
+        <v>1</v>
+      </c>
+      <c r="J37" s="32">
         <v>16.05</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10">
       <c r="A38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B38" s="11">
+      <c r="B38" s="10">
         <f t="shared" si="3"/>
         <v>0.79100000000000004</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="11">
         <v>7.9100000000000004E-4</v>
       </c>
-      <c r="G38" s="32" t="s">
+      <c r="G38" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="H38" s="34" t="s">
+      <c r="H38" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="I38" s="34">
-        <v>1</v>
-      </c>
-      <c r="J38" s="33">
+      <c r="I38" s="33">
+        <v>1</v>
+      </c>
+      <c r="J38" s="32">
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10">
       <c r="A39" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="10">
         <f t="shared" si="3"/>
         <v>0.82899999999999996</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="11">
         <v>8.2899999999999998E-4</v>
       </c>
-      <c r="G39" s="32" t="s">
+      <c r="G39" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="H39" s="32" t="s">
+      <c r="H39" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="I39" s="32">
-        <v>1</v>
-      </c>
-      <c r="J39" s="33">
+      <c r="I39" s="31">
+        <v>1</v>
+      </c>
+      <c r="J39" s="32">
         <v>28.01</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B40" s="11">
+      <c r="B40" s="10">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="11">
         <v>1E-3</v>
       </c>
-      <c r="G40" s="32" t="s">
+      <c r="G40" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="H40" s="32" t="s">
+      <c r="H40" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="I40" s="32">
-        <v>1</v>
-      </c>
-      <c r="J40" s="33">
+      <c r="I40" s="31">
+        <v>1</v>
+      </c>
+      <c r="J40" s="32">
         <f>J36</f>
         <v>2.02</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G41" s="32" t="s">
+    <row r="41" spans="1:10">
+      <c r="G41" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="H41" s="32" t="s">
+      <c r="H41" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="I41" s="32">
-        <v>1</v>
-      </c>
-      <c r="J41" s="33">
+      <c r="I41" s="31">
+        <v>1</v>
+      </c>
+      <c r="J41" s="32">
         <v>159.69</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="7" t="s">
+    <row r="42" spans="1:10" ht="18" thickBot="1">
+      <c r="A42" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B42"/>
-      <c r="C42" s="13"/>
-      <c r="G42" s="32" t="s">
+      <c r="C42" s="12"/>
+      <c r="G42" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="H42" s="32" t="s">
+      <c r="H42" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="I42" s="32">
-        <v>1</v>
-      </c>
-      <c r="J42" s="33">
+      <c r="I42" s="31">
+        <v>1</v>
+      </c>
+      <c r="J42" s="32">
         <f>55.845*2</f>
         <v>111.69</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" ht="16.5" thickTop="1">
       <c r="A43" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <f t="shared" ref="B43:B56" si="4">C43*1000</f>
         <v>5</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G43" s="32" t="s">
+      <c r="G43" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="H43" s="32" t="s">
+      <c r="H43" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="I43" s="32">
-        <v>1</v>
-      </c>
-      <c r="J43" s="33">
+      <c r="I43" s="31">
+        <v>1</v>
+      </c>
+      <c r="J43" s="32">
         <f>55.845*2</f>
         <v>111.69</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10">
       <c r="A44" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="11">
+      <c r="B44" s="10">
         <f t="shared" si="4"/>
         <v>54.4</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="11">
         <v>5.4399999999999997E-2</v>
       </c>
-      <c r="G44" s="32" t="s">
+      <c r="G44" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="H44" s="32" t="s">
+      <c r="H44" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="I44" s="32">
-        <v>1</v>
-      </c>
-      <c r="J44" s="33">
+      <c r="I44" s="31">
+        <v>1</v>
+      </c>
+      <c r="J44" s="32">
         <f>12.02+4*1.008</f>
         <v>16.052</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10">
       <c r="A45" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="10">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G45" s="32" t="s">
+      <c r="G45" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="H45" s="32" t="s">
+      <c r="H45" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="I45" s="32">
-        <v>1</v>
-      </c>
-      <c r="J45" s="33">
+      <c r="I45" s="31">
+        <v>1</v>
+      </c>
+      <c r="J45" s="32">
         <f>(28.086*2)+(16*2)</f>
         <v>88.171999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="18.75">
       <c r="A46" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B46" s="11">
+      <c r="B46" s="10">
         <f t="shared" si="4"/>
         <v>6.0000000000000005E-2</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="11">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="G46" s="32" t="s">
+      <c r="G46" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="H46" s="32" t="s">
+      <c r="H46" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="I46" s="32">
-        <v>1</v>
-      </c>
-      <c r="J46" s="33">
+      <c r="I46" s="31">
+        <v>1</v>
+      </c>
+      <c r="J46" s="32">
         <v>46.07</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10">
       <c r="A47" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <f t="shared" si="4"/>
         <v>5.0108799999999993</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="11">
         <v>5.0108799999999997E-3</v>
       </c>
-      <c r="G47" s="32" t="s">
+      <c r="G47" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="H47" s="32" t="s">
+      <c r="H47" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="I47" s="32">
-        <v>1</v>
-      </c>
-      <c r="J47" s="33">
+      <c r="I47" s="31">
+        <v>1</v>
+      </c>
+      <c r="J47" s="32">
         <v>233.88</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B48" s="11">
+      <c r="B48" s="10">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G48" s="32" t="s">
+      <c r="G48" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="H48" s="32" t="s">
+      <c r="H48" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="I48" s="32">
-        <v>1</v>
-      </c>
-      <c r="J48" s="33">
+      <c r="I48" s="31">
+        <v>1</v>
+      </c>
+      <c r="J48" s="32">
         <f>14.007*2</f>
         <v>28.013999999999999</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <f t="shared" si="4"/>
         <v>8.6</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="11">
         <v>8.6E-3</v>
       </c>
-      <c r="G49" s="32" t="s">
+      <c r="G49" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="H49" s="32" t="s">
+      <c r="H49" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="I49" s="32">
-        <v>1</v>
-      </c>
-      <c r="J49" s="33">
+      <c r="I49" s="31">
+        <v>1</v>
+      </c>
+      <c r="J49" s="32">
         <v>92.04</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B50" s="11">
+      <c r="B50" s="10">
         <f t="shared" si="4"/>
         <v>5.7050000000000001</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="11">
         <v>5.705E-3</v>
       </c>
-      <c r="G50" s="32" t="s">
+      <c r="G50" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="H50" s="32" t="s">
+      <c r="H50" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="I50" s="32">
-        <v>1</v>
-      </c>
-      <c r="J50" s="33">
+      <c r="I50" s="31">
+        <v>1</v>
+      </c>
+      <c r="J50" s="32">
         <v>32</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="10">
         <f t="shared" si="4"/>
         <v>0.35399999999999998</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="11">
         <v>3.5399999999999999E-4</v>
       </c>
-      <c r="G51" s="32" t="s">
+      <c r="G51" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="H51" s="32" t="s">
+      <c r="H51" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="I51" s="32">
-        <v>1</v>
-      </c>
-      <c r="J51" s="33">
+      <c r="I51" s="31">
+        <v>1</v>
+      </c>
+      <c r="J51" s="32">
         <v>30.97</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B52" s="11">
+      <c r="B52" s="10">
         <f t="shared" si="4"/>
         <v>2.12805</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="11">
         <v>2.1280499999999998E-3</v>
       </c>
-      <c r="G52" s="32" t="s">
+      <c r="G52" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="H52" s="32" t="s">
+      <c r="H52" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="I52" s="32">
-        <v>1</v>
-      </c>
-      <c r="J52" s="33">
+      <c r="I52" s="31">
+        <v>1</v>
+      </c>
+      <c r="J52" s="32">
         <f>195.078</f>
         <v>195.078</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="10">
         <f t="shared" si="4"/>
         <v>4.1000000000000005</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="11">
         <v>4.1000000000000003E-3</v>
       </c>
-      <c r="G53" s="32" t="s">
+      <c r="G53" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="H53" s="32" t="s">
+      <c r="H53" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="I53" s="32">
-        <v>1</v>
-      </c>
-      <c r="J53" s="33">
+      <c r="I53" s="31">
+        <v>1</v>
+      </c>
+      <c r="J53" s="32">
         <v>76.08</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B54" s="11">
+      <c r="B54" s="10">
         <f t="shared" si="4"/>
         <v>12.5</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="11">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="G54" s="32" t="s">
+      <c r="G54" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="H54" s="32" t="s">
+      <c r="H54" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="I54" s="32">
-        <v>1</v>
-      </c>
-      <c r="J54" s="33">
+      <c r="I54" s="31">
+        <v>1</v>
+      </c>
+      <c r="J54" s="32">
         <v>28.09</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="10">
         <f t="shared" si="4"/>
         <v>7.5</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="11">
         <v>7.4999999999999997E-3</v>
       </c>
-      <c r="G55" s="32" t="s">
+      <c r="G55" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="H55" s="32" t="s">
+      <c r="H55" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="I55" s="32">
-        <v>1</v>
-      </c>
-      <c r="J55" s="33">
+      <c r="I55" s="31">
+        <v>1</v>
+      </c>
+      <c r="J55" s="32">
         <v>186.09</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10">
       <c r="A56" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B56" s="11">
+      <c r="B56" s="10">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G56" s="32" t="s">
+      <c r="G56" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="H56" s="32" t="s">
+      <c r="H56" s="31" t="s">
         <v>188</v>
       </c>
-      <c r="I56" s="32">
-        <v>1</v>
-      </c>
-      <c r="J56" s="33">
+      <c r="I56" s="31">
+        <v>1</v>
+      </c>
+      <c r="J56" s="32">
         <v>270.02999999999997</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G57" s="32" t="s">
+    <row r="57" spans="1:10">
+      <c r="G57" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="H57" s="32" t="s">
+      <c r="H57" s="31" t="s">
         <v>189</v>
       </c>
-      <c r="I57" s="32">
-        <v>1</v>
-      </c>
-      <c r="J57" s="33">
+      <c r="I57" s="31">
+        <v>1</v>
+      </c>
+      <c r="J57" s="32">
         <v>60.1</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G58" s="32" t="s">
+    <row r="58" spans="1:10">
+      <c r="G58" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="H58" s="32" t="s">
+      <c r="H58" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="I58" s="32">
-        <v>1</v>
-      </c>
-      <c r="J58" s="33">
+      <c r="I58" s="31">
+        <v>1</v>
+      </c>
+      <c r="J58" s="32">
         <f>SUM(($D$38*0.25)+($D$82*0.75))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G59" s="32" t="s">
+    <row r="59" spans="1:10">
+      <c r="G59" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="H59" s="32" t="s">
+      <c r="H59" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="I59" s="32">
-        <v>1</v>
-      </c>
-      <c r="J59" s="33">
+      <c r="I59" s="31">
+        <v>1</v>
+      </c>
+      <c r="J59" s="32">
         <v>18.02</v>
       </c>
     </row>
-    <row r="78" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="32"/>
-      <c r="J78" s="33"/>
+    <row r="78" spans="7:10">
+      <c r="G78" s="31"/>
+      <c r="H78" s="31"/>
+      <c r="I78" s="31"/>
+      <c r="J78" s="32"/>
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
@@ -5641,7 +5625,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:IV16"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="12.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="13.85546875" style="2" customWidth="1"/>
@@ -5654,18 +5638,18 @@
     <col min="257" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="84" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-      <c r="F1" s="85"/>
-      <c r="G1" s="85"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="E1" s="84"/>
+      <c r="F1" s="84"/>
+      <c r="G1" s="84"/>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -5688,7 +5672,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -5715,7 +5699,7 @@
         <v>4043923.419697999</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -5742,7 +5726,7 @@
         <v>4923873.4622719996</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -5769,7 +5753,7 @@
         <v>5558591.5257679988</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
@@ -5796,7 +5780,7 @@
         <v>4771204.5341204992</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
@@ -5823,7 +5807,7 @@
         <v>4043923.419697999</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
@@ -5850,7 +5834,7 @@
         <v>5723281.6293645008</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
@@ -5880,7 +5864,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -5907,7 +5891,7 @@
         <v>4620939.8410579991</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
         <v>16</v>
       </c>
@@ -5934,7 +5918,7 @@
         <v>4923873.4622719996</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
         <v>17</v>
       </c>
@@ -5961,7 +5945,7 @@
         <v>4620939.841058</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
         <v>18</v>
       </c>
@@ -5988,7 +5972,7 @@
         <v>4473079.3830845002</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
         <v>19</v>
       </c>
@@ -6015,7 +5999,7 @@
         <v>5890375.9680500003</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
@@ -6042,7 +6026,7 @@
         <v>4771204.5341204992</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -6085,7 +6069,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J86"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="22" style="5" customWidth="1"/>
     <col min="2" max="3" width="20" style="5" customWidth="1"/>
@@ -6097,21 +6081,21 @@
     <col min="11" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="86" t="s">
+    <row r="1" spans="1:10" ht="20.25" thickBot="1">
+      <c r="A1" s="85" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="49" t="s">
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+    </row>
+    <row r="2" spans="1:10" ht="18.75" thickTop="1" thickBot="1">
+      <c r="A2" s="48" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="16.5" thickTop="1">
       <c r="B3" s="2" t="s">
         <v>214</v>
       </c>
@@ -6122,19 +6106,19 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4"/>
-      <c r="B4" s="23">
+      <c r="B4" s="22">
         <v>203946</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="25">
         <v>2300</v>
       </c>
-      <c r="G4" s="51">
+      <c r="G4" s="50">
         <v>299792458</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="A5"/>
       <c r="B5" s="2" t="s">
         <v>3</v>
@@ -6149,21 +6133,21 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="A6" s="2"/>
-      <c r="B6" s="20">
+      <c r="B6" s="19">
         <f>B4*G7</f>
         <v>2000027.0408999999</v>
       </c>
-      <c r="C6" s="61">
+      <c r="C6" s="60">
         <f>IFERROR(C4*1000/B6,0)</f>
         <v>1.1499844516927202</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="19">
         <f>C4*1000*B6</f>
         <v>4600062194070</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="19">
         <f>IFERROR(D6/C6,0)</f>
         <v>4000108164331.21</v>
       </c>
@@ -6171,32 +6155,32 @@
         <v>207</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10">
       <c r="B7" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="49">
         <v>9.8066499999999994</v>
       </c>
       <c r="J7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="30">
+    <row r="8" spans="1:10">
+      <c r="B8" s="29">
         <f>B6/G4</f>
         <v>6.671372102696459E-3</v>
       </c>
       <c r="J8"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10">
       <c r="J9"/>
     </row>
-    <row r="10" spans="1:10" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="49" t="s">
+    <row r="10" spans="1:10" ht="18" thickBot="1">
+      <c r="A10" s="48" t="s">
         <v>99</v>
       </c>
       <c r="J10"/>
     </row>
-    <row r="11" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="16.5" thickTop="1">
       <c r="B11" s="2" t="s">
         <v>214</v>
       </c>
@@ -6204,16 +6188,16 @@
         <v>96</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="24">
+    <row r="12" spans="1:10">
+      <c r="B12" s="23">
         <v>960</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="24">
         <f>(C14*B14)/1000</f>
         <v>0.29543542033151998</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10">
       <c r="B13" s="2" t="s">
         <v>3</v>
       </c>
@@ -6228,25 +6212,25 @@
       </c>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="20">
+    <row r="14" spans="1:10">
+      <c r="B14" s="19">
         <f>B12*G7</f>
         <v>9414.384</v>
       </c>
-      <c r="C14" s="61">
+      <c r="C14" s="60">
         <f>E14/D14</f>
         <v>3.1381279999999998E-2</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <v>2824315200</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="19">
         <f>IFERROR((B14^2),0)</f>
         <v>88630626.099455997</v>
       </c>
       <c r="G14"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10">
       <c r="A15"/>
       <c r="B15"/>
       <c r="C15"/>
@@ -6254,14 +6238,14 @@
       <c r="E15"/>
       <c r="G15"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B16" s="64" t="s">
+    <row r="16" spans="1:10">
+      <c r="B16" s="63" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="64"/>
+      <c r="C16" s="63"/>
       <c r="G16"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="B17" s="5" t="s">
         <v>212</v>
       </c>
@@ -6273,30 +6257,30 @@
       </c>
       <c r="G17"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="22">
-        <v>1</v>
-      </c>
-      <c r="C18" s="22">
+    <row r="18" spans="1:8">
+      <c r="B18" s="21">
+        <v>1</v>
+      </c>
+      <c r="C18" s="21">
         <v>0</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="20">
         <f>C12/(B18*G7)</f>
         <v>3.0126028799999999E-2</v>
       </c>
       <c r="G18"/>
       <c r="H18"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="G19"/>
       <c r="H19"/>
     </row>
-    <row r="21" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="49" t="s">
+    <row r="21" spans="1:8" ht="18" thickBot="1">
+      <c r="A21" s="48" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="16.5" thickTop="1">
       <c r="B22" s="5" t="s">
         <v>33</v>
       </c>
@@ -6307,25 +6291,25 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="29">
+    <row r="23" spans="1:8">
+      <c r="B23" s="28">
         <v>1000000000</v>
       </c>
-      <c r="C23" s="55">
+      <c r="C23" s="54">
         <f>(B23/G4/1000)</f>
         <v>3.3356409519815205E-3</v>
       </c>
-      <c r="D23" s="52">
+      <c r="D23" s="51">
         <f>B23/1000</f>
         <v>1000000</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="49" t="s">
+    <row r="26" spans="1:8" ht="18" thickBot="1">
+      <c r="A26" s="48" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="16.5" thickTop="1">
       <c r="B27" s="5" t="s">
         <v>214</v>
       </c>
@@ -6333,16 +6317,16 @@
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="28">
+    <row r="28" spans="1:8">
+      <c r="B28" s="27">
         <f>B30/G7</f>
         <v>749335.32127174258</v>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="21">
         <v>3800</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="B29" s="5" t="s">
         <v>3</v>
       </c>
@@ -6356,192 +6340,192 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="28">
+    <row r="30" spans="1:8">
+      <c r="B30" s="27">
         <f>(2*E30)^0.5</f>
         <v>7348469.2283495339</v>
       </c>
-      <c r="C30" s="61">
+      <c r="C30" s="60">
         <f>IFERROR(C28*1000/B30,0)</f>
         <v>0.51711450125422653</v>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="27">
         <f>C28*1000*B30</f>
         <v>27924183067728.23</v>
       </c>
-      <c r="E30" s="27">
+      <c r="E30" s="26">
         <v>27000000000000</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8">
       <c r="B31" s="5" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="30">
+    <row r="32" spans="1:8">
+      <c r="B32" s="29">
         <f>B30/G4</f>
         <v>2.4511854892458749E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="49" t="s">
+    <row r="35" spans="1:9" ht="18" thickBot="1">
+      <c r="A35" s="48" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="57"/>
+    <row r="36" spans="1:9" ht="16.5" thickTop="1">
+      <c r="A36" s="56"/>
       <c r="G36"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="39" t="s">
+    <row r="37" spans="1:9">
+      <c r="B37" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C37" s="35">
+      <c r="C37" s="34">
         <v>2130</v>
       </c>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
       <c r="F37"/>
       <c r="G37"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="39" t="s">
+    <row r="38" spans="1:9">
+      <c r="B38" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="35">
         <v>8.3144621000000001</v>
       </c>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
       <c r="F38"/>
     </row>
-    <row r="39" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="39" t="s">
+    <row r="39" spans="1:9" ht="16.5" thickBot="1">
+      <c r="B39" s="38" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="14" t="s">
+      <c r="C39" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D39" s="40">
+      <c r="D39" s="39">
         <f>IFERROR(VLOOKUP(C39,Database!$G$2:$J$59,4,FALSE),"-")</f>
         <v>2.02</v>
       </c>
-      <c r="E39" s="41">
+      <c r="E39" s="40">
         <f>D39/1000</f>
         <v>2.0200000000000001E-3</v>
       </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="1:9" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="39"/>
-      <c r="C40" s="14" t="s">
+    <row r="40" spans="1:9" ht="17.25" thickTop="1" thickBot="1">
+      <c r="B40" s="38"/>
+      <c r="C40" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D40" s="40">
+      <c r="D40" s="39">
         <f>IFERROR(VLOOKUP(C40,Database!$G$2:$J$59,4,FALSE),"-")</f>
         <v>18.02</v>
       </c>
-      <c r="E40" s="41">
+      <c r="E40" s="40">
         <f>D40/1000</f>
         <v>1.8020000000000001E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="39" t="s">
+    <row r="41" spans="1:9" ht="16.5" thickTop="1">
+      <c r="B41" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1.3979999999999999</v>
       </c>
       <c r="D41"/>
-      <c r="E41" s="31"/>
-    </row>
-    <row r="42" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="39" t="s">
+      <c r="E41" s="30"/>
+    </row>
+    <row r="42" spans="1:9" ht="16.5" thickBot="1">
+      <c r="B42" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="C42" s="37">
+      <c r="C42" s="36">
         <v>0</v>
       </c>
-      <c r="D42" s="56">
+      <c r="D42" s="55">
         <f>IFERROR(C42*101320,101.32)</f>
         <v>0</v>
       </c>
-      <c r="E42" s="31"/>
-    </row>
-    <row r="43" spans="1:9" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="39" t="s">
+      <c r="E42" s="30"/>
+    </row>
+    <row r="43" spans="1:9" ht="17.25" thickTop="1" thickBot="1">
+      <c r="B43" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C43" s="37">
+      <c r="C43" s="36">
         <v>500</v>
       </c>
-      <c r="D43" s="56">
+      <c r="D43" s="55">
         <f>C43*101320</f>
         <v>50660000</v>
       </c>
-      <c r="E43" s="31"/>
-    </row>
-    <row r="44" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="39"/>
-      <c r="C44" s="31"/>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B45" s="39" t="s">
+      <c r="E43" s="30"/>
+    </row>
+    <row r="44" spans="1:9" ht="16.5" thickTop="1">
+      <c r="B44" s="38"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="C45" s="38">
+      <c r="C45" s="37">
         <f>(C37*C38)/E39</f>
         <v>8767229.8381188121</v>
       </c>
-      <c r="D45" s="31"/>
-      <c r="E45" s="38">
+      <c r="D45" s="30"/>
+      <c r="E45" s="37">
         <f>(C37*C38)/E40</f>
         <v>982786.03068812436</v>
       </c>
-      <c r="H45" s="42"/>
-      <c r="I45" s="42"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B46" s="39" t="s">
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="B46" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="C46" s="38">
+      <c r="C46" s="37">
         <f>(2*C41)/(C41-1)</f>
         <v>7.0251256281407048</v>
       </c>
-      <c r="D46" s="31"/>
+      <c r="D46" s="30"/>
       <c r="E46"/>
-      <c r="H46" s="42"/>
-      <c r="I46" s="42"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B47" s="39" t="s">
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="B47" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="C47" s="38">
+      <c r="C47" s="37">
         <f>(C41-1)/C41</f>
         <v>0.284692417739628</v>
       </c>
-      <c r="D47" s="31"/>
+      <c r="D47" s="30"/>
       <c r="E47"/>
     </row>
-    <row r="48" spans="1:9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" customFormat="1">
       <c r="A48" s="5"/>
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="C48" s="38">
+      <c r="C48" s="37">
         <f>1-((D42/D43)^C47)</f>
         <v>1</v>
       </c>
-      <c r="D48" s="31"/>
+      <c r="D48" s="30"/>
       <c r="F48" s="5"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49"/>
@@ -6549,61 +6533,61 @@
       <c r="E49"/>
       <c r="F49"/>
     </row>
-    <row r="50" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="39"/>
-      <c r="C50" s="18" t="str">
+    <row r="50" spans="1:7" ht="16.5" thickBot="1">
+      <c r="B50" s="38"/>
+      <c r="C50" s="17" t="str">
         <f>C39</f>
         <v>LqdHydrogen</v>
       </c>
-      <c r="D50" s="31"/>
-      <c r="E50" s="18" t="str">
+      <c r="D50" s="30"/>
+      <c r="E50" s="17" t="str">
         <f>C40</f>
         <v>Water (CRP)</v>
       </c>
-      <c r="G50" s="43"/>
-    </row>
-    <row r="51" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="39" t="s">
+      <c r="G50" s="42"/>
+    </row>
+    <row r="51" spans="1:7" ht="16.5" thickTop="1">
+      <c r="B51" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="53">
+      <c r="C51" s="52">
         <f>(C45*C46*C48)^0.5</f>
         <v>7847.9864311534302</v>
       </c>
-      <c r="D51" s="31"/>
-      <c r="E51" s="53">
+      <c r="D51" s="30"/>
+      <c r="E51" s="52">
         <f>(E45*C46*C48)^0.5</f>
         <v>2627.5835536031618</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B52" s="39" t="s">
+    <row r="52" spans="1:7">
+      <c r="B52" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="C52" s="53">
+      <c r="C52" s="52">
         <f>C51/9.80655</f>
         <v>800.28006089332439</v>
       </c>
-      <c r="D52" s="31"/>
-      <c r="E52" s="53">
+      <c r="D52" s="30"/>
+      <c r="E52" s="52">
         <f>E51/9.80655</f>
         <v>267.94168730115706</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E54" s="42"/>
-    </row>
-    <row r="55" spans="1:7" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="49" t="s">
+    <row r="53" spans="1:7">
+      <c r="E53" s="41"/>
+      <c r="F53" s="41"/>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="E54" s="41"/>
+    </row>
+    <row r="55" spans="1:7" ht="18" thickBot="1">
+      <c r="A55" s="48" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="16.5" thickTop="1"/>
+    <row r="57" spans="1:7">
       <c r="C57" s="5" t="s">
         <v>195</v>
       </c>
@@ -6614,15 +6598,15 @@
         <v>201</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D58" s="47">
+    <row r="58" spans="1:7">
+      <c r="D58" s="46">
         <v>60</v>
       </c>
-      <c r="E58" s="58">
+      <c r="E58" s="57">
         <v>0.75</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7">
       <c r="B60" s="5" t="s">
         <v>211</v>
       </c>
@@ -6630,270 +6614,270 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="45" t="s">
+    <row r="61" spans="1:7" ht="16.5" thickBot="1">
+      <c r="B61" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="C61" s="60">
+      <c r="C61" s="59">
         <v>800</v>
       </c>
-      <c r="D61" s="59">
+      <c r="D61" s="58">
         <f>D58</f>
         <v>60</v>
       </c>
-      <c r="E61" s="48">
+      <c r="E61" s="47">
         <f t="shared" ref="E61:E67" si="0">($C$61/C61)^$E$58</f>
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="45" t="s">
+    <row r="62" spans="1:7" ht="16.5" thickTop="1">
+      <c r="B62" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="C62" s="60">
+      <c r="C62" s="59">
         <v>606</v>
       </c>
-      <c r="D62" s="54">
+      <c r="D62" s="53">
         <f t="shared" ref="D62:D67" si="1">$D$58*(($C$61/C62)^$E$58)</f>
         <v>73.894867118770051</v>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="47">
         <f t="shared" si="0"/>
         <v>1.2315811186461676</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B63" s="45" t="s">
+    <row r="63" spans="1:7">
+      <c r="B63" s="44" t="s">
         <v>121</v>
       </c>
-      <c r="C63" s="60">
+      <c r="C63" s="59">
         <v>400</v>
       </c>
-      <c r="D63" s="54">
+      <c r="D63" s="53">
         <f t="shared" si="1"/>
         <v>100.90756983044574</v>
       </c>
-      <c r="E63" s="48">
+      <c r="E63" s="47">
         <f t="shared" si="0"/>
         <v>1.681792830507429</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B64" s="45" t="s">
+    <row r="64" spans="1:7">
+      <c r="B64" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="C64" s="60">
+      <c r="C64" s="59">
         <v>253</v>
       </c>
-      <c r="D64" s="54">
+      <c r="D64" s="53">
         <f t="shared" si="1"/>
         <v>142.27491989040757</v>
       </c>
-      <c r="E64" s="48">
+      <c r="E64" s="47">
         <f t="shared" si="0"/>
         <v>2.3712486648401261</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B65" s="44" t="s">
+    <row r="65" spans="2:5">
+      <c r="B65" s="43" t="s">
         <v>191</v>
       </c>
-      <c r="C65" s="60">
+      <c r="C65" s="59">
         <v>370</v>
       </c>
-      <c r="D65" s="54">
+      <c r="D65" s="53">
         <f t="shared" si="1"/>
         <v>106.98365906113423</v>
       </c>
-      <c r="E65" s="48">
+      <c r="E65" s="47">
         <f t="shared" si="0"/>
         <v>1.7830609843522371</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B66" s="44" t="s">
+    <row r="66" spans="2:5">
+      <c r="B66" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="C66" s="60">
+      <c r="C66" s="59">
         <v>283</v>
       </c>
-      <c r="D66" s="54">
+      <c r="D66" s="53">
         <f t="shared" si="1"/>
         <v>130.80637609525397</v>
       </c>
-      <c r="E66" s="48">
+      <c r="E66" s="47">
         <f t="shared" si="0"/>
         <v>2.1801062682542329</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B67" s="44" t="s">
+    <row r="67" spans="2:5">
+      <c r="B67" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="C67" s="60">
+      <c r="C67" s="59">
         <v>253</v>
       </c>
-      <c r="D67" s="54">
+      <c r="D67" s="53">
         <f t="shared" si="1"/>
         <v>142.27491989040757</v>
       </c>
-      <c r="E67" s="48">
+      <c r="E67" s="47">
         <f t="shared" si="0"/>
         <v>2.3712486648401261</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="C68" s="60"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="46"/>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:5">
+      <c r="C68" s="59"/>
+      <c r="D68" s="41"/>
+      <c r="E68" s="45"/>
+    </row>
+    <row r="69" spans="2:5">
       <c r="B69" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C69" s="60"/>
-      <c r="D69" s="42"/>
-      <c r="E69" s="46"/>
-    </row>
-    <row r="70" spans="2:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="45" t="s">
+      <c r="C69" s="59"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="45"/>
+    </row>
+    <row r="70" spans="2:5" ht="16.5" thickBot="1">
+      <c r="B70" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="C70" s="60">
+      <c r="C70" s="59">
         <v>800</v>
       </c>
-      <c r="D70" s="59">
+      <c r="D70" s="58">
         <f>D58</f>
         <v>60</v>
       </c>
-      <c r="E70" s="48">
+      <c r="E70" s="47">
         <f>($C$61/C70)^$E$58</f>
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="2:5" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="45" t="s">
+    <row r="71" spans="2:5" ht="16.5" thickTop="1">
+      <c r="B71" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="C71" s="60">
+      <c r="C71" s="59">
         <v>606</v>
       </c>
-      <c r="D71" s="54">
+      <c r="D71" s="53">
         <f>$D$58*(($C$70/C71)^$E$58)</f>
         <v>73.894867118770051</v>
       </c>
-      <c r="E71" s="48">
+      <c r="E71" s="47">
         <f>($C$70/C71)^$E$58</f>
         <v>1.2315811186461676</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B72" s="45" t="s">
+    <row r="72" spans="2:5">
+      <c r="B72" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="C72" s="60">
+      <c r="C72" s="59">
         <v>253</v>
       </c>
-      <c r="D72" s="54">
+      <c r="D72" s="53">
         <f>$D$58*(($C$70/C72)^$E$58)</f>
         <v>142.27491989040757</v>
       </c>
-      <c r="E72" s="48">
+      <c r="E72" s="47">
         <f>($C$70/C72)^$E$58</f>
         <v>2.3712486648401261</v>
       </c>
     </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B73" s="44" t="s">
+    <row r="73" spans="2:5">
+      <c r="B73" s="43" t="s">
         <v>198</v>
       </c>
-      <c r="C73" s="60">
+      <c r="C73" s="59">
         <v>370</v>
       </c>
-      <c r="D73" s="54">
+      <c r="D73" s="53">
         <f>$D$58*(($C$70/C73)^$E$58)</f>
         <v>106.98365906113423</v>
       </c>
-      <c r="E73" s="48">
+      <c r="E73" s="47">
         <f>($C$70/C73)^$E$58</f>
         <v>1.7830609843522371</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B74" s="44" t="s">
+    <row r="74" spans="2:5">
+      <c r="B74" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="C74" s="60">
+      <c r="C74" s="59">
         <v>283</v>
       </c>
-      <c r="D74" s="54">
+      <c r="D74" s="53">
         <f>$D$58*(($C$70/C74)^$E$58)</f>
         <v>130.80637609525397</v>
       </c>
-      <c r="E74" s="48">
+      <c r="E74" s="47">
         <f>($C$70/C74)^$E$58</f>
         <v>2.1801062682542329</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B75" s="44" t="s">
+    <row r="75" spans="2:5">
+      <c r="B75" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C75" s="60">
+      <c r="C75" s="59">
         <v>253</v>
       </c>
-      <c r="D75" s="54">
+      <c r="D75" s="53">
         <f>$D$58*(($C$70/C75)^$E$58)</f>
         <v>142.27491989040757</v>
       </c>
-      <c r="E75" s="48">
+      <c r="E75" s="47">
         <f>($C$70/C75)^$E$58</f>
         <v>2.3712486648401261</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="49" t="s">
+    <row r="81" spans="1:3" ht="18" thickBot="1">
+      <c r="A81" s="48" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="16.5" thickTop="1">
       <c r="B82" t="s">
         <v>216</v>
       </c>
-      <c r="C82" s="62">
+      <c r="C82" s="61">
         <v>4000</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3">
       <c r="B83" t="s">
         <v>218</v>
       </c>
-      <c r="C83" s="35">
+      <c r="C83" s="34">
         <v>1600</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="B84" t="s">
         <v>217</v>
       </c>
-      <c r="C84" s="35">
+      <c r="C84" s="34">
         <v>1000</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3">
       <c r="B85" t="s">
         <v>215</v>
       </c>
-      <c r="C85" s="63">
+      <c r="C85" s="62">
         <f>C82*(1-(C84/C83))</f>
         <v>1500</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="B86" t="s">
         <v>219</v>
       </c>
-      <c r="C86" s="38">
+      <c r="C86" s="37">
         <f>C83/C84</f>
         <v>1.6</v>
       </c>

--- a/RR_fuelflow.xlsx
+++ b/RR_fuelflow.xlsx
@@ -994,7 +994,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="240">
   <si>
     <t>name</t>
   </si>
@@ -1743,6 +1743,9 @@
   </si>
   <si>
     <t>Engine 2</t>
+  </si>
+  <si>
+    <t>LqdFluorine</t>
   </si>
 </sst>
 </file>
@@ -2079,7 +2082,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2180,6 +2183,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Calculation" xfId="4" builtinId="22"/>
@@ -2718,10 +2723,10 @@
         <v>66</v>
       </c>
       <c r="B7" s="22">
-        <v>289</v>
+        <v>219.6</v>
       </c>
       <c r="C7" s="22">
-        <v>90</v>
+        <v>0.16</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2790,23 +2795,23 @@
     <row r="9" spans="1:28" ht="16.5" thickTop="1">
       <c r="B9" s="19">
         <f>B7*9.80665</f>
-        <v>2834.12185</v>
+        <v>2153.54034</v>
       </c>
       <c r="C9" s="70">
         <f>IFERROR(C7*1000/B9,0)</f>
-        <v>31.755868224226138</v>
+        <v>7.4296263240650515E-2</v>
       </c>
       <c r="D9" s="19">
         <f>C7*1000*B9</f>
-        <v>255070966.5</v>
+        <v>344566.45439999999</v>
       </c>
       <c r="E9" s="19">
         <f>IFERROR(D9/C9,0)</f>
-        <v>8032246.660647423</v>
+        <v>4637735.9960073149</v>
       </c>
       <c r="G9" s="74">
         <f>SUM(B16:E16)</f>
-        <v>31.755868224226141</v>
+        <v>7.4296263240650515E-2</v>
       </c>
       <c r="H9" s="69" t="str">
         <f>IF($C$9&gt;$G$9,"Input excesive",IF($C$9&lt;$G$9,"Output excessive","Equal"))</f>
@@ -2820,7 +2825,7 @@
       </c>
       <c r="N9" s="70">
         <f>IFERROR(C7*1000/M9/B9,0)</f>
-        <v>21.170578816150758</v>
+        <v>4.9530842160433672E-2</v>
       </c>
       <c r="V9" s="2">
         <v>5</v>
@@ -2847,7 +2852,7 @@
       </c>
       <c r="N10" s="70">
         <f>IFERROR(C7*1000/M10/B9,0)</f>
-        <v>26.46322352018845</v>
+        <v>6.1913552700542093E-2</v>
       </c>
       <c r="O10" s="2"/>
       <c r="T10" s="5"/>
@@ -2886,7 +2891,7 @@
       </c>
       <c r="N11" s="70">
         <f>IFERROR(C7*1000/M11/B9,0)</f>
-        <v>8.5826670876286855</v>
+        <v>2.0080071146121758E-2</v>
       </c>
       <c r="V11" s="2">
         <v>7</v>
@@ -2909,15 +2914,13 @@
         <v>65</v>
       </c>
       <c r="B12" s="16">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="C12" s="16">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="D12" s="15"/>
-      <c r="E12" s="16">
-        <v>1.8527</v>
-      </c>
+      <c r="E12" s="16"/>
       <c r="G12" s="75" t="s">
         <v>88</v>
       </c>
@@ -2935,7 +2938,7 @@
       </c>
       <c r="N12" s="70">
         <f>IFERROR(C7*1000/M12/B9,0)</f>
-        <v>23.876592649794087</v>
+        <v>5.5861852060639483E-2</v>
       </c>
       <c r="V12" s="2">
         <v>8</v>
@@ -2958,10 +2961,10 @@
         <v>64</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="65" t="s">
@@ -2969,11 +2972,11 @@
       </c>
       <c r="G13" s="76">
         <f>IFERROR(E15/I13,"-")</f>
-        <v>0.37673593219496804</v>
-      </c>
-      <c r="H13" s="77">
+        <v>0</v>
+      </c>
+      <c r="H13" s="77" t="str">
         <f>IFERROR(E12/G13,"-")</f>
-        <v>4.9177682341200004</v>
+        <v>-</v>
       </c>
       <c r="I13" s="78">
         <v>200</v>
@@ -2991,15 +2994,15 @@
         <v>24</v>
       </c>
       <c r="B14" s="8">
-        <f>IFERROR(VLOOKUP(B13,Database!$A$2:$B$56,2,0),"-")</f>
-        <v>0.70209999999999995</v>
+        <f>IFERROR(VLOOKUP(B13,Database!$A$2:$B$57,2,0),"-")</f>
+        <v>5</v>
       </c>
       <c r="C14" s="8">
-        <f>IFERROR(VLOOKUP(C13,Database!$A$2:$B$56,2,0),"-")</f>
-        <v>5</v>
+        <f>IFERROR(VLOOKUP(C13,Database!$A$2:$B$57,2,0),"-")</f>
+        <v>1.141</v>
       </c>
       <c r="D14" s="8" t="str">
-        <f>IFERROR(VLOOKUP(D13,Database!$A$2:$B$56,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(D13,Database!$A$2:$B$57,2,0),"-")</f>
         <v>-</v>
       </c>
       <c r="E14" s="9">
@@ -3023,13 +3026,13 @@
       <c r="A15" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="74">
+      <c r="B15" s="87">
         <f>IFERROR(C9*B12/SUM(B17:D17),"-")</f>
-        <v>16.267541736707209</v>
-      </c>
-      <c r="C15" s="74">
+        <v>8.8206414864834999E-3</v>
+      </c>
+      <c r="C15" s="87">
         <f>IFERROR(C9*C12/SUM(B17:D17),"-")</f>
-        <v>4.0668854341768021</v>
+        <v>2.6461924459450496E-2</v>
       </c>
       <c r="D15" s="74">
         <f>IFERROR(C9*D12/SUM(B17:D17),"-")</f>
@@ -3037,8 +3040,9 @@
       </c>
       <c r="E15" s="74">
         <f>IFERROR(C9*E12/SUM(B17:D17),0)</f>
-        <v>75.347186438993603</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G15" s="86"/>
       <c r="L15" s="30"/>
       <c r="M15" s="21">
         <v>2080</v>
@@ -3069,11 +3073,11 @@
       </c>
       <c r="B16" s="69">
         <f>IFERROR($B$14*$B$15,"-")</f>
-        <v>11.42144105334213</v>
+        <v>4.4103207432417496E-2</v>
       </c>
       <c r="C16" s="69">
         <f t="shared" ref="C16:D16" si="0">IFERROR(C14*C15,"-")</f>
-        <v>20.334427170884013</v>
+        <v>3.0193055808233015E-2</v>
       </c>
       <c r="D16" s="69" t="str">
         <f t="shared" si="0"/>
@@ -3106,11 +3110,11 @@
       </c>
       <c r="B17" s="69">
         <f>IFERROR(B12*B14,"-")</f>
-        <v>0.28083999999999998</v>
+        <v>5</v>
       </c>
       <c r="C17" s="69">
         <f t="shared" ref="C17:D17" si="1">IFERROR(C12*C14,"-")</f>
-        <v>0.5</v>
+        <v>3.423</v>
       </c>
       <c r="D17" s="69" t="str">
         <f t="shared" si="1"/>
@@ -3599,15 +3603,15 @@
         <v>24</v>
       </c>
       <c r="B29" s="8">
-        <f>IFERROR(VLOOKUP(B28,Database!$A$2:$B$56,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(B28,Database!$A$2:$B$57,2,0),"-")</f>
         <v>7.0849999999999996E-2</v>
       </c>
       <c r="C29" s="8">
-        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$56,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$57,2,0),"-")</f>
         <v>5</v>
       </c>
       <c r="D29" s="8" t="str">
-        <f>IFERROR(VLOOKUP(D28,Database!$A$2:$B$56,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(D28,Database!$A$2:$B$57,2,0),"-")</f>
         <v>-</v>
       </c>
       <c r="E29" s="9">
@@ -4238,12 +4242,18 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$56</xm:f>
+            <xm:f>Database!$A$2:$A$57</xm:f>
           </x14:formula1>
-          <xm:sqref>B13:D13 B28:D28</xm:sqref>
+          <xm:sqref>B13:D13</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Database!$A$2:$A$57</xm:f>
+          </x14:formula1>
+          <xm:sqref>B28:D28</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4872,14 +4882,14 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>46</v>
+        <v>239</v>
       </c>
       <c r="B28" s="10">
-        <f t="shared" si="3"/>
-        <v>5.8999999999999997E-2</v>
+        <f t="shared" ref="B28" si="4">C28*1000</f>
+        <v>1.5050000000000001</v>
       </c>
       <c r="C28" s="11">
-        <v>5.8999999999999998E-5</v>
+        <v>1.505E-3</v>
       </c>
       <c r="G28" s="31" t="s">
         <v>103</v>
@@ -4896,14 +4906,14 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B29" s="10">
-        <f t="shared" si="3"/>
-        <v>7.0849999999999996E-2</v>
+        <f>C29*1000</f>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="C29" s="11">
-        <v>7.0850000000000001E-5</v>
+        <v>5.8999999999999998E-5</v>
       </c>
       <c r="G29" s="31" t="s">
         <v>38</v>
@@ -4920,14 +4930,14 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="10">
-        <f t="shared" si="3"/>
-        <v>0.42560999999999999</v>
+        <f>C30*1000</f>
+        <v>7.0849999999999996E-2</v>
       </c>
       <c r="C30" s="11">
-        <v>4.2560999999999999E-4</v>
+        <v>7.0850000000000001E-5</v>
       </c>
       <c r="G30" s="31" t="s">
         <v>45</v>
@@ -4944,14 +4954,14 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="B31" s="10">
-        <f t="shared" si="3"/>
-        <v>1.141</v>
+        <f>C31*1000</f>
+        <v>0.42560999999999999</v>
       </c>
       <c r="C31" s="11">
-        <v>1.1410000000000001E-3</v>
+        <v>4.2560999999999999E-4</v>
       </c>
       <c r="G31" s="31" t="s">
         <v>161</v>
@@ -4968,14 +4978,14 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B32" s="10">
-        <f t="shared" si="3"/>
-        <v>0.82490700000000006</v>
+        <f>C32*1000</f>
+        <v>1.141</v>
       </c>
       <c r="C32" s="11">
-        <v>8.2490700000000005E-4</v>
+        <v>1.1410000000000001E-3</v>
       </c>
       <c r="G32" s="31" t="s">
         <v>44</v>
@@ -4992,14 +5002,14 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="B33" s="10">
-        <f t="shared" si="3"/>
-        <v>7.8</v>
+        <f>C33*1000</f>
+        <v>0.82490700000000006</v>
       </c>
       <c r="C33" s="11">
-        <v>7.7999999999999996E-3</v>
+        <v>8.2490700000000005E-4</v>
       </c>
       <c r="G33" s="31" t="s">
         <v>43</v>
@@ -5016,14 +5026,14 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B34" s="10">
-        <f t="shared" si="3"/>
-        <v>7.085</v>
+        <f>C34*1000</f>
+        <v>7.8</v>
       </c>
       <c r="C34" s="11">
-        <v>7.0850000000000002E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="G34" s="31" t="s">
         <v>46</v>
@@ -5040,14 +5050,14 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B35" s="10">
-        <f t="shared" si="3"/>
-        <v>0.88</v>
+        <f>C35*1000</f>
+        <v>7.085</v>
       </c>
       <c r="C35" s="11">
-        <v>8.8000000000000003E-4</v>
+        <v>7.0850000000000002E-3</v>
       </c>
       <c r="G35" s="31" t="s">
         <v>162</v>
@@ -5064,14 +5074,14 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B36" s="10">
-        <f t="shared" si="3"/>
-        <v>1.45</v>
+        <f>C36*1000</f>
+        <v>0.88</v>
       </c>
       <c r="C36" s="11">
-        <v>1.4499999999999999E-3</v>
+        <v>8.8000000000000003E-4</v>
       </c>
       <c r="G36" s="31" t="s">
         <v>29</v>
@@ -5087,15 +5097,15 @@
       </c>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="5" t="s">
-        <v>80</v>
+      <c r="A37" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="B37" s="10">
-        <f t="shared" si="3"/>
-        <v>1.05</v>
+        <f>C37*1000</f>
+        <v>1.45</v>
       </c>
       <c r="C37" s="11">
-        <v>1.0499999999999999E-3</v>
+        <v>1.4499999999999999E-3</v>
       </c>
       <c r="G37" s="31" t="s">
         <v>30</v>
@@ -5112,14 +5122,14 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B38" s="10">
-        <f t="shared" si="3"/>
-        <v>0.79100000000000004</v>
+        <f>C38*1000</f>
+        <v>1.05</v>
       </c>
       <c r="C38" s="11">
-        <v>7.9100000000000004E-4</v>
+        <v>1.0499999999999999E-3</v>
       </c>
       <c r="G38" s="31" t="s">
         <v>85</v>
@@ -5136,14 +5146,14 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B39" s="10">
-        <f t="shared" si="3"/>
-        <v>0.82899999999999996</v>
+        <f>C39*1000</f>
+        <v>0.79100000000000004</v>
       </c>
       <c r="C39" s="11">
-        <v>8.2899999999999998E-4</v>
+        <v>7.9100000000000004E-4</v>
       </c>
       <c r="G39" s="31" t="s">
         <v>106</v>
@@ -5159,15 +5169,15 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="2" t="s">
-        <v>77</v>
+      <c r="A40" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="B40" s="10">
-        <f t="shared" si="3"/>
-        <v>1</v>
+        <f>C40*1000</f>
+        <v>0.82899999999999996</v>
       </c>
       <c r="C40" s="11">
-        <v>1E-3</v>
+        <v>8.2899999999999998E-4</v>
       </c>
       <c r="G40" s="31" t="s">
         <v>79</v>
@@ -5184,6 +5194,16 @@
       </c>
     </row>
     <row r="41" spans="1:10">
+      <c r="A41" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" s="10">
+        <f>C41*1000</f>
+        <v>1</v>
+      </c>
+      <c r="C41" s="11">
+        <v>1E-3</v>
+      </c>
       <c r="G41" s="31" t="s">
         <v>166</v>
       </c>
@@ -5197,12 +5217,7 @@
         <v>159.69</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="18" thickBot="1">
-      <c r="A42" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B42"/>
-      <c r="C42" s="12"/>
+    <row r="42" spans="1:10">
       <c r="G42" s="31" t="s">
         <v>168</v>
       </c>
@@ -5217,17 +5232,12 @@
         <v>111.69</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="16.5" thickTop="1">
-      <c r="A43" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="10">
-        <f t="shared" ref="B43:B56" si="4">C43*1000</f>
-        <v>5</v>
-      </c>
-      <c r="C43" s="11">
-        <v>5.0000000000000001E-3</v>
-      </c>
+    <row r="43" spans="1:10" ht="18" thickBot="1">
+      <c r="A43" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43"/>
+      <c r="C43" s="12"/>
       <c r="G43" s="31" t="s">
         <v>42</v>
       </c>
@@ -5242,16 +5252,16 @@
         <v>111.69</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" ht="16.5" thickTop="1">
       <c r="A44" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B44" s="10">
-        <f t="shared" si="4"/>
-        <v>54.4</v>
+        <f t="shared" ref="B44:B57" si="5">C44*1000</f>
+        <v>5</v>
       </c>
       <c r="C44" s="11">
-        <v>5.4399999999999997E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G44" s="31" t="s">
         <v>170</v>
@@ -5269,14 +5279,14 @@
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B45" s="10">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>54.4</v>
       </c>
       <c r="C45" s="11">
-        <v>5.0000000000000001E-3</v>
+        <v>5.4399999999999997E-2</v>
       </c>
       <c r="G45" s="31" t="s">
         <v>171</v>
@@ -5294,14 +5304,14 @@
     </row>
     <row r="46" spans="1:10" ht="18.75">
       <c r="A46" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B46" s="10">
-        <f t="shared" si="4"/>
-        <v>6.0000000000000005E-2</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="C46" s="11">
-        <v>6.0000000000000002E-5</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G46" s="31" t="s">
         <v>82</v>
@@ -5318,14 +5328,14 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B47" s="10">
-        <f t="shared" si="4"/>
-        <v>5.0108799999999993</v>
+        <f t="shared" si="5"/>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="C47" s="11">
-        <v>5.0108799999999997E-3</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="G47" s="31" t="s">
         <v>174</v>
@@ -5342,14 +5352,14 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B48" s="10">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>5.0108799999999993</v>
       </c>
       <c r="C48" s="11">
-        <v>5.0000000000000001E-3</v>
+        <v>5.0108799999999997E-3</v>
       </c>
       <c r="G48" s="31" t="s">
         <v>176</v>
@@ -5367,14 +5377,14 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B49" s="10">
-        <f t="shared" si="4"/>
-        <v>8.6</v>
+        <f t="shared" si="5"/>
+        <v>5</v>
       </c>
       <c r="C49" s="11">
-        <v>8.6E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G49" s="31" t="s">
         <v>83</v>
@@ -5391,14 +5401,14 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B50" s="10">
-        <f t="shared" si="4"/>
-        <v>5.7050000000000001</v>
+        <f t="shared" si="5"/>
+        <v>8.6</v>
       </c>
       <c r="C50" s="11">
-        <v>5.705E-3</v>
+        <v>8.6E-3</v>
       </c>
       <c r="G50" s="31" t="s">
         <v>178</v>
@@ -5415,14 +5425,14 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B51" s="10">
-        <f t="shared" si="4"/>
-        <v>0.35399999999999998</v>
+        <f t="shared" si="5"/>
+        <v>5.7050000000000001</v>
       </c>
       <c r="C51" s="11">
-        <v>3.5399999999999999E-4</v>
+        <v>5.705E-3</v>
       </c>
       <c r="G51" s="31" t="s">
         <v>179</v>
@@ -5439,14 +5449,14 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" s="10">
-        <f t="shared" si="4"/>
-        <v>2.12805</v>
+        <f t="shared" si="5"/>
+        <v>0.35399999999999998</v>
       </c>
       <c r="C52" s="11">
-        <v>2.1280499999999998E-3</v>
+        <v>3.5399999999999999E-4</v>
       </c>
       <c r="G52" s="31" t="s">
         <v>180</v>
@@ -5464,14 +5474,14 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B53" s="10">
-        <f t="shared" si="4"/>
-        <v>4.1000000000000005</v>
+        <f t="shared" si="5"/>
+        <v>2.12805</v>
       </c>
       <c r="C53" s="11">
-        <v>4.1000000000000003E-3</v>
+        <v>2.1280499999999998E-3</v>
       </c>
       <c r="G53" s="31" t="s">
         <v>182</v>
@@ -5488,14 +5498,14 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="B54" s="10">
-        <f t="shared" si="4"/>
-        <v>12.5</v>
+        <f t="shared" si="5"/>
+        <v>4.1000000000000005</v>
       </c>
       <c r="C54" s="11">
-        <v>1.2500000000000001E-2</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="G54" s="31" t="s">
         <v>183</v>
@@ -5512,14 +5522,14 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B55" s="10">
-        <f t="shared" si="4"/>
-        <v>7.5</v>
+        <f t="shared" si="5"/>
+        <v>12.5</v>
       </c>
       <c r="C55" s="11">
-        <v>7.4999999999999997E-3</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="G55" s="31" t="s">
         <v>185</v>
@@ -5535,15 +5545,15 @@
       </c>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="5" t="s">
-        <v>78</v>
+      <c r="A56" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="B56" s="10">
-        <f t="shared" si="4"/>
-        <v>5</v>
+        <f t="shared" si="5"/>
+        <v>7.5</v>
       </c>
       <c r="C56" s="11">
-        <v>5.0000000000000001E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="G56" s="31" t="s">
         <v>187</v>
@@ -5559,6 +5569,16 @@
       </c>
     </row>
     <row r="57" spans="1:10">
+      <c r="A57" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B57" s="10">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="C57" s="11">
+        <v>5.0000000000000001E-3</v>
+      </c>
       <c r="G57" s="31" t="s">
         <v>86</v>
       </c>
@@ -5610,7 +5630,7 @@
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2">
-      <formula1>$A$11:$A$40</formula1>
+      <formula1>$A$11:$A$41</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="1" right="1" top="1.6666666666666667" bottom="1.6666666666666667" header="1" footer="1"/>

--- a/RR_fuelflow.xlsx
+++ b/RR_fuelflow.xlsx
@@ -994,7 +994,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="242">
   <si>
     <t>name</t>
   </si>
@@ -1746,6 +1746,12 @@
   </si>
   <si>
     <t>LqdFluorine</t>
+  </si>
+  <si>
+    <t>LithiumSaltWater</t>
+  </si>
+  <si>
+    <t>Octaazacubane</t>
   </si>
 </sst>
 </file>
@@ -2174,6 +2180,8 @@
     <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="181" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2183,8 +2191,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="181" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Calculation" xfId="4" builtinId="22"/>
@@ -2564,13 +2570,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="20.25" thickBot="1">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="85" t="s">
         <v>209</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
     </row>
     <row r="2" spans="1:28" ht="16.5" thickTop="1">
       <c r="A2" s="65" t="s">
@@ -2723,10 +2729,10 @@
         <v>66</v>
       </c>
       <c r="B7" s="22">
-        <v>219.6</v>
+        <v>183</v>
       </c>
       <c r="C7" s="22">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2795,23 +2801,23 @@
     <row r="9" spans="1:28" ht="16.5" thickTop="1">
       <c r="B9" s="19">
         <f>B7*9.80665</f>
-        <v>2153.54034</v>
+        <v>1794.6169499999999</v>
       </c>
       <c r="C9" s="70">
         <f>IFERROR(C7*1000/B9,0)</f>
-        <v>7.4296263240650515E-2</v>
+        <v>5.5722197430487889E-2</v>
       </c>
       <c r="D9" s="19">
         <f>C7*1000*B9</f>
-        <v>344566.45439999999</v>
+        <v>179461.69499999998</v>
       </c>
       <c r="E9" s="19">
         <f>IFERROR(D9/C9,0)</f>
-        <v>4637735.9960073149</v>
+        <v>3220649.9972273018</v>
       </c>
       <c r="G9" s="74">
         <f>SUM(B16:E16)</f>
-        <v>7.4296263240650515E-2</v>
+        <v>5.5722197430487889E-2</v>
       </c>
       <c r="H9" s="69" t="str">
         <f>IF($C$9&gt;$G$9,"Input excesive",IF($C$9&lt;$G$9,"Output excessive","Equal"))</f>
@@ -2825,7 +2831,7 @@
       </c>
       <c r="N9" s="70">
         <f>IFERROR(C7*1000/M9/B9,0)</f>
-        <v>4.9530842160433672E-2</v>
+        <v>3.7148131620325257E-2</v>
       </c>
       <c r="V9" s="2">
         <v>5</v>
@@ -2852,7 +2858,7 @@
       </c>
       <c r="N10" s="70">
         <f>IFERROR(C7*1000/M10/B9,0)</f>
-        <v>6.1913552700542093E-2</v>
+        <v>4.643516452540658E-2</v>
       </c>
       <c r="O10" s="2"/>
       <c r="T10" s="5"/>
@@ -2891,7 +2897,7 @@
       </c>
       <c r="N11" s="70">
         <f>IFERROR(C7*1000/M11/B9,0)</f>
-        <v>2.0080071146121758E-2</v>
+        <v>1.5060053359591319E-2</v>
       </c>
       <c r="V11" s="2">
         <v>7</v>
@@ -2917,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
@@ -2938,7 +2944,7 @@
       </c>
       <c r="N12" s="70">
         <f>IFERROR(C7*1000/M12/B9,0)</f>
-        <v>5.5861852060639483E-2</v>
+        <v>4.1896389045479612E-2</v>
       </c>
       <c r="V12" s="2">
         <v>8</v>
@@ -2961,7 +2967,7 @@
         <v>64</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>26</v>
+        <v>161</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>85</v>
@@ -2994,15 +3000,15 @@
         <v>24</v>
       </c>
       <c r="B14" s="8">
-        <f>IFERROR(VLOOKUP(B13,Database!$A$2:$B$57,2,0),"-")</f>
-        <v>5</v>
+        <f>IFERROR(VLOOKUP(B13,Database!$A$2:$B$59,2,0),"-")</f>
+        <v>0.79</v>
       </c>
       <c r="C14" s="8">
-        <f>IFERROR(VLOOKUP(C13,Database!$A$2:$B$57,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(C13,Database!$A$2:$B$59,2,0),"-")</f>
         <v>1.141</v>
       </c>
       <c r="D14" s="8" t="str">
-        <f>IFERROR(VLOOKUP(D13,Database!$A$2:$B$57,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(D13,Database!$A$2:$B$59,2,0),"-")</f>
         <v>-</v>
       </c>
       <c r="E14" s="9">
@@ -3026,13 +3032,13 @@
       <c r="A15" s="71" t="s">
         <v>73</v>
       </c>
-      <c r="B15" s="87">
+      <c r="B15" s="84">
         <f>IFERROR(C9*B12/SUM(B17:D17),"-")</f>
-        <v>8.8206414864834999E-3</v>
-      </c>
-      <c r="C15" s="87">
+        <v>2.8856653252453592E-2</v>
+      </c>
+      <c r="C15" s="84">
         <f>IFERROR(C9*C12/SUM(B17:D17),"-")</f>
-        <v>2.6461924459450496E-2</v>
+        <v>2.8856653252453592E-2</v>
       </c>
       <c r="D15" s="74">
         <f>IFERROR(C9*D12/SUM(B17:D17),"-")</f>
@@ -3042,7 +3048,7 @@
         <f>IFERROR(C9*E12/SUM(B17:D17),0)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="86"/>
+      <c r="G15" s="83"/>
       <c r="L15" s="30"/>
       <c r="M15" s="21">
         <v>2080</v>
@@ -3073,11 +3079,11 @@
       </c>
       <c r="B16" s="69">
         <f>IFERROR($B$14*$B$15,"-")</f>
-        <v>4.4103207432417496E-2</v>
+        <v>2.2796756069438338E-2</v>
       </c>
       <c r="C16" s="69">
         <f t="shared" ref="C16:D16" si="0">IFERROR(C14*C15,"-")</f>
-        <v>3.0193055808233015E-2</v>
+        <v>3.2925441361049551E-2</v>
       </c>
       <c r="D16" s="69" t="str">
         <f t="shared" si="0"/>
@@ -3110,11 +3116,11 @@
       </c>
       <c r="B17" s="69">
         <f>IFERROR(B12*B14,"-")</f>
-        <v>5</v>
+        <v>0.79</v>
       </c>
       <c r="C17" s="69">
         <f t="shared" ref="C17:D17" si="1">IFERROR(C12*C14,"-")</f>
-        <v>3.423</v>
+        <v>1.141</v>
       </c>
       <c r="D17" s="69" t="str">
         <f t="shared" si="1"/>
@@ -3603,15 +3609,15 @@
         <v>24</v>
       </c>
       <c r="B29" s="8">
-        <f>IFERROR(VLOOKUP(B28,Database!$A$2:$B$57,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(B28,Database!$A$2:$B$59,2,0),"-")</f>
         <v>7.0849999999999996E-2</v>
       </c>
       <c r="C29" s="8">
-        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$57,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$59,2,0),"-")</f>
         <v>5</v>
       </c>
       <c r="D29" s="8" t="str">
-        <f>IFERROR(VLOOKUP(D28,Database!$A$2:$B$57,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(D28,Database!$A$2:$B$59,2,0),"-")</f>
         <v>-</v>
       </c>
       <c r="E29" s="9">
@@ -4245,13 +4251,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$57</xm:f>
+            <xm:f>Database!$A$2:$A$59</xm:f>
           </x14:formula1>
           <xm:sqref>B13:D13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$57</xm:f>
+            <xm:f>Database!$A$2:$A$59</xm:f>
           </x14:formula1>
           <xm:sqref>B28:D28</xm:sqref>
         </x14:dataValidation>
@@ -4784,15 +4790,15 @@
       </c>
     </row>
     <row r="24" spans="1:10">
-      <c r="A24" s="5" t="s">
-        <v>45</v>
+      <c r="A24" s="2" t="s">
+        <v>240</v>
       </c>
       <c r="B24" s="10">
-        <f t="shared" si="2"/>
-        <v>0.70209999999999995</v>
+        <f t="shared" ref="B24" si="3">C24*1000</f>
+        <v>8.6964000000000006</v>
       </c>
       <c r="C24" s="11">
-        <v>7.0209999999999999E-4</v>
+        <v>8.6964E-3</v>
       </c>
       <c r="G24" s="31" t="s">
         <v>152</v>
@@ -4808,15 +4814,15 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>161</v>
+      <c r="A25" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="B25" s="10">
-        <f t="shared" si="2"/>
-        <v>0.79</v>
+        <f>C25*1000</f>
+        <v>0.70209999999999995</v>
       </c>
       <c r="C25" s="11">
-        <v>7.9000000000000001E-4</v>
+        <v>7.0209999999999999E-4</v>
       </c>
       <c r="G25" s="31" t="s">
         <v>154</v>
@@ -4833,14 +4839,14 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
       <c r="B26" s="10">
-        <f t="shared" ref="B26:B40" si="3">C26*1000</f>
-        <v>1.1732500000000001</v>
+        <f>C26*1000</f>
+        <v>0.79</v>
       </c>
       <c r="C26" s="11">
-        <v>1.17325E-3</v>
+        <v>7.9000000000000001E-4</v>
       </c>
       <c r="G26" s="31" t="s">
         <v>156</v>
@@ -4858,14 +4864,14 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="10">
-        <f t="shared" si="3"/>
-        <v>0.16239999999999999</v>
+        <f t="shared" ref="B27:B28" si="4">C27*1000</f>
+        <v>1.1732500000000001</v>
       </c>
       <c r="C27" s="11">
-        <v>1.6239999999999999E-4</v>
+        <v>1.17325E-3</v>
       </c>
       <c r="G27" s="31" t="s">
         <v>107</v>
@@ -4882,14 +4888,14 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>239</v>
+        <v>43</v>
       </c>
       <c r="B28" s="10">
-        <f t="shared" ref="B28" si="4">C28*1000</f>
-        <v>1.5050000000000001</v>
+        <f t="shared" si="4"/>
+        <v>0.16239999999999999</v>
       </c>
       <c r="C28" s="11">
-        <v>1.505E-3</v>
+        <v>1.6239999999999999E-4</v>
       </c>
       <c r="G28" s="31" t="s">
         <v>103</v>
@@ -4906,14 +4912,14 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>46</v>
+        <v>239</v>
       </c>
       <c r="B29" s="10">
-        <f>C29*1000</f>
-        <v>5.8999999999999997E-2</v>
+        <f t="shared" ref="B29" si="5">C29*1000</f>
+        <v>1.5050000000000001</v>
       </c>
       <c r="C29" s="11">
-        <v>5.8999999999999998E-5</v>
+        <v>1.505E-3</v>
       </c>
       <c r="G29" s="31" t="s">
         <v>38</v>
@@ -4930,14 +4936,14 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B30" s="10">
-        <f>C30*1000</f>
-        <v>7.0849999999999996E-2</v>
+        <f t="shared" ref="B30:B42" si="6">C30*1000</f>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="C30" s="11">
-        <v>7.0850000000000001E-5</v>
+        <v>5.8999999999999998E-5</v>
       </c>
       <c r="G30" s="31" t="s">
         <v>45</v>
@@ -4954,14 +4960,14 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="10">
-        <f>C31*1000</f>
-        <v>0.42560999999999999</v>
+        <f t="shared" si="6"/>
+        <v>7.0849999999999996E-2</v>
       </c>
       <c r="C31" s="11">
-        <v>4.2560999999999999E-4</v>
+        <v>7.0850000000000001E-5</v>
       </c>
       <c r="G31" s="31" t="s">
         <v>161</v>
@@ -4978,14 +4984,14 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="B32" s="10">
-        <f>C32*1000</f>
-        <v>1.141</v>
+        <f t="shared" si="6"/>
+        <v>0.42560999999999999</v>
       </c>
       <c r="C32" s="11">
-        <v>1.1410000000000001E-3</v>
+        <v>4.2560999999999999E-4</v>
       </c>
       <c r="G32" s="31" t="s">
         <v>44</v>
@@ -5002,14 +5008,14 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="B33" s="10">
-        <f>C33*1000</f>
-        <v>0.82490700000000006</v>
+        <f t="shared" si="6"/>
+        <v>1.141</v>
       </c>
       <c r="C33" s="11">
-        <v>8.2490700000000005E-4</v>
+        <v>1.1410000000000001E-3</v>
       </c>
       <c r="G33" s="31" t="s">
         <v>43</v>
@@ -5026,14 +5032,14 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="B34" s="10">
-        <f>C34*1000</f>
-        <v>7.8</v>
+        <f t="shared" si="6"/>
+        <v>0.82490700000000006</v>
       </c>
       <c r="C34" s="11">
-        <v>7.7999999999999996E-3</v>
+        <v>8.2490700000000005E-4</v>
       </c>
       <c r="G34" s="31" t="s">
         <v>46</v>
@@ -5050,14 +5056,14 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="B35" s="10">
-        <f>C35*1000</f>
-        <v>7.085</v>
+        <f t="shared" si="6"/>
+        <v>7.8</v>
       </c>
       <c r="C35" s="11">
-        <v>7.0850000000000002E-3</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="G35" s="31" t="s">
         <v>162</v>
@@ -5074,14 +5080,14 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B36" s="10">
-        <f>C36*1000</f>
-        <v>0.88</v>
+        <f t="shared" si="6"/>
+        <v>7.085</v>
       </c>
       <c r="C36" s="11">
-        <v>8.8000000000000003E-4</v>
+        <v>7.0850000000000002E-3</v>
       </c>
       <c r="G36" s="31" t="s">
         <v>29</v>
@@ -5098,14 +5104,14 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B37" s="10">
-        <f>C37*1000</f>
-        <v>1.45</v>
+        <f t="shared" si="6"/>
+        <v>0.88</v>
       </c>
       <c r="C37" s="11">
-        <v>1.4499999999999999E-3</v>
+        <v>8.8000000000000003E-4</v>
       </c>
       <c r="G37" s="31" t="s">
         <v>30</v>
@@ -5121,15 +5127,15 @@
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="5" t="s">
-        <v>80</v>
+      <c r="A38" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="B38" s="10">
-        <f>C38*1000</f>
-        <v>1.05</v>
+        <f t="shared" si="6"/>
+        <v>1.45</v>
       </c>
       <c r="C38" s="11">
-        <v>1.0499999999999999E-3</v>
+        <v>1.4499999999999999E-3</v>
       </c>
       <c r="G38" s="31" t="s">
         <v>85</v>
@@ -5146,14 +5152,14 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="5" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B39" s="10">
-        <f>C39*1000</f>
-        <v>0.79100000000000004</v>
+        <f t="shared" si="6"/>
+        <v>1.05</v>
       </c>
       <c r="C39" s="11">
-        <v>7.9100000000000004E-4</v>
+        <v>1.0499999999999999E-3</v>
       </c>
       <c r="G39" s="31" t="s">
         <v>106</v>
@@ -5169,15 +5175,15 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="5" t="s">
-        <v>87</v>
+      <c r="A40" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="B40" s="10">
-        <f>C40*1000</f>
-        <v>0.82899999999999996</v>
+        <f t="shared" si="6"/>
+        <v>3.3103319999999998</v>
       </c>
       <c r="C40" s="11">
-        <v>8.2899999999999998E-4</v>
+        <v>3.310332E-3</v>
       </c>
       <c r="G40" s="31" t="s">
         <v>79</v>
@@ -5194,15 +5200,15 @@
       </c>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="2" t="s">
-        <v>77</v>
+      <c r="A41" s="5" t="s">
+        <v>86</v>
       </c>
       <c r="B41" s="10">
         <f>C41*1000</f>
-        <v>1</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="C41" s="11">
-        <v>1E-3</v>
+        <v>7.9100000000000004E-4</v>
       </c>
       <c r="G41" s="31" t="s">
         <v>166</v>
@@ -5218,6 +5224,16 @@
       </c>
     </row>
     <row r="42" spans="1:10">
+      <c r="A42" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="10">
+        <f>C42*1000</f>
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="C42" s="11">
+        <v>8.2899999999999998E-4</v>
+      </c>
       <c r="G42" s="31" t="s">
         <v>168</v>
       </c>
@@ -5232,12 +5248,17 @@
         <v>111.69</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="18" thickBot="1">
-      <c r="A43" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B43"/>
-      <c r="C43" s="12"/>
+    <row r="43" spans="1:10">
+      <c r="A43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B43" s="10">
+        <f>C43*1000</f>
+        <v>1</v>
+      </c>
+      <c r="C43" s="11">
+        <v>1E-3</v>
+      </c>
       <c r="G43" s="31" t="s">
         <v>42</v>
       </c>
@@ -5252,17 +5273,7 @@
         <v>111.69</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="16.5" thickTop="1">
-      <c r="A44" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B44" s="10">
-        <f t="shared" ref="B44:B57" si="5">C44*1000</f>
-        <v>5</v>
-      </c>
-      <c r="C44" s="11">
-        <v>5.0000000000000001E-3</v>
-      </c>
+    <row r="44" spans="1:10">
       <c r="G44" s="31" t="s">
         <v>170</v>
       </c>
@@ -5277,17 +5288,12 @@
         <v>16.052</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B45" s="10">
-        <f t="shared" si="5"/>
-        <v>54.4</v>
-      </c>
-      <c r="C45" s="11">
-        <v>5.4399999999999997E-2</v>
-      </c>
+    <row r="45" spans="1:10" ht="18" thickBot="1">
+      <c r="A45" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45"/>
+      <c r="C45" s="12"/>
       <c r="G45" s="31" t="s">
         <v>171</v>
       </c>
@@ -5302,12 +5308,12 @@
         <v>88.171999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="18.75">
+    <row r="46" spans="1:10" ht="19.5" thickTop="1">
       <c r="A46" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="B46:B59" si="7">C46*1000</f>
         <v>5</v>
       </c>
       <c r="C46" s="11">
@@ -5328,14 +5334,14 @@
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B47" s="10">
-        <f t="shared" si="5"/>
-        <v>6.0000000000000005E-2</v>
+        <f t="shared" si="7"/>
+        <v>54.4</v>
       </c>
       <c r="C47" s="11">
-        <v>6.0000000000000002E-5</v>
+        <v>5.4399999999999997E-2</v>
       </c>
       <c r="G47" s="31" t="s">
         <v>174</v>
@@ -5352,14 +5358,14 @@
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B48" s="10">
-        <f t="shared" si="5"/>
-        <v>5.0108799999999993</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="C48" s="11">
-        <v>5.0108799999999997E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G48" s="31" t="s">
         <v>176</v>
@@ -5377,14 +5383,14 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B49" s="10">
-        <f t="shared" si="5"/>
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="C49" s="11">
-        <v>5.0000000000000001E-3</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="G49" s="31" t="s">
         <v>83</v>
@@ -5401,14 +5407,14 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B50" s="10">
-        <f t="shared" si="5"/>
-        <v>8.6</v>
+        <f t="shared" si="7"/>
+        <v>5.0108799999999993</v>
       </c>
       <c r="C50" s="11">
-        <v>8.6E-3</v>
+        <v>5.0108799999999997E-3</v>
       </c>
       <c r="G50" s="31" t="s">
         <v>178</v>
@@ -5425,14 +5431,14 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B51" s="10">
-        <f t="shared" si="5"/>
-        <v>5.7050000000000001</v>
+        <f t="shared" si="7"/>
+        <v>5</v>
       </c>
       <c r="C51" s="11">
-        <v>5.705E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G51" s="31" t="s">
         <v>179</v>
@@ -5449,14 +5455,14 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52" s="10">
-        <f t="shared" si="5"/>
-        <v>0.35399999999999998</v>
+        <f t="shared" si="7"/>
+        <v>8.6</v>
       </c>
       <c r="C52" s="11">
-        <v>3.5399999999999999E-4</v>
+        <v>8.6E-3</v>
       </c>
       <c r="G52" s="31" t="s">
         <v>180</v>
@@ -5474,14 +5480,14 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B53" s="10">
-        <f t="shared" si="5"/>
-        <v>2.12805</v>
+        <f t="shared" si="7"/>
+        <v>5.7050000000000001</v>
       </c>
       <c r="C53" s="11">
-        <v>2.1280499999999998E-3</v>
+        <v>5.705E-3</v>
       </c>
       <c r="G53" s="31" t="s">
         <v>182</v>
@@ -5498,14 +5504,14 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B54" s="10">
-        <f t="shared" si="5"/>
-        <v>4.1000000000000005</v>
+        <f t="shared" si="7"/>
+        <v>0.35399999999999998</v>
       </c>
       <c r="C54" s="11">
-        <v>4.1000000000000003E-3</v>
+        <v>3.5399999999999999E-4</v>
       </c>
       <c r="G54" s="31" t="s">
         <v>183</v>
@@ -5522,14 +5528,14 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B55" s="10">
-        <f t="shared" si="5"/>
-        <v>12.5</v>
+        <f t="shared" si="7"/>
+        <v>2.12805</v>
       </c>
       <c r="C55" s="11">
-        <v>1.2500000000000001E-2</v>
+        <v>2.1280499999999998E-3</v>
       </c>
       <c r="G55" s="31" t="s">
         <v>185</v>
@@ -5546,14 +5552,14 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B56" s="10">
-        <f t="shared" si="5"/>
-        <v>7.5</v>
+        <f t="shared" si="7"/>
+        <v>4.1000000000000005</v>
       </c>
       <c r="C56" s="11">
-        <v>7.4999999999999997E-3</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="G56" s="31" t="s">
         <v>187</v>
@@ -5569,15 +5575,15 @@
       </c>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="5" t="s">
-        <v>78</v>
+      <c r="A57" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="B57" s="10">
-        <f t="shared" si="5"/>
-        <v>5</v>
+        <f t="shared" si="7"/>
+        <v>12.5</v>
       </c>
       <c r="C57" s="11">
-        <v>5.0000000000000001E-3</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="G57" s="31" t="s">
         <v>86</v>
@@ -5593,6 +5599,16 @@
       </c>
     </row>
     <row r="58" spans="1:10">
+      <c r="A58" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="10">
+        <f t="shared" si="7"/>
+        <v>7.5</v>
+      </c>
+      <c r="C58" s="11">
+        <v>7.4999999999999997E-3</v>
+      </c>
       <c r="G58" s="31" t="s">
         <v>87</v>
       </c>
@@ -5608,6 +5624,16 @@
       </c>
     </row>
     <row r="59" spans="1:10">
+      <c r="A59" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" s="10">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="C59" s="11">
+        <v>5.0000000000000001E-3</v>
+      </c>
       <c r="G59" s="31" t="s">
         <v>77</v>
       </c>
@@ -5630,7 +5656,7 @@
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2">
-      <formula1>$A$11:$A$41</formula1>
+      <formula1>$A$11:$A$43</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="1" right="1" top="1.6666666666666667" bottom="1.6666666666666667" header="1" footer="1"/>
@@ -5659,15 +5685,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="86" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="84"/>
-      <c r="C1" s="84"/>
-      <c r="D1" s="84"/>
-      <c r="E1" s="84"/>
-      <c r="F1" s="84"/>
-      <c r="G1" s="84"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
@@ -6102,13 +6128,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25" thickBot="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="87" t="s">
         <v>204</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" thickTop="1" thickBot="1">
       <c r="A2" s="48" t="s">

--- a/RR_fuelflow.xlsx
+++ b/RR_fuelflow.xlsx
@@ -158,54 +158,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="M9" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Jadon Wade:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Reference multipliers for Isp to buffer against annoying and near-unplayable dV with some part mods</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N9" authorId="0" shapeId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Jadon Wade:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-If Isp goes up, mass flow must go down. The opposite is true.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="G12" authorId="0" shapeId="0">
       <text>
         <r>
@@ -994,7 +946,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="230">
   <si>
     <t>name</t>
   </si>
@@ -1068,9 +1020,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Mass (kg)</t>
-  </si>
-  <si>
     <t>Density (kg)</t>
   </si>
   <si>
@@ -1204,9 +1153,6 @@
   </si>
   <si>
     <t>Supports stock, CRP and WBI.</t>
-  </si>
-  <si>
-    <t>Mass (kg/s)</t>
   </si>
   <si>
     <t>Ratio (U/s)</t>
@@ -1700,45 +1646,6 @@
     <t>Orthosilicate (SiO4)</t>
   </si>
   <si>
-    <t>New Isp</t>
-  </si>
-  <si>
-    <t>Isp Mult</t>
-  </si>
-  <si>
-    <t>New thrust</t>
-  </si>
-  <si>
-    <t>Isp mult to -3/4 power</t>
-  </si>
-  <si>
-    <t>Base thrust</t>
-  </si>
-  <si>
-    <t>Base Isp</t>
-  </si>
-  <si>
-    <t>Isp</t>
-  </si>
-  <si>
-    <t>Thrust</t>
-  </si>
-  <si>
-    <t>EnrU ratio</t>
-  </si>
-  <si>
-    <t>Gear</t>
-  </si>
-  <si>
-    <t>B Ratio</t>
-  </si>
-  <si>
-    <t>W Ratio</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>Engine 1</t>
   </si>
   <si>
@@ -1752,6 +1659,15 @@
   </si>
   <si>
     <t>Octaazacubane</t>
+  </si>
+  <si>
+    <t>FreshAir</t>
+  </si>
+  <si>
+    <t>FumingButterscotch</t>
+  </si>
+  <si>
+    <t>Mass flow (kg/s)</t>
   </si>
 </sst>
 </file>
@@ -2088,7 +2004,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
@@ -2107,7 +2023,6 @@
     <xf numFmtId="166" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="167" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="5"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="8" applyAlignment="1"/>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="10" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="4"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="3"/>
@@ -2161,27 +2076,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="3" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="3" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="4" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="7" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="9" applyFont="1"/>
     <xf numFmtId="167" fontId="4" fillId="3" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="8" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="8"/>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="3" fillId="2" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="181" fontId="13" fillId="3" borderId="5" xfId="8" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2554,9 +2463,7 @@
   <dimension ref="A1:IQ80"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="3" width="19.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="21.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" style="2" customWidth="1"/>
+    <col min="1" max="5" width="22.85546875" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="2"/>
     <col min="7" max="7" width="14.28515625" style="2" customWidth="1"/>
     <col min="8" max="8" width="14.140625" style="2" customWidth="1"/>
@@ -2570,863 +2477,675 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="20.25" thickBot="1">
-      <c r="A1" s="85" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
+      <c r="A1" s="78" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+      <c r="O1"/>
+      <c r="P1"/>
+      <c r="Q1"/>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
+      <c r="X1"/>
+      <c r="Y1"/>
+      <c r="Z1"/>
+      <c r="AA1"/>
+      <c r="AB1"/>
     </row>
     <row r="2" spans="1:28" ht="16.5" thickTop="1">
-      <c r="A2" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="L2" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="M2" s="67">
-        <v>60</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>235</v>
-      </c>
+      <c r="A2" s="63" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="Q2"/>
+      <c r="R2"/>
+      <c r="S2"/>
+      <c r="T2"/>
+      <c r="U2"/>
+      <c r="V2"/>
+      <c r="W2"/>
+      <c r="X2"/>
+      <c r="Y2"/>
+      <c r="Z2"/>
+      <c r="AA2"/>
+      <c r="AB2"/>
     </row>
     <row r="3" spans="1:28">
-      <c r="A3" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="66"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="66"/>
-      <c r="L3" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="M3" s="67">
-        <v>800</v>
-      </c>
-      <c r="N3" s="68"/>
-      <c r="W3" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="A3" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="64"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="Q3"/>
+      <c r="R3"/>
+      <c r="S3"/>
+      <c r="T3"/>
+      <c r="U3"/>
+      <c r="V3"/>
+      <c r="W3"/>
+      <c r="X3"/>
+      <c r="Y3"/>
+      <c r="Z3"/>
+      <c r="AA3"/>
+      <c r="AB3"/>
     </row>
     <row r="4" spans="1:28">
-      <c r="A4" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="66"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="66"/>
-      <c r="E4" s="66"/>
-      <c r="L4" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="M4" s="67">
-        <v>380</v>
-      </c>
-      <c r="N4" s="68"/>
-      <c r="X4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="AA4" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="A4" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4"/>
+      <c r="AA4"/>
+      <c r="AB4"/>
     </row>
     <row r="5" spans="1:28" ht="18" thickBot="1">
-      <c r="A5" s="48" t="s">
-        <v>237</v>
-      </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="L5" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="M5" s="69">
-        <f>M4/M3</f>
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="N5" s="68"/>
-      <c r="V5" s="2">
-        <v>1</v>
-      </c>
-      <c r="W5" s="2">
-        <v>0</v>
-      </c>
-      <c r="X5" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="2">
-        <v>0</v>
-      </c>
+      <c r="A5" s="47" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5"/>
+      <c r="AA5"/>
+      <c r="AB5"/>
     </row>
     <row r="6" spans="1:28" ht="16.5" thickTop="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="5"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6"/>
+      <c r="AA6"/>
+      <c r="AB6"/>
+    </row>
+    <row r="7" spans="1:28">
+      <c r="A7" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" s="21">
+        <v>549</v>
+      </c>
+      <c r="C7" s="21">
+        <v>1</v>
+      </c>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="5"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+    </row>
+    <row r="8" spans="1:28" ht="18" thickBot="1">
+      <c r="A8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="L6" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="M6" s="70">
-        <f>M5^-0.75</f>
-        <v>1.7477519396551873</v>
-      </c>
-      <c r="N6" s="68" t="s">
-        <v>227</v>
-      </c>
-      <c r="V6" s="2">
-        <v>2</v>
-      </c>
-      <c r="W6" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="X6" s="2">
-        <v>0.23899999999999999</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>1.1086</v>
-      </c>
-      <c r="AA6" s="2">
-        <v>3.38</v>
-      </c>
-      <c r="AB6" s="5"/>
-    </row>
-    <row r="7" spans="1:28">
-      <c r="A7" s="71" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="22">
-        <v>183</v>
-      </c>
-      <c r="C7" s="22">
-        <v>0.1</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="L7" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="M7" s="72">
-        <f>60*M6</f>
-        <v>104.86511637931123</v>
-      </c>
-      <c r="N7" s="68"/>
-      <c r="V7" s="2">
+      <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="W7" s="2">
-        <v>2.9537</v>
-      </c>
-      <c r="X7" s="2">
-        <v>0.63800000000000001</v>
-      </c>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5">
-        <v>2.95208</v>
-      </c>
-      <c r="AA7" s="5">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" ht="18" thickBot="1">
-      <c r="A8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G8" s="73" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="73"/>
-      <c r="V8" s="5">
-        <v>4</v>
-      </c>
-      <c r="W8" s="5">
-        <v>5.5324099999999996</v>
-      </c>
-      <c r="X8" s="2">
-        <v>1.1950000000000001</v>
-      </c>
-      <c r="Z8" s="2">
-        <v>5.53024</v>
-      </c>
-      <c r="AA8" s="2">
-        <v>16.86</v>
-      </c>
+      <c r="D8" s="77" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="68"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8"/>
+      <c r="AA8"/>
+      <c r="AB8"/>
     </row>
     <row r="9" spans="1:28" ht="16.5" thickTop="1">
-      <c r="B9" s="19">
+      <c r="A9" s="1"/>
+      <c r="B9" s="18">
         <f>B7*9.80665</f>
-        <v>1794.6169499999999</v>
-      </c>
-      <c r="C9" s="70">
+        <v>5383.8508499999998</v>
+      </c>
+      <c r="C9" s="66">
         <f>IFERROR(C7*1000/B9,0)</f>
-        <v>5.5722197430487889E-2</v>
-      </c>
-      <c r="D9" s="19">
+        <v>0.18574065810162629</v>
+      </c>
+      <c r="D9" s="18">
         <f>C7*1000*B9</f>
-        <v>179461.69499999998</v>
-      </c>
-      <c r="E9" s="19">
+        <v>5383850.8499999996</v>
+      </c>
+      <c r="E9" s="18">
         <f>IFERROR(D9/C9,0)</f>
-        <v>3220649.9972273018</v>
-      </c>
-      <c r="G9" s="74">
+        <v>28985849.975045718</v>
+      </c>
+      <c r="G9" s="69">
         <f>SUM(B16:E16)</f>
-        <v>5.5722197430487889E-2</v>
-      </c>
-      <c r="H9" s="69" t="str">
+        <v>0.18574065810162632</v>
+      </c>
+      <c r="H9" s="65" t="str">
         <f>IF($C$9&gt;$G$9,"Input excesive",IF($C$9&lt;$G$9,"Output excessive","Equal"))</f>
         <v>Equal</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="N9" s="70">
-        <f>IFERROR(C7*1000/M9/B9,0)</f>
-        <v>3.7148131620325257E-2</v>
-      </c>
-      <c r="V9" s="2">
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9"/>
+      <c r="AA9"/>
+      <c r="AB9"/>
+    </row>
+    <row r="10" spans="1:28" s="64" customFormat="1" ht="16.5" customHeight="1">
+      <c r="A10" s="77"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="77"/>
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="J10"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10"/>
+      <c r="AA10"/>
+      <c r="AB10"/>
+    </row>
+    <row r="11" spans="1:28">
+      <c r="A11" s="77"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11"/>
+      <c r="AA11"/>
+      <c r="AB11"/>
+    </row>
+    <row r="12" spans="1:28" ht="16.5" thickBot="1">
+      <c r="A12" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="16">
+        <v>1</v>
+      </c>
+      <c r="C12" s="16">
         <v>5</v>
-      </c>
-      <c r="W9" s="2">
-        <v>8.86111</v>
-      </c>
-      <c r="X9" s="5">
-        <v>1.9139999999999999</v>
-      </c>
-      <c r="Z9" s="2">
-        <v>8.8562499999999993</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" s="66" customFormat="1">
-      <c r="L10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="2">
-        <v>1.2</v>
-      </c>
-      <c r="N10" s="70">
-        <f>IFERROR(C7*1000/M10/B9,0)</f>
-        <v>4.643516452540658E-2</v>
-      </c>
-      <c r="O10" s="2"/>
-      <c r="T10" s="5"/>
-      <c r="V10" s="2">
-        <v>6</v>
-      </c>
-      <c r="W10" s="2">
-        <v>12.9213</v>
-      </c>
-      <c r="X10" s="2">
-        <v>2.7909999999999999</v>
-      </c>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2">
-        <v>12.9236</v>
-      </c>
-      <c r="AA10" s="2">
-        <v>39.4</v>
-      </c>
-      <c r="AB10" s="2"/>
-    </row>
-    <row r="11" spans="1:28">
-      <c r="A11" s="66"/>
-      <c r="B11" s="66"/>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="L11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11" s="2">
-        <v>3.7</v>
-      </c>
-      <c r="N11" s="70">
-        <f>IFERROR(C7*1000/M11/B9,0)</f>
-        <v>1.5060053359591319E-2</v>
-      </c>
-      <c r="V11" s="2">
-        <v>7</v>
-      </c>
-      <c r="W11" s="2">
-        <v>17.708300000000001</v>
-      </c>
-      <c r="X11" s="2">
-        <v>3.8250000000000002</v>
-      </c>
-      <c r="Z11" s="2">
-        <v>17.712499999999999</v>
-      </c>
-      <c r="AA11" s="2">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" ht="16.5" thickBot="1">
-      <c r="A12" s="71" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="16">
-        <v>1</v>
-      </c>
-      <c r="C12" s="16">
-        <v>1</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
-      <c r="G12" s="75" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="75" t="s">
-        <v>91</v>
-      </c>
-      <c r="I12" s="75" t="s">
-        <v>92</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M12" s="2">
-        <v>1.33</v>
-      </c>
-      <c r="N12" s="70">
-        <f>IFERROR(C7*1000/M12/B9,0)</f>
-        <v>4.1896389045479612E-2</v>
-      </c>
-      <c r="V12" s="2">
-        <v>8</v>
-      </c>
-      <c r="W12" s="2">
-        <v>23.25</v>
-      </c>
-      <c r="X12" s="2">
-        <v>5.0220000000000002</v>
-      </c>
-      <c r="Z12" s="2">
-        <v>23.2559</v>
-      </c>
-      <c r="AA12" s="2">
-        <v>70.900000000000006</v>
-      </c>
+      <c r="G12" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="I12" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12"/>
+      <c r="AA12"/>
+      <c r="AB12"/>
     </row>
     <row r="13" spans="1:28">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="D13" s="13"/>
-      <c r="E13" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="G13" s="76">
+      <c r="E13" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="71">
         <f>IFERROR(E15/I13,"-")</f>
         <v>0</v>
       </c>
-      <c r="H13" s="77" t="str">
+      <c r="H13" s="72" t="str">
         <f>IFERROR(E12/G13,"-")</f>
         <v>-</v>
       </c>
-      <c r="I13" s="78">
-        <v>200</v>
-      </c>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
+      <c r="I13" s="73">
+        <v>18.8</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="Z13"/>
+      <c r="AA13"/>
+      <c r="AB13"/>
     </row>
     <row r="14" spans="1:28" ht="16.5" thickBot="1">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="8">
-        <f>IFERROR(VLOOKUP(B13,Database!$A$2:$B$59,2,0),"-")</f>
-        <v>0.79</v>
+        <f>IFERROR(VLOOKUP(B13,Database!$A$2:$B$61,2,0),"-")</f>
+        <v>6.24</v>
       </c>
       <c r="C14" s="8">
-        <f>IFERROR(VLOOKUP(C13,Database!$A$2:$B$59,2,0),"-")</f>
-        <v>1.141</v>
+        <f>IFERROR(VLOOKUP(C13,Database!$A$2:$B$61,2,0),"-")</f>
+        <v>0.35399999999999998</v>
       </c>
       <c r="D14" s="8" t="str">
-        <f>IFERROR(VLOOKUP(D13,Database!$A$2:$B$59,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(D13,Database!$A$2:$B$61,2,0),"-")</f>
         <v>-</v>
       </c>
       <c r="E14" s="9">
         <v>0</v>
       </c>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30" t="s">
-        <v>232</v>
-      </c>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14"/>
+      <c r="AA14"/>
+      <c r="AB14"/>
     </row>
     <row r="15" spans="1:28" ht="16.5" thickTop="1">
-      <c r="A15" s="71" t="s">
-        <v>73</v>
-      </c>
-      <c r="B15" s="84">
+      <c r="A15" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="76">
         <f>IFERROR(C9*B12/SUM(B17:D17),"-")</f>
-        <v>2.8856653252453592E-2</v>
-      </c>
-      <c r="C15" s="84">
+        <v>2.3188596517056966E-2</v>
+      </c>
+      <c r="C15" s="76">
         <f>IFERROR(C9*C12/SUM(B17:D17),"-")</f>
-        <v>2.8856653252453592E-2</v>
-      </c>
-      <c r="D15" s="74">
+        <v>0.11594298258528483</v>
+      </c>
+      <c r="D15" s="69">
         <f>IFERROR(C9*D12/SUM(B17:D17),"-")</f>
         <v>0</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E15" s="69">
         <f>IFERROR(C9*E12/SUM(B17:D17),0)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="83"/>
-      <c r="L15" s="30"/>
-      <c r="M15" s="21">
-        <v>2080</v>
-      </c>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="21">
-        <v>2100</v>
-      </c>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="30"/>
-      <c r="W15" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="Z15" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA15" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="G15" s="2">
+        <f>B15/C15</f>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15"/>
+      <c r="AA15"/>
+      <c r="AB15"/>
     </row>
     <row r="16" spans="1:28">
-      <c r="A16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="69">
+      <c r="A16" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B16" s="65">
         <f>IFERROR($B$14*$B$15,"-")</f>
-        <v>2.2796756069438338E-2</v>
-      </c>
-      <c r="C16" s="69">
+        <v>0.14469684226643548</v>
+      </c>
+      <c r="C16" s="65">
         <f t="shared" ref="C16:D16" si="0">IFERROR(C14*C15,"-")</f>
-        <v>3.2925441361049551E-2</v>
-      </c>
-      <c r="D16" s="69" t="str">
+        <v>4.1043815835190831E-2</v>
+      </c>
+      <c r="D16" s="65" t="str">
         <f t="shared" si="0"/>
         <v>-</v>
       </c>
-      <c r="E16" s="69">
+      <c r="E16" s="65">
         <f>E14*E15</f>
         <v>0</v>
       </c>
-      <c r="L16" s="30"/>
+      <c r="G16" s="2">
+        <f>B16/C16</f>
+        <v>3.5254237288135597</v>
+      </c>
+      <c r="L16" s="5"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
       <c r="P16" s="5"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="64">
-        <v>0.1</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA16" s="2" t="s">
-        <v>198</v>
-      </c>
+      <c r="Q16" s="5"/>
+      <c r="R16" s="5"/>
+      <c r="S16" s="5"/>
+      <c r="T16" s="5"/>
+      <c r="U16" s="5"/>
+      <c r="V16" s="5"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
     </row>
     <row r="17" spans="1:28">
-      <c r="A17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B17" s="69">
+      <c r="A17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="65">
         <f>IFERROR(B12*B14,"-")</f>
-        <v>0.79</v>
-      </c>
-      <c r="C17" s="69">
+        <v>6.24</v>
+      </c>
+      <c r="C17" s="65">
         <f t="shared" ref="C17:D17" si="1">IFERROR(C12*C14,"-")</f>
-        <v>1.141</v>
-      </c>
-      <c r="D17" s="69" t="str">
+        <v>1.77</v>
+      </c>
+      <c r="D17" s="65" t="str">
         <f t="shared" si="1"/>
         <v>-</v>
       </c>
-      <c r="E17" s="69"/>
-      <c r="L17" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="M17" s="79">
-        <f t="shared" ref="M17:M23" si="2">N17*$O$17</f>
-        <v>2080</v>
-      </c>
-      <c r="N17" s="30">
-        <v>800</v>
-      </c>
-      <c r="O17" s="20">
-        <f>($M$15/N17)</f>
-        <v>2.6</v>
-      </c>
-      <c r="P17" s="79">
-        <f t="shared" ref="P17:P23" si="3">$P$15*Q17</f>
-        <v>2100</v>
-      </c>
-      <c r="Q17" s="30">
-        <v>1</v>
-      </c>
-      <c r="R17" s="30">
-        <v>1E-4</v>
-      </c>
-      <c r="S17" s="18">
-        <f t="shared" ref="S17:S23" si="4">$S$16*R17</f>
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="V17" s="2">
-        <v>1</v>
-      </c>
-      <c r="W17" s="2">
-        <v>0</v>
-      </c>
-      <c r="X17" s="2">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="2">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="2">
-        <v>0</v>
-      </c>
+      <c r="E17" s="65"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="5"/>
+      <c r="R17" s="5"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="5"/>
+      <c r="U17" s="5"/>
+      <c r="V17" s="5"/>
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17"/>
+      <c r="Z17"/>
+      <c r="AA17"/>
+      <c r="AB17"/>
     </row>
     <row r="18" spans="1:28">
-      <c r="A18" s="5"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="L18" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="M18" s="79">
-        <f t="shared" si="2"/>
-        <v>657.80000000000007</v>
-      </c>
-      <c r="N18" s="30">
-        <v>253</v>
-      </c>
+      <c r="A18" s="77"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="64"/>
+      <c r="I18" s="64"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5"/>
       <c r="O18" s="5"/>
-      <c r="P18" s="79">
-        <f t="shared" si="3"/>
-        <v>4977</v>
-      </c>
-      <c r="Q18" s="30">
-        <v>2.37</v>
-      </c>
-      <c r="R18" s="30">
-        <v>1.4672099999999999E-4</v>
-      </c>
-      <c r="S18" s="18">
-        <f t="shared" si="4"/>
-        <v>1.46721E-5</v>
-      </c>
-      <c r="V18" s="2">
-        <v>2</v>
-      </c>
-      <c r="W18" s="2">
-        <v>1</v>
-      </c>
-      <c r="X18" s="80">
-        <v>0.61019999999999996</v>
-      </c>
-      <c r="Z18" s="2">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="80">
-        <v>4.3200000000000002E-2</v>
-      </c>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="5"/>
+      <c r="R18" s="5"/>
+      <c r="S18" s="5"/>
+      <c r="T18" s="5"/>
+      <c r="U18" s="5"/>
+      <c r="V18" s="5"/>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18"/>
+      <c r="AB18"/>
     </row>
     <row r="19" spans="1:28">
-      <c r="L19" s="30" t="s">
-        <v>121</v>
-      </c>
-      <c r="M19" s="79">
-        <f t="shared" si="2"/>
-        <v>1040</v>
-      </c>
-      <c r="N19" s="30">
-        <v>400</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="5"/>
       <c r="O19" s="5"/>
-      <c r="P19" s="79">
-        <f t="shared" si="3"/>
-        <v>3528</v>
-      </c>
-      <c r="Q19" s="30">
-        <v>1.68</v>
-      </c>
-      <c r="R19" s="30">
-        <v>2.9090700000000003E-4</v>
-      </c>
-      <c r="S19" s="18">
-        <f t="shared" si="4"/>
-        <v>2.9090700000000003E-5</v>
-      </c>
-      <c r="V19" s="2">
-        <v>3</v>
-      </c>
-      <c r="W19" s="2">
-        <v>2.95</v>
-      </c>
-      <c r="X19" s="80">
-        <f t="shared" ref="X19:X24" si="5">$X$18*W19</f>
-        <v>1.80009</v>
-      </c>
-      <c r="Z19" s="2">
-        <v>2.95</v>
-      </c>
-      <c r="AA19" s="80">
-        <f t="shared" ref="AA19:AA24" si="6">$AA$18*W19</f>
-        <v>0.12744000000000003</v>
-      </c>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="5"/>
+      <c r="R19" s="5"/>
+      <c r="S19" s="5"/>
+      <c r="T19" s="5"/>
+      <c r="U19" s="5"/>
+      <c r="V19" s="5"/>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19"/>
+      <c r="AB19"/>
     </row>
     <row r="20" spans="1:28" ht="18" thickBot="1">
       <c r="A20" s="6" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="L20" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="M20" s="79">
-        <f t="shared" si="2"/>
-        <v>657.80000000000007</v>
-      </c>
-      <c r="N20" s="30">
-        <v>253</v>
-      </c>
+      <c r="L20" s="5"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
       <c r="O20" s="5"/>
-      <c r="P20" s="79">
-        <f t="shared" si="3"/>
-        <v>4977</v>
-      </c>
-      <c r="Q20" s="30">
-        <v>2.37</v>
-      </c>
-      <c r="R20" s="30">
-        <v>1.53485E-4</v>
-      </c>
-      <c r="S20" s="18">
-        <f t="shared" si="4"/>
-        <v>1.5348500000000001E-5</v>
-      </c>
-      <c r="V20" s="5">
-        <v>4</v>
-      </c>
-      <c r="W20" s="38">
-        <v>5.53</v>
-      </c>
-      <c r="X20" s="80">
-        <f t="shared" si="5"/>
-        <v>3.374406</v>
-      </c>
-      <c r="Y20" s="38"/>
-      <c r="Z20" s="38"/>
-      <c r="AA20" s="80">
-        <f t="shared" si="6"/>
-        <v>0.23889600000000002</v>
-      </c>
-      <c r="AB20" s="38"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20"/>
+      <c r="X20"/>
+      <c r="Y20"/>
+      <c r="Z20"/>
+      <c r="AA20"/>
+      <c r="AB20"/>
     </row>
     <row r="21" spans="1:28" ht="16.5" thickTop="1">
       <c r="A21" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-      <c r="L21" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="M21" s="79">
-        <f t="shared" si="2"/>
-        <v>1575.6000000000001</v>
-      </c>
-      <c r="N21" s="30">
-        <v>606</v>
-      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
       <c r="O21" s="5"/>
-      <c r="P21" s="79">
-        <f t="shared" si="3"/>
-        <v>2583</v>
-      </c>
-      <c r="Q21" s="30">
-        <v>1.23</v>
-      </c>
-      <c r="R21" s="30">
-        <v>3.6680399999999998E-4</v>
-      </c>
-      <c r="S21" s="18">
-        <f t="shared" si="4"/>
-        <v>3.6680400000000002E-5</v>
-      </c>
-      <c r="V21" s="2">
-        <v>5</v>
-      </c>
-      <c r="W21" s="30">
-        <v>8.86</v>
-      </c>
-      <c r="X21" s="80">
-        <f t="shared" si="5"/>
-        <v>5.4063719999999993</v>
-      </c>
-      <c r="Y21" s="30"/>
-      <c r="Z21" s="30"/>
-      <c r="AA21" s="80">
-        <f t="shared" si="6"/>
-        <v>0.38275199999999998</v>
-      </c>
-      <c r="AB21" s="30"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21"/>
+      <c r="X21"/>
+      <c r="Y21"/>
+      <c r="Z21"/>
+      <c r="AA21"/>
+      <c r="AB21"/>
     </row>
     <row r="22" spans="1:28">
-      <c r="A22" s="71" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22" s="22">
-        <v>800</v>
-      </c>
-      <c r="C22" s="22">
-        <v>60</v>
+      <c r="A22" s="67" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="21">
+        <v>428</v>
+      </c>
+      <c r="C22" s="21">
+        <v>1</v>
       </c>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-      <c r="L22" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="M22" s="79">
-        <f t="shared" si="2"/>
-        <v>735.80000000000007</v>
-      </c>
-      <c r="N22" s="30">
-        <v>283</v>
-      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
       <c r="O22" s="5"/>
-      <c r="P22" s="79">
-        <f t="shared" si="3"/>
-        <v>4578</v>
-      </c>
-      <c r="Q22" s="30">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="R22" s="30">
-        <v>2.6534900000000001E-4</v>
-      </c>
-      <c r="S22" s="18">
-        <f t="shared" si="4"/>
-        <v>2.6534900000000002E-5</v>
-      </c>
-      <c r="V22" s="2">
-        <v>6</v>
-      </c>
-      <c r="W22" s="30">
-        <v>12.92</v>
-      </c>
-      <c r="X22" s="80">
-        <f t="shared" si="5"/>
-        <v>7.8837839999999995</v>
-      </c>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="80">
-        <f t="shared" si="6"/>
-        <v>0.55814399999999997</v>
-      </c>
-      <c r="AB22" s="30"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22"/>
+      <c r="X22"/>
+      <c r="Y22"/>
+      <c r="Z22"/>
+      <c r="AA22"/>
+      <c r="AB22"/>
     </row>
     <row r="23" spans="1:28" ht="18" thickBot="1">
       <c r="A23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>3</v>
@@ -3435,805 +3154,789 @@
         <v>22</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="G23" s="73" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="73"/>
-      <c r="L23" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="M23" s="79">
-        <f t="shared" si="2"/>
-        <v>962</v>
-      </c>
-      <c r="N23" s="30">
-        <v>370</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="G23" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="68"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
       <c r="O23" s="5"/>
-      <c r="P23" s="79">
-        <f t="shared" si="3"/>
-        <v>3738</v>
-      </c>
-      <c r="Q23" s="30">
-        <v>1.78</v>
-      </c>
-      <c r="R23" s="30">
-        <v>3.6195500000000001E-4</v>
-      </c>
-      <c r="S23" s="18">
-        <f t="shared" si="4"/>
-        <v>3.6195500000000003E-5</v>
-      </c>
-      <c r="V23" s="2">
-        <v>7</v>
-      </c>
-      <c r="W23" s="30">
-        <v>17.7</v>
-      </c>
-      <c r="X23" s="80">
-        <f t="shared" si="5"/>
-        <v>10.80054</v>
-      </c>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="80">
-        <f t="shared" si="6"/>
-        <v>0.76463999999999999</v>
-      </c>
-      <c r="AB23" s="30"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23"/>
+      <c r="X23"/>
+      <c r="Y23"/>
+      <c r="Z23"/>
+      <c r="AA23"/>
+      <c r="AB23"/>
     </row>
     <row r="24" spans="1:28" ht="16.5" thickTop="1">
-      <c r="B24" s="19">
+      <c r="B24" s="18">
         <f>B22*9.80665</f>
-        <v>7845.32</v>
-      </c>
-      <c r="C24" s="70">
+        <v>4197.2461999999996</v>
+      </c>
+      <c r="C24" s="66">
         <f>IFERROR(C22*1000/B24,0)</f>
-        <v>7.6478715973344622</v>
-      </c>
-      <c r="D24" s="19">
+        <v>0.2382514516303571</v>
+      </c>
+      <c r="D24" s="18">
         <f>C22*1000*B24</f>
-        <v>470719200</v>
-      </c>
-      <c r="E24" s="19">
+        <v>4197246.1999999993</v>
+      </c>
+      <c r="E24" s="18">
         <f>IFERROR(D24/C24,0)</f>
-        <v>61549045.902399994</v>
-      </c>
-      <c r="G24" s="74">
+        <v>17616875.663414434</v>
+      </c>
+      <c r="G24" s="69">
         <f>SUM(B31:E31)</f>
-        <v>7.6478715973344622</v>
-      </c>
-      <c r="H24" s="69" t="str">
+        <v>0.2382514516303571</v>
+      </c>
+      <c r="H24" s="65" t="str">
         <f>IF($C$9&gt;$G$9,"Input excesive",IF($C$9&lt;$G$9,"Output excessive","Equal"))</f>
         <v>Equal</v>
       </c>
-      <c r="V24" s="2">
-        <v>8</v>
-      </c>
-      <c r="W24" s="5">
-        <v>23.25</v>
-      </c>
-      <c r="X24" s="80">
-        <f t="shared" si="5"/>
-        <v>14.187149999999999</v>
-      </c>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5"/>
-      <c r="AA24" s="80">
-        <f t="shared" si="6"/>
-        <v>1.0044</v>
-      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24"/>
+      <c r="X24"/>
+      <c r="Y24"/>
+      <c r="Z24"/>
+      <c r="AA24"/>
+      <c r="AB24"/>
     </row>
     <row r="25" spans="1:28">
-      <c r="A25" s="66"/>
-      <c r="B25" s="66"/>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66"/>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66"/>
+      <c r="A25" s="64"/>
+      <c r="B25" s="64"/>
+      <c r="C25" s="64"/>
+      <c r="D25" s="64"/>
+      <c r="E25" s="64"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="64"/>
+      <c r="I25" s="64"/>
+      <c r="J25" s="64"/>
     </row>
     <row r="26" spans="1:28">
-      <c r="A26" s="66"/>
-      <c r="B26" s="66"/>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
+      <c r="A26" s="64"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
+      <c r="E26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="64"/>
+      <c r="I26" s="64"/>
+      <c r="J26" s="64"/>
     </row>
     <row r="27" spans="1:28" ht="16.5" thickBot="1">
-      <c r="A27" s="71" t="s">
-        <v>65</v>
+      <c r="A27" s="67" t="s">
+        <v>64</v>
       </c>
       <c r="B27" s="16">
         <v>1</v>
       </c>
       <c r="C27" s="16">
-        <v>0</v>
-      </c>
-      <c r="D27" s="82"/>
+        <v>4</v>
+      </c>
+      <c r="D27" s="75"/>
       <c r="E27" s="16">
-        <v>4.5380000000000003</v>
-      </c>
-      <c r="G27" s="75" t="s">
-        <v>88</v>
-      </c>
-      <c r="H27" s="75" t="s">
-        <v>91</v>
-      </c>
-      <c r="I27" s="75" t="s">
-        <v>92</v>
-      </c>
-      <c r="J27" s="66"/>
+        <v>5</v>
+      </c>
+      <c r="G27" s="70" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="70" t="s">
+        <v>89</v>
+      </c>
+      <c r="I27" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="J27" s="64"/>
     </row>
     <row r="28" spans="1:28">
       <c r="A28" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="D28" s="13"/>
-      <c r="E28" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="G28" s="76">
+      <c r="E28" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="71">
         <f>IFERROR(E30/I28,"-")</f>
-        <v>2.4492619131054192</v>
-      </c>
-      <c r="H28" s="77">
+        <v>8.8982934663714552E-3</v>
+      </c>
+      <c r="H28" s="72">
         <f>IFERROR(E27/G28,"-")</f>
-        <v>1.8528030733333334</v>
-      </c>
-      <c r="I28" s="78">
-        <v>200</v>
-      </c>
-      <c r="J28" s="66"/>
+        <v>561.90549557576003</v>
+      </c>
+      <c r="I28" s="73">
+        <v>18.8</v>
+      </c>
+      <c r="J28" s="64"/>
     </row>
     <row r="29" spans="1:28" ht="16.5" thickBot="1">
       <c r="A29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B29" s="8">
-        <f>IFERROR(VLOOKUP(B28,Database!$A$2:$B$59,2,0),"-")</f>
-        <v>7.0849999999999996E-2</v>
+        <f>IFERROR(VLOOKUP(B28,Database!$A$2:$B$61,2,0),"-")</f>
+        <v>5.7050000000000001</v>
       </c>
       <c r="C29" s="8">
-        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$59,2,0),"-")</f>
-        <v>5</v>
+        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$61,2,0),"-")</f>
+        <v>0.35399999999999998</v>
       </c>
       <c r="D29" s="8" t="str">
-        <f>IFERROR(VLOOKUP(D28,Database!$A$2:$B$59,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(D28,Database!$A$2:$B$61,2,0),"-")</f>
         <v>-</v>
       </c>
       <c r="E29" s="9">
         <v>0</v>
       </c>
-      <c r="J29" s="66"/>
+      <c r="J29" s="64"/>
     </row>
     <row r="30" spans="1:28" ht="16.5" thickTop="1">
-      <c r="A30" s="71" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="74">
+      <c r="A30" s="67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="69">
         <f>IFERROR(C24*B27/SUM(B32:D32),"-")</f>
-        <v>107.94455324395854</v>
-      </c>
-      <c r="C30" s="74">
+        <v>3.3457583433556676E-2</v>
+      </c>
+      <c r="C30" s="69">
         <f>IFERROR(C24*C27/SUM(B32:D32),"-")</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="74">
+        <v>0.1338303337342267</v>
+      </c>
+      <c r="D30" s="69">
         <f>IFERROR(C24*D27/SUM(B32:D32),"-")</f>
         <v>0</v>
       </c>
-      <c r="E30" s="74">
+      <c r="E30" s="69">
         <f>IFERROR(C24*E27/SUM(B32:D32),0)</f>
-        <v>489.85238262108385</v>
-      </c>
-      <c r="J30" s="66"/>
+        <v>0.16728791716778338</v>
+      </c>
+      <c r="G30" s="2">
+        <f>B30/C30</f>
+        <v>0.25</v>
+      </c>
+      <c r="J30" s="64"/>
     </row>
     <row r="31" spans="1:28">
-      <c r="A31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="69">
+      <c r="A31" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" s="65">
         <f>IFERROR($B$29*$B$30,"-")</f>
-        <v>7.6478715973344622</v>
-      </c>
-      <c r="C31" s="69">
-        <f t="shared" ref="C31:D31" si="7">IFERROR(C29*C30,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="69" t="str">
-        <f t="shared" si="7"/>
+        <v>0.19087551348844084</v>
+      </c>
+      <c r="C31" s="65">
+        <f t="shared" ref="C31:D31" si="2">IFERROR(C29*C30,"-")</f>
+        <v>4.7375938141916249E-2</v>
+      </c>
+      <c r="D31" s="65" t="str">
+        <f t="shared" si="2"/>
         <v>-</v>
       </c>
-      <c r="E31" s="69">
+      <c r="E31" s="65">
         <f>E29*E30</f>
         <v>0</v>
       </c>
-      <c r="J31" s="66"/>
+      <c r="G31" s="2">
+        <f>B31/C31</f>
+        <v>4.0289548022598876</v>
+      </c>
+      <c r="J31" s="64"/>
     </row>
     <row r="32" spans="1:28">
-      <c r="A32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="69">
+      <c r="A32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="65">
         <f>IFERROR(B27*B29,"-")</f>
-        <v>7.0849999999999996E-2</v>
-      </c>
-      <c r="C32" s="69">
-        <f t="shared" ref="C32:D32" si="8">IFERROR(C27*C29,"-")</f>
-        <v>0</v>
-      </c>
-      <c r="D32" s="69" t="str">
-        <f t="shared" si="8"/>
+        <v>5.7050000000000001</v>
+      </c>
+      <c r="C32" s="65">
+        <f t="shared" ref="C32:D32" si="3">IFERROR(C27*C29,"-")</f>
+        <v>1.4159999999999999</v>
+      </c>
+      <c r="D32" s="65" t="str">
+        <f t="shared" si="3"/>
         <v>-</v>
       </c>
-      <c r="E32" s="69"/>
-      <c r="H32" s="81"/>
-      <c r="J32" s="66"/>
+      <c r="E32" s="65"/>
+      <c r="H32" s="74"/>
+      <c r="J32" s="64"/>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="5"/>
-      <c r="G33" s="66"/>
-      <c r="H33" s="66"/>
-      <c r="I33" s="66"/>
-      <c r="J33" s="66"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
     </row>
     <row r="34" spans="1:10">
       <c r="D34"/>
-      <c r="J34" s="66"/>
+      <c r="J34" s="64"/>
     </row>
     <row r="35" spans="1:10">
       <c r="D35"/>
-      <c r="J35" s="66"/>
+      <c r="J35" s="64"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="J36" s="66"/>
+      <c r="J36" s="64"/>
     </row>
     <row r="37" spans="1:10">
-      <c r="A37" s="66"/>
-      <c r="B37" s="66"/>
-      <c r="C37" s="66"/>
-      <c r="D37" s="66"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="66"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="66"/>
-      <c r="J37" s="66"/>
+      <c r="A37" s="64"/>
+      <c r="B37" s="64"/>
+      <c r="C37" s="64"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="64"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="64"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="66"/>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66"/>
-      <c r="J38" s="66"/>
+      <c r="A38" s="64"/>
+      <c r="B38" s="64"/>
+      <c r="C38" s="64"/>
+      <c r="D38" s="64"/>
+      <c r="E38" s="64"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="64"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="66"/>
-      <c r="B39" s="66"/>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="66"/>
-      <c r="H39" s="66"/>
-      <c r="I39" s="66"/>
-      <c r="J39" s="66"/>
+      <c r="A39" s="64"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="64"/>
+      <c r="D39" s="64"/>
+      <c r="E39" s="64"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="64"/>
+      <c r="J39" s="64"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="66"/>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="66"/>
-      <c r="J40" s="66"/>
+      <c r="A40" s="64"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
+      <c r="E40" s="64"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="64"/>
+      <c r="J40" s="64"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="66"/>
-      <c r="B41" s="66"/>
-      <c r="C41" s="66"/>
-      <c r="D41" s="66"/>
-      <c r="E41" s="66"/>
-      <c r="F41" s="66"/>
-      <c r="G41" s="66"/>
-      <c r="H41" s="66"/>
-      <c r="I41" s="66"/>
-      <c r="J41" s="66"/>
+      <c r="A41" s="64"/>
+      <c r="B41" s="64"/>
+      <c r="C41" s="64"/>
+      <c r="D41" s="64"/>
+      <c r="E41" s="64"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="64"/>
+      <c r="J41" s="64"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="66"/>
-      <c r="B42" s="66"/>
-      <c r="C42" s="66"/>
-      <c r="D42" s="66"/>
-      <c r="E42" s="66"/>
-      <c r="F42" s="66"/>
-      <c r="G42" s="66"/>
-      <c r="H42" s="66"/>
-      <c r="I42" s="66"/>
-      <c r="J42" s="66"/>
+      <c r="A42" s="64"/>
+      <c r="B42" s="64"/>
+      <c r="C42" s="64"/>
+      <c r="D42" s="64"/>
+      <c r="E42" s="64"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="64"/>
+      <c r="J42" s="64"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="66"/>
-      <c r="B43" s="66"/>
-      <c r="C43" s="66"/>
-      <c r="D43" s="66"/>
-      <c r="E43" s="66"/>
-      <c r="F43" s="66"/>
-      <c r="G43" s="66"/>
-      <c r="H43" s="66"/>
-      <c r="I43" s="66"/>
-      <c r="J43" s="66"/>
+      <c r="A43" s="64"/>
+      <c r="B43" s="64"/>
+      <c r="C43" s="64"/>
+      <c r="D43" s="64"/>
+      <c r="E43" s="64"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="64"/>
+      <c r="J43" s="64"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="66"/>
-      <c r="B44" s="66"/>
-      <c r="C44" s="66"/>
-      <c r="D44" s="66"/>
-      <c r="E44" s="66"/>
-      <c r="F44" s="66"/>
-      <c r="G44" s="66"/>
-      <c r="H44" s="66"/>
-      <c r="I44" s="66"/>
-      <c r="J44" s="66"/>
+      <c r="A44" s="64"/>
+      <c r="B44" s="64"/>
+      <c r="C44" s="64"/>
+      <c r="D44" s="64"/>
+      <c r="E44" s="64"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="64"/>
+      <c r="J44" s="64"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="66"/>
-      <c r="B45" s="66"/>
-      <c r="C45" s="66"/>
-      <c r="D45" s="66"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="66"/>
-      <c r="G45" s="66"/>
-      <c r="H45" s="66"/>
-      <c r="I45" s="66"/>
-      <c r="J45" s="66"/>
+      <c r="A45" s="64"/>
+      <c r="B45" s="64"/>
+      <c r="C45" s="64"/>
+      <c r="D45" s="64"/>
+      <c r="E45" s="64"/>
+      <c r="F45" s="64"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="64"/>
+      <c r="J45" s="64"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="66"/>
-      <c r="B46" s="66"/>
-      <c r="C46" s="66"/>
-      <c r="D46" s="66"/>
-      <c r="E46" s="66"/>
-      <c r="F46" s="66"/>
-      <c r="G46" s="66"/>
-      <c r="H46" s="66"/>
-      <c r="I46" s="66"/>
-      <c r="J46" s="66"/>
+      <c r="A46" s="64"/>
+      <c r="B46" s="64"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="64"/>
+      <c r="J46" s="64"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="A47" s="66"/>
-      <c r="B47" s="66"/>
-      <c r="C47" s="66"/>
-      <c r="D47" s="66"/>
-      <c r="E47" s="66"/>
-      <c r="F47" s="66"/>
-      <c r="G47" s="66"/>
-      <c r="H47" s="66"/>
-      <c r="I47" s="66"/>
-      <c r="J47" s="66"/>
+      <c r="A47" s="64"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="64"/>
+      <c r="F47" s="64"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="64"/>
+      <c r="J47" s="64"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="66"/>
-      <c r="B48" s="66"/>
-      <c r="C48" s="66"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
-      <c r="G48" s="66"/>
-      <c r="H48" s="66"/>
-      <c r="I48" s="66"/>
-      <c r="J48" s="66"/>
+      <c r="A48" s="64"/>
+      <c r="B48" s="64"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="64"/>
+      <c r="E48" s="64"/>
+      <c r="F48" s="64"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="64"/>
+      <c r="J48" s="64"/>
     </row>
     <row r="49" spans="1:10">
-      <c r="A49" s="66"/>
-      <c r="B49" s="66"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="66"/>
-      <c r="E49" s="66"/>
-      <c r="F49" s="66"/>
-      <c r="G49" s="66"/>
-      <c r="H49" s="66"/>
-      <c r="I49" s="66"/>
-      <c r="J49" s="66"/>
+      <c r="A49" s="64"/>
+      <c r="B49" s="64"/>
+      <c r="C49" s="64"/>
+      <c r="D49" s="64"/>
+      <c r="E49" s="64"/>
+      <c r="F49" s="64"/>
+      <c r="G49" s="64"/>
+      <c r="H49" s="64"/>
+      <c r="I49" s="64"/>
+      <c r="J49" s="64"/>
     </row>
     <row r="50" spans="1:10">
-      <c r="A50" s="66"/>
-      <c r="B50" s="66"/>
-      <c r="C50" s="66"/>
-      <c r="D50" s="66"/>
-      <c r="E50" s="66"/>
-      <c r="F50" s="66"/>
-      <c r="G50" s="66"/>
-      <c r="H50" s="66"/>
-      <c r="I50" s="66"/>
-      <c r="J50" s="66"/>
+      <c r="A50" s="64"/>
+      <c r="B50" s="64"/>
+      <c r="C50" s="64"/>
+      <c r="D50" s="64"/>
+      <c r="E50" s="64"/>
+      <c r="F50" s="64"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="64"/>
+      <c r="I50" s="64"/>
+      <c r="J50" s="64"/>
     </row>
     <row r="51" spans="1:10">
-      <c r="A51" s="66"/>
-      <c r="B51" s="66"/>
-      <c r="C51" s="66"/>
-      <c r="D51" s="66"/>
-      <c r="E51" s="66"/>
-      <c r="F51" s="66"/>
-      <c r="G51" s="66"/>
-      <c r="H51" s="66"/>
-      <c r="I51" s="66"/>
-      <c r="J51" s="66"/>
+      <c r="A51" s="64"/>
+      <c r="B51" s="64"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="64"/>
+      <c r="F51" s="64"/>
+      <c r="G51" s="64"/>
+      <c r="H51" s="64"/>
+      <c r="I51" s="64"/>
+      <c r="J51" s="64"/>
     </row>
     <row r="52" spans="1:10">
-      <c r="A52" s="66"/>
-      <c r="B52" s="66"/>
-      <c r="C52" s="66"/>
-      <c r="D52" s="66"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="66"/>
-      <c r="G52" s="66"/>
-      <c r="H52" s="66"/>
-      <c r="I52" s="66"/>
-      <c r="J52" s="66"/>
+      <c r="A52" s="64"/>
+      <c r="B52" s="64"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="64"/>
+      <c r="E52" s="64"/>
+      <c r="F52" s="64"/>
+      <c r="G52" s="64"/>
+      <c r="H52" s="64"/>
+      <c r="I52" s="64"/>
+      <c r="J52" s="64"/>
     </row>
     <row r="53" spans="1:10">
-      <c r="A53" s="66"/>
-      <c r="B53" s="66"/>
-      <c r="C53" s="66"/>
-      <c r="D53" s="66"/>
-      <c r="E53" s="66"/>
-      <c r="F53" s="66"/>
-      <c r="G53" s="66"/>
-      <c r="H53" s="66"/>
-      <c r="I53" s="66"/>
-      <c r="J53" s="66"/>
+      <c r="A53" s="64"/>
+      <c r="B53" s="64"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="64"/>
+      <c r="E53" s="64"/>
+      <c r="F53" s="64"/>
+      <c r="G53" s="64"/>
+      <c r="H53" s="64"/>
+      <c r="I53" s="64"/>
+      <c r="J53" s="64"/>
     </row>
     <row r="54" spans="1:10">
-      <c r="A54" s="66"/>
-      <c r="B54" s="66"/>
-      <c r="C54" s="66"/>
-      <c r="D54" s="66"/>
-      <c r="E54" s="66"/>
-      <c r="F54" s="66"/>
-      <c r="G54" s="66"/>
-      <c r="H54" s="66"/>
-      <c r="I54" s="66"/>
-      <c r="J54" s="66"/>
+      <c r="A54" s="64"/>
+      <c r="B54" s="64"/>
+      <c r="C54" s="64"/>
+      <c r="D54" s="64"/>
+      <c r="E54" s="64"/>
+      <c r="F54" s="64"/>
+      <c r="G54" s="64"/>
+      <c r="H54" s="64"/>
+      <c r="I54" s="64"/>
+      <c r="J54" s="64"/>
     </row>
     <row r="55" spans="1:10">
-      <c r="A55" s="66"/>
-      <c r="B55" s="66"/>
-      <c r="C55" s="66"/>
-      <c r="D55" s="66"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="66"/>
-      <c r="G55" s="66"/>
-      <c r="H55" s="66"/>
-      <c r="I55" s="66"/>
-      <c r="J55" s="66"/>
+      <c r="A55" s="64"/>
+      <c r="B55" s="64"/>
+      <c r="C55" s="64"/>
+      <c r="D55" s="64"/>
+      <c r="E55" s="64"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="64"/>
+      <c r="I55" s="64"/>
+      <c r="J55" s="64"/>
     </row>
     <row r="56" spans="1:10">
-      <c r="A56" s="66"/>
-      <c r="B56" s="66"/>
-      <c r="C56" s="66"/>
-      <c r="D56" s="66"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="66"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="66"/>
-      <c r="I56" s="66"/>
-      <c r="J56" s="66"/>
+      <c r="A56" s="64"/>
+      <c r="B56" s="64"/>
+      <c r="C56" s="64"/>
+      <c r="D56" s="64"/>
+      <c r="E56" s="64"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="64"/>
+      <c r="I56" s="64"/>
+      <c r="J56" s="64"/>
     </row>
     <row r="57" spans="1:10">
-      <c r="A57" s="66"/>
-      <c r="B57" s="66"/>
-      <c r="C57" s="66"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="66"/>
-      <c r="G57" s="66"/>
-      <c r="H57" s="66"/>
-      <c r="I57" s="66"/>
-      <c r="J57" s="66"/>
+      <c r="A57" s="64"/>
+      <c r="B57" s="64"/>
+      <c r="C57" s="64"/>
+      <c r="D57" s="64"/>
+      <c r="E57" s="64"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
+      <c r="H57" s="64"/>
+      <c r="I57" s="64"/>
+      <c r="J57" s="64"/>
     </row>
     <row r="58" spans="1:10">
-      <c r="A58" s="66"/>
-      <c r="B58" s="66"/>
-      <c r="C58" s="66"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="66"/>
-      <c r="F58" s="66"/>
-      <c r="G58" s="66"/>
-      <c r="H58" s="66"/>
-      <c r="I58" s="66"/>
-      <c r="J58" s="66"/>
+      <c r="A58" s="64"/>
+      <c r="B58" s="64"/>
+      <c r="C58" s="64"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="64"/>
+      <c r="G58" s="64"/>
+      <c r="H58" s="64"/>
+      <c r="I58" s="64"/>
+      <c r="J58" s="64"/>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="66"/>
-      <c r="B59" s="66"/>
-      <c r="C59" s="66"/>
-      <c r="D59" s="66"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="66"/>
-      <c r="H59" s="66"/>
-      <c r="I59" s="66"/>
-      <c r="J59" s="66"/>
+      <c r="A59" s="64"/>
+      <c r="B59" s="64"/>
+      <c r="C59" s="64"/>
+      <c r="D59" s="64"/>
+      <c r="E59" s="64"/>
+      <c r="F59" s="64"/>
+      <c r="G59" s="64"/>
+      <c r="H59" s="64"/>
+      <c r="I59" s="64"/>
+      <c r="J59" s="64"/>
     </row>
     <row r="60" spans="1:10">
-      <c r="A60" s="66"/>
-      <c r="B60" s="66"/>
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="66"/>
-      <c r="I60" s="66"/>
-      <c r="J60" s="66"/>
+      <c r="A60" s="64"/>
+      <c r="B60" s="64"/>
+      <c r="C60" s="64"/>
+      <c r="D60" s="64"/>
+      <c r="E60" s="64"/>
+      <c r="F60" s="64"/>
+      <c r="G60" s="64"/>
+      <c r="H60" s="64"/>
+      <c r="I60" s="64"/>
+      <c r="J60" s="64"/>
     </row>
     <row r="61" spans="1:10">
-      <c r="A61" s="66"/>
-      <c r="B61" s="66"/>
-      <c r="C61" s="66"/>
-      <c r="D61" s="66"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="66"/>
-      <c r="G61" s="66"/>
-      <c r="H61" s="66"/>
-      <c r="I61" s="66"/>
-      <c r="J61" s="66"/>
+      <c r="A61" s="64"/>
+      <c r="B61" s="64"/>
+      <c r="C61" s="64"/>
+      <c r="D61" s="64"/>
+      <c r="E61" s="64"/>
+      <c r="F61" s="64"/>
+      <c r="G61" s="64"/>
+      <c r="H61" s="64"/>
+      <c r="I61" s="64"/>
+      <c r="J61" s="64"/>
     </row>
     <row r="62" spans="1:10">
-      <c r="A62" s="66"/>
-      <c r="B62" s="66"/>
-      <c r="C62" s="66"/>
-      <c r="D62" s="66"/>
-      <c r="E62" s="66"/>
-      <c r="F62" s="66"/>
-      <c r="G62" s="66"/>
-      <c r="H62" s="66"/>
-      <c r="I62" s="66"/>
-      <c r="J62" s="66"/>
+      <c r="A62" s="64"/>
+      <c r="B62" s="64"/>
+      <c r="C62" s="64"/>
+      <c r="D62" s="64"/>
+      <c r="E62" s="64"/>
+      <c r="F62" s="64"/>
+      <c r="G62" s="64"/>
+      <c r="H62" s="64"/>
+      <c r="I62" s="64"/>
+      <c r="J62" s="64"/>
     </row>
     <row r="63" spans="1:10">
-      <c r="A63" s="66"/>
-      <c r="B63" s="66"/>
-      <c r="C63" s="66"/>
-      <c r="D63" s="66"/>
-      <c r="E63" s="66"/>
-      <c r="F63" s="66"/>
-      <c r="G63" s="66"/>
-      <c r="H63" s="66"/>
-      <c r="I63" s="66"/>
-      <c r="J63" s="66"/>
+      <c r="A63" s="64"/>
+      <c r="B63" s="64"/>
+      <c r="C63" s="64"/>
+      <c r="D63" s="64"/>
+      <c r="E63" s="64"/>
+      <c r="F63" s="64"/>
+      <c r="G63" s="64"/>
+      <c r="H63" s="64"/>
+      <c r="I63" s="64"/>
+      <c r="J63" s="64"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="66"/>
-      <c r="B64" s="66"/>
-      <c r="C64" s="66"/>
-      <c r="D64" s="66"/>
-      <c r="E64" s="66"/>
-      <c r="F64" s="66"/>
-      <c r="G64" s="66"/>
-      <c r="H64" s="66"/>
-      <c r="I64" s="66"/>
-      <c r="J64" s="66"/>
+      <c r="A64" s="64"/>
+      <c r="B64" s="64"/>
+      <c r="C64" s="64"/>
+      <c r="D64" s="64"/>
+      <c r="E64" s="64"/>
+      <c r="F64" s="64"/>
+      <c r="G64" s="64"/>
+      <c r="H64" s="64"/>
+      <c r="I64" s="64"/>
+      <c r="J64" s="64"/>
     </row>
     <row r="65" spans="1:10">
-      <c r="A65" s="66"/>
-      <c r="B65" s="66"/>
-      <c r="C65" s="66"/>
-      <c r="D65" s="66"/>
-      <c r="E65" s="66"/>
-      <c r="F65" s="66"/>
-      <c r="G65" s="66"/>
-      <c r="H65" s="66"/>
-      <c r="I65" s="66"/>
-      <c r="J65" s="66"/>
+      <c r="A65" s="64"/>
+      <c r="B65" s="64"/>
+      <c r="C65" s="64"/>
+      <c r="D65" s="64"/>
+      <c r="E65" s="64"/>
+      <c r="F65" s="64"/>
+      <c r="G65" s="64"/>
+      <c r="H65" s="64"/>
+      <c r="I65" s="64"/>
+      <c r="J65" s="64"/>
     </row>
     <row r="66" spans="1:10">
-      <c r="A66" s="66"/>
-      <c r="B66" s="66"/>
-      <c r="C66" s="66"/>
-      <c r="D66" s="66"/>
-      <c r="E66" s="66"/>
-      <c r="F66" s="66"/>
-      <c r="G66" s="66"/>
-      <c r="H66" s="66"/>
-      <c r="I66" s="66"/>
-      <c r="J66" s="66"/>
+      <c r="A66" s="64"/>
+      <c r="B66" s="64"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
+      <c r="E66" s="64"/>
+      <c r="F66" s="64"/>
+      <c r="G66" s="64"/>
+      <c r="H66" s="64"/>
+      <c r="I66" s="64"/>
+      <c r="J66" s="64"/>
     </row>
     <row r="67" spans="1:10">
-      <c r="A67" s="66"/>
-      <c r="B67" s="66"/>
-      <c r="C67" s="66"/>
-      <c r="D67" s="66"/>
-      <c r="E67" s="66"/>
-      <c r="F67" s="66"/>
-      <c r="G67" s="66"/>
-      <c r="H67" s="66"/>
-      <c r="I67" s="66"/>
-      <c r="J67" s="66"/>
+      <c r="A67" s="64"/>
+      <c r="B67" s="64"/>
+      <c r="C67" s="64"/>
+      <c r="D67" s="64"/>
+      <c r="E67" s="64"/>
+      <c r="F67" s="64"/>
+      <c r="G67" s="64"/>
+      <c r="H67" s="64"/>
+      <c r="I67" s="64"/>
+      <c r="J67" s="64"/>
     </row>
     <row r="68" spans="1:10">
-      <c r="A68" s="66"/>
-      <c r="B68" s="66"/>
-      <c r="C68" s="66"/>
-      <c r="D68" s="66"/>
-      <c r="E68" s="66"/>
-      <c r="F68" s="66"/>
-      <c r="G68" s="66"/>
-      <c r="H68" s="66"/>
-      <c r="I68" s="66"/>
-      <c r="J68" s="66"/>
+      <c r="A68" s="64"/>
+      <c r="B68" s="64"/>
+      <c r="C68" s="64"/>
+      <c r="D68" s="64"/>
+      <c r="E68" s="64"/>
+      <c r="F68" s="64"/>
+      <c r="G68" s="64"/>
+      <c r="H68" s="64"/>
+      <c r="I68" s="64"/>
+      <c r="J68" s="64"/>
     </row>
     <row r="69" spans="1:10">
-      <c r="A69" s="66"/>
-      <c r="B69" s="66"/>
-      <c r="C69" s="66"/>
-      <c r="D69" s="66"/>
-      <c r="E69" s="66"/>
-      <c r="F69" s="66"/>
-      <c r="G69" s="66"/>
-      <c r="H69" s="66"/>
-      <c r="I69" s="66"/>
-      <c r="J69" s="66"/>
+      <c r="A69" s="64"/>
+      <c r="B69" s="64"/>
+      <c r="C69" s="64"/>
+      <c r="D69" s="64"/>
+      <c r="E69" s="64"/>
+      <c r="F69" s="64"/>
+      <c r="G69" s="64"/>
+      <c r="H69" s="64"/>
+      <c r="I69" s="64"/>
+      <c r="J69" s="64"/>
     </row>
     <row r="70" spans="1:10">
-      <c r="A70" s="66"/>
-      <c r="B70" s="66"/>
-      <c r="C70" s="66"/>
-      <c r="D70" s="66"/>
-      <c r="E70" s="66"/>
-      <c r="F70" s="66"/>
-      <c r="G70" s="66"/>
-      <c r="H70" s="66"/>
-      <c r="I70" s="66"/>
-      <c r="J70" s="66"/>
+      <c r="A70" s="64"/>
+      <c r="B70" s="64"/>
+      <c r="C70" s="64"/>
+      <c r="D70" s="64"/>
+      <c r="E70" s="64"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="64"/>
+      <c r="I70" s="64"/>
+      <c r="J70" s="64"/>
     </row>
     <row r="71" spans="1:10">
-      <c r="A71" s="66"/>
-      <c r="B71" s="66"/>
-      <c r="C71" s="66"/>
-      <c r="D71" s="66"/>
-      <c r="E71" s="66"/>
-      <c r="F71" s="66"/>
-      <c r="G71" s="66"/>
-      <c r="H71" s="66"/>
-      <c r="I71" s="66"/>
-      <c r="J71" s="66"/>
+      <c r="A71" s="64"/>
+      <c r="B71" s="64"/>
+      <c r="C71" s="64"/>
+      <c r="D71" s="64"/>
+      <c r="E71" s="64"/>
+      <c r="F71" s="64"/>
+      <c r="G71" s="64"/>
+      <c r="H71" s="64"/>
+      <c r="I71" s="64"/>
+      <c r="J71" s="64"/>
     </row>
     <row r="72" spans="1:10">
-      <c r="A72" s="66"/>
-      <c r="B72" s="66"/>
-      <c r="C72" s="66"/>
-      <c r="D72" s="66"/>
-      <c r="E72" s="66"/>
-      <c r="F72" s="66"/>
-      <c r="G72" s="66"/>
-      <c r="H72" s="66"/>
-      <c r="I72" s="66"/>
-      <c r="J72" s="66"/>
+      <c r="A72" s="64"/>
+      <c r="B72" s="64"/>
+      <c r="C72" s="64"/>
+      <c r="D72" s="64"/>
+      <c r="E72" s="64"/>
+      <c r="F72" s="64"/>
+      <c r="G72" s="64"/>
+      <c r="H72" s="64"/>
+      <c r="I72" s="64"/>
+      <c r="J72" s="64"/>
     </row>
     <row r="73" spans="1:10">
-      <c r="A73" s="66"/>
-      <c r="B73" s="66"/>
-      <c r="C73" s="66"/>
-      <c r="D73" s="66"/>
-      <c r="E73" s="66"/>
-      <c r="F73" s="66"/>
-      <c r="G73" s="66"/>
-      <c r="H73" s="66"/>
-      <c r="I73" s="66"/>
-      <c r="J73" s="66"/>
+      <c r="A73" s="64"/>
+      <c r="B73" s="64"/>
+      <c r="C73" s="64"/>
+      <c r="D73" s="64"/>
+      <c r="E73" s="64"/>
+      <c r="F73" s="64"/>
+      <c r="G73" s="64"/>
+      <c r="H73" s="64"/>
+      <c r="I73" s="64"/>
+      <c r="J73" s="64"/>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="66"/>
-      <c r="B74" s="66"/>
-      <c r="C74" s="66"/>
-      <c r="D74" s="66"/>
-      <c r="E74" s="66"/>
-      <c r="F74" s="66"/>
-      <c r="G74" s="66"/>
-      <c r="H74" s="66"/>
-      <c r="I74" s="66"/>
-      <c r="J74" s="66"/>
+      <c r="A74" s="64"/>
+      <c r="B74" s="64"/>
+      <c r="C74" s="64"/>
+      <c r="D74" s="64"/>
+      <c r="E74" s="64"/>
+      <c r="F74" s="64"/>
+      <c r="G74" s="64"/>
+      <c r="H74" s="64"/>
+      <c r="I74" s="64"/>
+      <c r="J74" s="64"/>
     </row>
     <row r="75" spans="1:10">
-      <c r="A75" s="66"/>
-      <c r="B75" s="66"/>
-      <c r="C75" s="66"/>
-      <c r="D75" s="66"/>
-      <c r="E75" s="66"/>
-      <c r="F75" s="66"/>
-      <c r="G75" s="66"/>
-      <c r="H75" s="66"/>
-      <c r="I75" s="66"/>
-      <c r="J75" s="66"/>
+      <c r="A75" s="64"/>
+      <c r="B75" s="64"/>
+      <c r="C75" s="64"/>
+      <c r="D75" s="64"/>
+      <c r="E75" s="64"/>
+      <c r="F75" s="64"/>
+      <c r="G75" s="64"/>
+      <c r="H75" s="64"/>
+      <c r="I75" s="64"/>
+      <c r="J75" s="64"/>
     </row>
     <row r="76" spans="1:10">
-      <c r="A76" s="66"/>
-      <c r="B76" s="66"/>
-      <c r="C76" s="66"/>
-      <c r="D76" s="66"/>
-      <c r="E76" s="66"/>
-      <c r="F76" s="66"/>
-      <c r="G76" s="66"/>
-      <c r="H76" s="66"/>
-      <c r="I76" s="66"/>
-      <c r="J76" s="66"/>
+      <c r="A76" s="64"/>
+      <c r="B76" s="64"/>
+      <c r="C76" s="64"/>
+      <c r="D76" s="64"/>
+      <c r="E76" s="64"/>
+      <c r="F76" s="64"/>
+      <c r="G76" s="64"/>
+      <c r="H76" s="64"/>
+      <c r="I76" s="64"/>
+      <c r="J76" s="64"/>
     </row>
     <row r="77" spans="1:10">
-      <c r="A77" s="66"/>
-      <c r="B77" s="66"/>
-      <c r="C77" s="66"/>
-      <c r="D77" s="66"/>
-      <c r="E77" s="66"/>
-      <c r="F77" s="66"/>
-      <c r="G77" s="66"/>
-      <c r="H77" s="66"/>
-      <c r="I77" s="66"/>
-      <c r="J77" s="66"/>
+      <c r="A77" s="64"/>
+      <c r="B77" s="64"/>
+      <c r="C77" s="64"/>
+      <c r="D77" s="64"/>
+      <c r="E77" s="64"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="64"/>
+      <c r="H77" s="64"/>
+      <c r="I77" s="64"/>
+      <c r="J77" s="64"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="66"/>
-      <c r="B78" s="66"/>
-      <c r="C78" s="66"/>
-      <c r="D78" s="66"/>
-      <c r="E78" s="66"/>
-      <c r="F78" s="66"/>
-      <c r="G78" s="66"/>
-      <c r="H78" s="66"/>
-      <c r="I78" s="66"/>
-      <c r="J78" s="66"/>
+      <c r="A78" s="64"/>
+      <c r="B78" s="64"/>
+      <c r="C78" s="64"/>
+      <c r="D78" s="64"/>
+      <c r="E78" s="64"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="64"/>
+      <c r="H78" s="64"/>
+      <c r="I78" s="64"/>
+      <c r="J78" s="64"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="66"/>
-      <c r="B79" s="66"/>
-      <c r="C79" s="66"/>
-      <c r="D79" s="66"/>
-      <c r="E79" s="66"/>
-      <c r="F79" s="66"/>
-      <c r="G79" s="66"/>
-      <c r="H79" s="66"/>
-      <c r="I79" s="66"/>
-      <c r="J79" s="66"/>
+      <c r="A79" s="64"/>
+      <c r="B79" s="64"/>
+      <c r="C79" s="64"/>
+      <c r="D79" s="64"/>
+      <c r="E79" s="64"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="64"/>
+      <c r="H79" s="64"/>
+      <c r="I79" s="64"/>
+      <c r="J79" s="64"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="66"/>
-      <c r="B80" s="66"/>
-      <c r="C80" s="66"/>
-      <c r="D80" s="66"/>
-      <c r="E80" s="66"/>
-      <c r="F80" s="66"/>
-      <c r="G80" s="66"/>
-      <c r="H80" s="66"/>
-      <c r="I80" s="66"/>
-      <c r="J80" s="66"/>
+      <c r="A80" s="64"/>
+      <c r="B80" s="64"/>
+      <c r="C80" s="64"/>
+      <c r="D80" s="64"/>
+      <c r="E80" s="64"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="64"/>
+      <c r="H80" s="64"/>
+      <c r="I80" s="64"/>
+      <c r="J80" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4251,13 +3954,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$59</xm:f>
+            <xm:f>Database!$A$2:$A$61</xm:f>
           </x14:formula1>
           <xm:sqref>B13:D13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$59</xm:f>
+            <xm:f>Database!$A$2:$A$61</xm:f>
           </x14:formula1>
           <xm:sqref>B28:D28</xm:sqref>
         </x14:dataValidation>
@@ -4289,196 +3992,196 @@
         <v>23</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>23</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>192</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" thickTop="1">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="31" t="s">
-        <v>116</v>
-      </c>
-      <c r="H2" s="31" t="s">
-        <v>117</v>
-      </c>
-      <c r="I2" s="31">
-        <v>1</v>
-      </c>
-      <c r="J2" s="32">
+      <c r="G2" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="H2" s="30" t="s">
+        <v>115</v>
+      </c>
+      <c r="I2" s="30">
+        <v>1</v>
+      </c>
+      <c r="J2" s="31">
         <v>101.96</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2">
         <v>5</v>
       </c>
-      <c r="G3" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H3" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="I3" s="31">
-        <v>1</v>
-      </c>
-      <c r="J3" s="32">
+      <c r="G3" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="H3" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="I3" s="30">
+        <v>1</v>
+      </c>
+      <c r="J3" s="31">
         <v>26.98</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2">
         <v>5</v>
       </c>
-      <c r="G4" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="I4" s="31">
-        <v>1</v>
-      </c>
-      <c r="J4" s="32">
+      <c r="G4" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="30">
+        <v>1</v>
+      </c>
+      <c r="J4" s="31">
         <v>17.03</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
-      <c r="G5" s="31" t="s">
-        <v>41</v>
-      </c>
-      <c r="H5" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" s="31">
-        <v>1</v>
-      </c>
-      <c r="J5" s="32">
+      <c r="G5" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" s="30">
+        <v>1</v>
+      </c>
+      <c r="J5" s="31">
         <v>39.950000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B6" s="2">
         <v>10</v>
       </c>
-      <c r="G6" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="I6" s="31">
-        <v>1</v>
-      </c>
-      <c r="J6" s="32">
+      <c r="G6" s="30" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="I6" s="30">
+        <v>1</v>
+      </c>
+      <c r="J6" s="31">
         <v>39.950000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" s="2">
         <v>7.5</v>
       </c>
-      <c r="G7" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="I7" s="31">
-        <v>1</v>
-      </c>
-      <c r="J7" s="32">
+      <c r="G7" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="I7" s="30">
+        <v>1</v>
+      </c>
+      <c r="J7" s="31">
         <v>12.01</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2">
         <v>0.1</v>
       </c>
-      <c r="G8" s="31" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="I8" s="31">
-        <v>1</v>
-      </c>
-      <c r="J8" s="32">
+      <c r="G8" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="H8" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" s="30">
+        <v>1</v>
+      </c>
+      <c r="J8" s="31">
         <v>44.01</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9"/>
-      <c r="G9" s="31" t="s">
-        <v>127</v>
-      </c>
-      <c r="H9" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="I9" s="31">
-        <v>1</v>
-      </c>
-      <c r="J9" s="32">
+      <c r="G9" s="30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="30">
+        <v>1</v>
+      </c>
+      <c r="J9" s="31">
         <v>28.01</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="18" thickBot="1">
       <c r="A10" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="31" t="s">
-        <v>129</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>130</v>
-      </c>
-      <c r="I10" s="31">
-        <v>1</v>
-      </c>
-      <c r="J10" s="32">
+        <v>59</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="H10" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="I10" s="30">
+        <v>1</v>
+      </c>
+      <c r="J10" s="31">
         <v>35.450000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="16.5" thickTop="1">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="10">
         <f>C11*1000</f>
@@ -4487,22 +4190,22 @@
       <c r="C11" s="11">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="G11" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="I11" s="31">
-        <v>1</v>
-      </c>
-      <c r="J11" s="32">
+      <c r="G11" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="H11" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="I11" s="30">
+        <v>1</v>
+      </c>
+      <c r="J11" s="31">
         <v>238.03</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="10">
         <f t="shared" ref="B12:B13" si="0">C12*1000</f>
@@ -4511,22 +4214,22 @@
       <c r="C12" s="11">
         <v>1.784E-6</v>
       </c>
-      <c r="G12" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="I12" s="31">
-        <v>1</v>
-      </c>
-      <c r="J12" s="32">
+      <c r="G12" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="H12" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="I12" s="30">
+        <v>1</v>
+      </c>
+      <c r="J12" s="31">
         <v>2.0139999999999998</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B13" s="10">
         <f t="shared" si="0"/>
@@ -4535,22 +4238,22 @@
       <c r="C13" s="11">
         <v>8.9999999999999998E-4</v>
       </c>
-      <c r="G13" s="31" t="s">
-        <v>135</v>
-      </c>
-      <c r="H13" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="I13" s="31">
-        <v>1</v>
-      </c>
-      <c r="J13" s="32">
+      <c r="G13" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="H13" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="30">
+        <v>1</v>
+      </c>
+      <c r="J13" s="31">
         <v>60.08</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B14" s="10">
         <f t="shared" ref="B14" si="1">C14*1000</f>
@@ -4559,46 +4262,46 @@
       <c r="C14" s="11">
         <v>2.4599999999999999E-3</v>
       </c>
-      <c r="G14" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>132</v>
-      </c>
-      <c r="I14" s="31">
-        <v>1</v>
-      </c>
-      <c r="J14" s="32">
+      <c r="G14" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="30">
+        <v>1</v>
+      </c>
+      <c r="J14" s="31">
         <v>238.03</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="10">
-        <f t="shared" ref="B15:B25" si="2">C15*1000</f>
+        <f t="shared" ref="B15:B23" si="2">C15*1000</f>
         <v>10.97</v>
       </c>
       <c r="C15" s="11">
         <v>1.0970000000000001E-2</v>
       </c>
-      <c r="G15" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="H15" s="31" t="s">
-        <v>137</v>
-      </c>
-      <c r="I15" s="31">
-        <v>1</v>
-      </c>
-      <c r="J15" s="32">
+      <c r="G15" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="I15" s="30">
+        <v>1</v>
+      </c>
+      <c r="J15" s="31">
         <v>46.07</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B16" s="10">
         <f t="shared" si="2"/>
@@ -4607,22 +4310,22 @@
       <c r="C16" s="11">
         <v>7.8899999999999999E-4</v>
       </c>
-      <c r="G16" s="31" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="I16" s="31">
-        <v>1</v>
-      </c>
-      <c r="J16" s="32">
+      <c r="G16" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16" s="30">
+        <v>1</v>
+      </c>
+      <c r="J16" s="31">
         <v>61.206800000000001</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B17" s="10">
         <f t="shared" si="2"/>
@@ -4631,22 +4334,22 @@
       <c r="C17" s="11">
         <v>8.4175000000000005E-4</v>
       </c>
-      <c r="G17" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="H17" s="31" t="s">
-        <v>140</v>
-      </c>
-      <c r="I17" s="31">
-        <v>1</v>
-      </c>
-      <c r="J17" s="32">
+      <c r="G17" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="I17" s="30">
+        <v>1</v>
+      </c>
+      <c r="J17" s="31">
         <v>183.88</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B18" s="10">
         <f t="shared" si="2"/>
@@ -4655,22 +4358,22 @@
       <c r="C18" s="11">
         <v>1E-3</v>
       </c>
-      <c r="G18" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="H18" s="31" t="s">
-        <v>142</v>
-      </c>
-      <c r="I18" s="31">
-        <v>1</v>
-      </c>
-      <c r="J18" s="32">
+      <c r="G18" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="H18" s="30" t="s">
+        <v>140</v>
+      </c>
+      <c r="I18" s="30">
+        <v>1</v>
+      </c>
+      <c r="J18" s="31">
         <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B19" s="10">
         <f t="shared" si="2"/>
@@ -4679,23 +4382,23 @@
       <c r="C19" s="11">
         <v>2.1599999999999999E-4</v>
       </c>
-      <c r="G19" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="H19" s="31" t="s">
-        <v>143</v>
-      </c>
-      <c r="I19" s="31">
-        <v>1</v>
-      </c>
-      <c r="J19" s="32">
+      <c r="G19" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" s="30">
+        <v>1</v>
+      </c>
+      <c r="J19" s="31">
         <f>5.03</f>
         <v>5.03</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" s="10">
         <f t="shared" si="2"/>
@@ -4704,22 +4407,22 @@
       <c r="C20" s="11">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G20" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="H20" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="I20" s="31">
-        <v>1</v>
-      </c>
-      <c r="J20" s="32">
+      <c r="G20" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" s="30">
+        <v>1</v>
+      </c>
+      <c r="J20" s="31">
         <v>92.09</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" s="10">
         <f t="shared" si="2"/>
@@ -4728,22 +4431,22 @@
       <c r="C21" s="11">
         <v>5.7999999999999996E-3</v>
       </c>
-      <c r="G21" s="31" t="s">
-        <v>146</v>
-      </c>
-      <c r="H21" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="I21" s="31">
-        <v>1</v>
-      </c>
-      <c r="J21" s="32">
+      <c r="G21" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="H21" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="I21" s="30">
+        <v>1</v>
+      </c>
+      <c r="J21" s="31">
         <v>172.14</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B22" s="10">
         <f t="shared" si="2"/>
@@ -4752,22 +4455,22 @@
       <c r="C22" s="11">
         <v>8.1999999999999998E-4</v>
       </c>
-      <c r="G22" s="31" t="s">
-        <v>148</v>
-      </c>
-      <c r="H22" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="I22" s="31">
-        <v>1</v>
-      </c>
-      <c r="J22" s="32">
+      <c r="G22" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="I22" s="30">
+        <v>1</v>
+      </c>
+      <c r="J22" s="31">
         <v>3.016</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="10">
         <f t="shared" si="2"/>
@@ -4776,22 +4479,22 @@
       <c r="C23" s="11">
         <v>5.3399999999999997E-4</v>
       </c>
-      <c r="G23" s="31" t="s">
-        <v>150</v>
-      </c>
-      <c r="H23" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="I23" s="31">
-        <v>1</v>
-      </c>
-      <c r="J23" s="32">
+      <c r="G23" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="H23" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="I23" s="30">
+        <v>1</v>
+      </c>
+      <c r="J23" s="31">
         <v>4.0019999999999998</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B24" s="10">
         <f t="shared" ref="B24" si="3">C24*1000</f>
@@ -4800,22 +4503,22 @@
       <c r="C24" s="11">
         <v>8.6964E-3</v>
       </c>
-      <c r="G24" s="31" t="s">
-        <v>152</v>
-      </c>
-      <c r="H24" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="I24" s="31">
-        <v>1</v>
-      </c>
-      <c r="J24" s="32">
+      <c r="G24" s="30" t="s">
+        <v>150</v>
+      </c>
+      <c r="H24" s="30" t="s">
+        <v>151</v>
+      </c>
+      <c r="I24" s="30">
+        <v>1</v>
+      </c>
+      <c r="J24" s="31">
         <v>34.01</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B25" s="10">
         <f>C25*1000</f>
@@ -4824,22 +4527,22 @@
       <c r="C25" s="11">
         <v>7.0209999999999999E-4</v>
       </c>
-      <c r="G25" s="31" t="s">
-        <v>154</v>
-      </c>
-      <c r="H25" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="I25" s="31">
-        <v>1</v>
-      </c>
-      <c r="J25" s="32">
+      <c r="G25" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="H25" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="I25" s="30">
+        <v>1</v>
+      </c>
+      <c r="J25" s="31">
         <v>168.69</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B26" s="10">
         <f>C26*1000</f>
@@ -4848,23 +4551,23 @@
       <c r="C26" s="11">
         <v>7.9000000000000001E-4</v>
       </c>
-      <c r="G26" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="H26" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="I26" s="31">
-        <v>1</v>
-      </c>
-      <c r="J26" s="32">
+      <c r="G26" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="H26" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="I26" s="30">
+        <v>1</v>
+      </c>
+      <c r="J26" s="31">
         <f>(14.007*2)+(1.008*4)</f>
         <v>32.045999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B27" s="10">
         <f t="shared" ref="B27:B28" si="4">C27*1000</f>
@@ -4873,22 +4576,22 @@
       <c r="C27" s="11">
         <v>1.17325E-3</v>
       </c>
-      <c r="G27" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="H27" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="I27" s="31">
-        <v>1</v>
-      </c>
-      <c r="J27" s="32">
+      <c r="G27" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="I27" s="30">
+        <v>1</v>
+      </c>
+      <c r="J27" s="31">
         <v>2.02</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="10">
         <f t="shared" si="4"/>
@@ -4897,22 +4600,22 @@
       <c r="C28" s="11">
         <v>1.6239999999999999E-4</v>
       </c>
-      <c r="G28" s="31" t="s">
-        <v>103</v>
-      </c>
-      <c r="H28" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="I28" s="31">
-        <v>1</v>
-      </c>
-      <c r="J28" s="32">
+      <c r="G28" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H28" s="30" t="s">
+        <v>157</v>
+      </c>
+      <c r="I28" s="30">
+        <v>1</v>
+      </c>
+      <c r="J28" s="31">
         <v>170.34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="B29" s="10">
         <f t="shared" ref="B29" si="5">C29*1000</f>
@@ -4921,46 +4624,46 @@
       <c r="C29" s="11">
         <v>1.505E-3</v>
       </c>
-      <c r="G29" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="H29" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="I29" s="31">
-        <v>1</v>
-      </c>
-      <c r="J29" s="32">
+      <c r="G29" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H29" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="I29" s="30">
+        <v>1</v>
+      </c>
+      <c r="J29" s="31">
         <v>6.94</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" s="10">
-        <f t="shared" ref="B30:B42" si="6">C30*1000</f>
+        <f t="shared" ref="B30:B40" si="6">C30*1000</f>
         <v>5.8999999999999997E-2</v>
       </c>
       <c r="C30" s="11">
         <v>5.8999999999999998E-5</v>
       </c>
-      <c r="G30" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="I30" s="31">
-        <v>1</v>
-      </c>
-      <c r="J30" s="32">
+      <c r="G30" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="H30" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="I30" s="30">
+        <v>1</v>
+      </c>
+      <c r="J30" s="31">
         <v>17.03</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B31" s="10">
         <f t="shared" si="6"/>
@@ -4969,22 +4672,22 @@
       <c r="C31" s="11">
         <v>7.0850000000000001E-5</v>
       </c>
-      <c r="G31" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="H31" s="31" t="s">
-        <v>128</v>
-      </c>
-      <c r="I31" s="31">
-        <v>1</v>
-      </c>
-      <c r="J31" s="32">
+      <c r="G31" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="H31" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="I31" s="30">
+        <v>1</v>
+      </c>
+      <c r="J31" s="31">
         <v>28.01</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="10">
         <f t="shared" si="6"/>
@@ -4993,22 +4696,22 @@
       <c r="C32" s="11">
         <v>4.2560999999999999E-4</v>
       </c>
-      <c r="G32" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="H32" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="I32" s="31">
-        <v>1</v>
-      </c>
-      <c r="J32" s="32">
+      <c r="G32" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="H32" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="I32" s="30">
+        <v>1</v>
+      </c>
+      <c r="J32" s="31">
         <v>44.01</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B33" s="10">
         <f t="shared" si="6"/>
@@ -5017,22 +4720,22 @@
       <c r="C33" s="11">
         <v>1.1410000000000001E-3</v>
       </c>
-      <c r="G33" s="31" t="s">
-        <v>43</v>
-      </c>
-      <c r="H33" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="I33" s="31">
-        <v>1</v>
-      </c>
-      <c r="J33" s="32">
+      <c r="G33" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="H33" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="I33" s="30">
+        <v>1</v>
+      </c>
+      <c r="J33" s="31">
         <v>2.0139999999999998</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B34" s="10">
         <f t="shared" si="6"/>
@@ -5041,22 +4744,22 @@
       <c r="C34" s="11">
         <v>8.2490700000000005E-4</v>
       </c>
-      <c r="G34" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="H34" s="31" t="s">
-        <v>149</v>
-      </c>
-      <c r="I34" s="31">
-        <v>1</v>
-      </c>
-      <c r="J34" s="32">
+      <c r="G34" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="I34" s="30">
+        <v>1</v>
+      </c>
+      <c r="J34" s="31">
         <v>3.016</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="10">
         <f t="shared" si="6"/>
@@ -5065,22 +4768,22 @@
       <c r="C35" s="11">
         <v>7.7999999999999996E-3</v>
       </c>
-      <c r="G35" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="H35" s="31" t="s">
-        <v>151</v>
-      </c>
-      <c r="I35" s="31">
-        <v>1</v>
-      </c>
-      <c r="J35" s="32">
+      <c r="G35" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="H35" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" s="30">
+        <v>1</v>
+      </c>
+      <c r="J35" s="31">
         <v>4.0019999999999998</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" s="10">
         <f t="shared" si="6"/>
@@ -5089,22 +4792,22 @@
       <c r="C36" s="11">
         <v>7.0850000000000002E-3</v>
       </c>
-      <c r="G36" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="H36" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="I36" s="31">
-        <v>1</v>
-      </c>
-      <c r="J36" s="32">
+      <c r="G36" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="H36" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="I36" s="30">
+        <v>1</v>
+      </c>
+      <c r="J36" s="31">
         <v>2.02</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B37" s="10">
         <f t="shared" si="6"/>
@@ -5113,22 +4816,22 @@
       <c r="C37" s="11">
         <v>8.8000000000000003E-4</v>
       </c>
-      <c r="G37" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="H37" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="I37" s="31">
-        <v>1</v>
-      </c>
-      <c r="J37" s="32">
+      <c r="G37" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="I37" s="30">
+        <v>1</v>
+      </c>
+      <c r="J37" s="31">
         <v>16.05</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B38" s="10">
         <f t="shared" si="6"/>
@@ -5137,22 +4840,22 @@
       <c r="C38" s="11">
         <v>1.4499999999999999E-3</v>
       </c>
-      <c r="G38" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="H38" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="I38" s="33">
-        <v>1</v>
-      </c>
-      <c r="J38" s="32">
+      <c r="G38" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="I38" s="32">
+        <v>1</v>
+      </c>
+      <c r="J38" s="31">
         <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B39" s="10">
         <f t="shared" si="6"/>
@@ -5161,22 +4864,22 @@
       <c r="C39" s="11">
         <v>1.0499999999999999E-3</v>
       </c>
-      <c r="G39" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="H39" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="I39" s="31">
-        <v>1</v>
-      </c>
-      <c r="J39" s="32">
+      <c r="G39" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="H39" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="I39" s="30">
+        <v>1</v>
+      </c>
+      <c r="J39" s="31">
         <v>28.01</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="B40" s="10">
         <f t="shared" si="6"/>
@@ -5185,23 +4888,23 @@
       <c r="C40" s="11">
         <v>3.310332E-3</v>
       </c>
-      <c r="G40" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="H40" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="I40" s="31">
-        <v>1</v>
-      </c>
-      <c r="J40" s="32">
+      <c r="G40" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="H40" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="I40" s="30">
+        <v>1</v>
+      </c>
+      <c r="J40" s="31">
         <f>J36</f>
         <v>2.02</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B41" s="10">
         <f>C41*1000</f>
@@ -5210,22 +4913,22 @@
       <c r="C41" s="11">
         <v>7.9100000000000004E-4</v>
       </c>
-      <c r="G41" s="31" t="s">
-        <v>166</v>
-      </c>
-      <c r="H41" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="I41" s="31">
-        <v>1</v>
-      </c>
-      <c r="J41" s="32">
+      <c r="G41" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="H41" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="I41" s="30">
+        <v>1</v>
+      </c>
+      <c r="J41" s="31">
         <v>159.69</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B42" s="10">
         <f>C42*1000</f>
@@ -5234,23 +4937,23 @@
       <c r="C42" s="11">
         <v>8.2899999999999998E-4</v>
       </c>
-      <c r="G42" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="H42" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="I42" s="31">
-        <v>1</v>
-      </c>
-      <c r="J42" s="32">
+      <c r="G42" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="H42" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="I42" s="30">
+        <v>1</v>
+      </c>
+      <c r="J42" s="31">
         <f>55.845*2</f>
         <v>111.69</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B43" s="10">
         <f>C43*1000</f>
@@ -5259,82 +4962,82 @@
       <c r="C43" s="11">
         <v>1E-3</v>
       </c>
-      <c r="G43" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="H43" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="I43" s="31">
-        <v>1</v>
-      </c>
-      <c r="J43" s="32">
+      <c r="G43" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="H43" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="I43" s="30">
+        <v>1</v>
+      </c>
+      <c r="J43" s="31">
         <f>55.845*2</f>
         <v>111.69</v>
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="G44" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="H44" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="I44" s="31">
-        <v>1</v>
-      </c>
-      <c r="J44" s="32">
+      <c r="G44" s="30" t="s">
+        <v>168</v>
+      </c>
+      <c r="H44" s="30" t="s">
+        <v>161</v>
+      </c>
+      <c r="I44" s="30">
+        <v>1</v>
+      </c>
+      <c r="J44" s="31">
         <f>12.02+4*1.008</f>
         <v>16.052</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="18" thickBot="1">
       <c r="A45" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45"/>
       <c r="C45" s="12"/>
-      <c r="G45" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="H45" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="I45" s="31">
-        <v>1</v>
-      </c>
-      <c r="J45" s="32">
+      <c r="G45" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="H45" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="I45" s="30">
+        <v>1</v>
+      </c>
+      <c r="J45" s="31">
         <f>(28.086*2)+(16*2)</f>
         <v>88.171999999999997</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="19.5" thickTop="1">
       <c r="A46" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46" s="10">
-        <f t="shared" ref="B46:B59" si="7">C46*1000</f>
+        <f t="shared" ref="B46:B50" si="7">C46*1000</f>
         <v>5</v>
       </c>
       <c r="C46" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G46" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="H46" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="I46" s="31">
-        <v>1</v>
-      </c>
-      <c r="J46" s="32">
+      <c r="G46" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="H46" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="I46" s="30">
+        <v>1</v>
+      </c>
+      <c r="J46" s="31">
         <v>46.07</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B47" s="10">
         <f t="shared" si="7"/>
@@ -5343,22 +5046,22 @@
       <c r="C47" s="11">
         <v>5.4399999999999997E-2</v>
       </c>
-      <c r="G47" s="31" t="s">
-        <v>174</v>
-      </c>
-      <c r="H47" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="I47" s="31">
-        <v>1</v>
-      </c>
-      <c r="J47" s="32">
+      <c r="G47" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="H47" s="30" t="s">
+        <v>173</v>
+      </c>
+      <c r="I47" s="30">
+        <v>1</v>
+      </c>
+      <c r="J47" s="31">
         <v>233.88</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B48" s="10">
         <f t="shared" si="7"/>
@@ -5367,23 +5070,23 @@
       <c r="C48" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G48" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="H48" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="I48" s="31">
-        <v>1</v>
-      </c>
-      <c r="J48" s="32">
+      <c r="G48" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="I48" s="30">
+        <v>1</v>
+      </c>
+      <c r="J48" s="31">
         <f>14.007*2</f>
         <v>28.013999999999999</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B49" s="10">
         <f t="shared" si="7"/>
@@ -5392,22 +5095,22 @@
       <c r="C49" s="11">
         <v>6.0000000000000002E-5</v>
       </c>
-      <c r="G49" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="H49" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="I49" s="31">
-        <v>1</v>
-      </c>
-      <c r="J49" s="32">
+      <c r="G49" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="H49" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="I49" s="30">
+        <v>1</v>
+      </c>
+      <c r="J49" s="31">
         <v>92.04</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B50" s="10">
         <f t="shared" si="7"/>
@@ -5416,242 +5119,266 @@
       <c r="C50" s="11">
         <v>5.0108799999999997E-3</v>
       </c>
-      <c r="G50" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="H50" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="I50" s="31">
-        <v>1</v>
-      </c>
-      <c r="J50" s="32">
+      <c r="G50" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="H50" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="I50" s="30">
+        <v>1</v>
+      </c>
+      <c r="J50" s="31">
         <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
-        <v>57</v>
+        <v>227</v>
       </c>
       <c r="B51" s="10">
-        <f t="shared" si="7"/>
-        <v>5</v>
+        <f t="shared" ref="B51" si="8">C51*1000</f>
+        <v>4.3499999999999996</v>
       </c>
       <c r="C51" s="11">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="G51" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="H51" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="I51" s="31">
-        <v>1</v>
-      </c>
-      <c r="J51" s="32">
+        <v>4.3499999999999997E-3</v>
+      </c>
+      <c r="G51" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="I51" s="30">
+        <v>1</v>
+      </c>
+      <c r="J51" s="31">
         <v>30.97</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
-        <v>51</v>
+        <v>228</v>
       </c>
       <c r="B52" s="10">
-        <f t="shared" si="7"/>
-        <v>8.6</v>
+        <f t="shared" ref="B52" si="9">C52*1000</f>
+        <v>6.24</v>
       </c>
       <c r="C52" s="11">
-        <v>8.6E-3</v>
-      </c>
-      <c r="G52" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="H52" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="I52" s="31">
-        <v>1</v>
-      </c>
-      <c r="J52" s="32">
+        <v>6.2399999999999999E-3</v>
+      </c>
+      <c r="G52" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="H52" s="30" t="s">
+        <v>179</v>
+      </c>
+      <c r="I52" s="30">
+        <v>1</v>
+      </c>
+      <c r="J52" s="31">
         <f>195.078</f>
         <v>195.078</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B53" s="10">
-        <f t="shared" si="7"/>
-        <v>5.7050000000000001</v>
+        <f t="shared" ref="B53:B61" si="10">C53*1000</f>
+        <v>5</v>
       </c>
       <c r="C53" s="11">
-        <v>5.705E-3</v>
-      </c>
-      <c r="G53" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="H53" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="I53" s="31">
-        <v>1</v>
-      </c>
-      <c r="J53" s="32">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="G53" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="H53" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="I53" s="30">
+        <v>1</v>
+      </c>
+      <c r="J53" s="31">
         <v>76.08</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B54" s="10">
-        <f t="shared" si="7"/>
-        <v>0.35399999999999998</v>
+        <f t="shared" si="10"/>
+        <v>8.6</v>
       </c>
       <c r="C54" s="11">
-        <v>3.5399999999999999E-4</v>
-      </c>
-      <c r="G54" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="H54" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="I54" s="31">
-        <v>1</v>
-      </c>
-      <c r="J54" s="32">
+        <v>8.6E-3</v>
+      </c>
+      <c r="G54" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="H54" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="I54" s="30">
+        <v>1</v>
+      </c>
+      <c r="J54" s="31">
         <v>28.09</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="10">
-        <f t="shared" si="7"/>
-        <v>2.12805</v>
+        <f t="shared" si="10"/>
+        <v>5.7050000000000001</v>
       </c>
       <c r="C55" s="11">
-        <v>2.1280499999999998E-3</v>
-      </c>
-      <c r="G55" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="H55" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="I55" s="31">
-        <v>1</v>
-      </c>
-      <c r="J55" s="32">
+        <v>5.705E-3</v>
+      </c>
+      <c r="G55" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="H55" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="I55" s="30">
+        <v>1</v>
+      </c>
+      <c r="J55" s="31">
         <v>186.09</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B56" s="10">
-        <f t="shared" si="7"/>
-        <v>4.1000000000000005</v>
+        <f t="shared" si="10"/>
+        <v>0.35399999999999998</v>
       </c>
       <c r="C56" s="11">
-        <v>4.1000000000000003E-3</v>
-      </c>
-      <c r="G56" s="31" t="s">
-        <v>187</v>
-      </c>
-      <c r="H56" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="I56" s="31">
-        <v>1</v>
-      </c>
-      <c r="J56" s="32">
+        <v>3.5399999999999999E-4</v>
+      </c>
+      <c r="G56" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="H56" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="I56" s="30">
+        <v>1</v>
+      </c>
+      <c r="J56" s="31">
         <v>270.02999999999997</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="2" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="B57" s="10">
-        <f t="shared" si="7"/>
-        <v>12.5</v>
+        <f t="shared" si="10"/>
+        <v>2.12805</v>
       </c>
       <c r="C57" s="11">
-        <v>1.2500000000000001E-2</v>
-      </c>
-      <c r="G57" s="31" t="s">
-        <v>86</v>
-      </c>
-      <c r="H57" s="31" t="s">
-        <v>189</v>
-      </c>
-      <c r="I57" s="31">
-        <v>1</v>
-      </c>
-      <c r="J57" s="32">
+        <v>2.1280499999999998E-3</v>
+      </c>
+      <c r="G57" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="H57" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="I57" s="30">
+        <v>1</v>
+      </c>
+      <c r="J57" s="31">
         <v>60.1</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B58" s="10">
-        <f t="shared" si="7"/>
-        <v>7.5</v>
+        <f t="shared" si="10"/>
+        <v>4.1000000000000005</v>
       </c>
       <c r="C58" s="11">
-        <v>7.4999999999999997E-3</v>
-      </c>
-      <c r="G58" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="H58" s="31" t="s">
-        <v>190</v>
-      </c>
-      <c r="I58" s="31">
-        <v>1</v>
-      </c>
-      <c r="J58" s="32">
+        <v>4.1000000000000003E-3</v>
+      </c>
+      <c r="G58" s="30" t="s">
+        <v>85</v>
+      </c>
+      <c r="H58" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="I58" s="30">
+        <v>1</v>
+      </c>
+      <c r="J58" s="31">
         <f>SUM(($D$38*0.25)+($D$82*0.75))</f>
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:10">
-      <c r="A59" s="5" t="s">
-        <v>78</v>
+      <c r="A59" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="B59" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
+        <v>12.5</v>
+      </c>
+      <c r="C59" s="11">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="G59" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H59" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="I59" s="30">
+        <v>1</v>
+      </c>
+      <c r="J59" s="31">
+        <v>18.02</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="10">
+        <f t="shared" si="10"/>
+        <v>7.5</v>
+      </c>
+      <c r="C60" s="11">
+        <v>7.4999999999999997E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B61" s="10">
+        <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C61" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="G59" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="H59" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="I59" s="31">
-        <v>1</v>
-      </c>
-      <c r="J59" s="32">
-        <v>18.02</v>
-      </c>
     </row>
     <row r="78" spans="7:10">
-      <c r="G78" s="31"/>
-      <c r="H78" s="31"/>
-      <c r="I78" s="31"/>
-      <c r="J78" s="32"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="30"/>
+      <c r="J78" s="31"/>
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
@@ -5685,15 +5412,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="86" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
+      <c r="A1" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
@@ -6128,39 +5855,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="20.25" thickBot="1">
-      <c r="A1" s="87" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
+      <c r="A1" s="80" t="s">
+        <v>202</v>
+      </c>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" thickTop="1" thickBot="1">
-      <c r="A2" s="48" t="s">
-        <v>98</v>
+      <c r="A2" s="47" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="16.5" thickTop="1">
       <c r="B3" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4"/>
-      <c r="B4" s="22">
+      <c r="B4" s="21">
         <v>203946</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="24">
         <v>2300</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="49">
         <v>299792458</v>
       </c>
     </row>
@@ -6173,45 +5900,45 @@
         <v>22</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2"/>
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <f>B4*G7</f>
         <v>2000027.0408999999</v>
       </c>
-      <c r="C6" s="60">
+      <c r="C6" s="59">
         <f>IFERROR(C4*1000/B6,0)</f>
         <v>1.1499844516927202</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <f>C4*1000*B6</f>
         <v>4600062194070</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <f>IFERROR(D6/C6,0)</f>
         <v>4000108164331.21</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G7" s="49">
+        <v>200</v>
+      </c>
+      <c r="G7" s="48">
         <v>9.8066499999999994</v>
       </c>
       <c r="J7"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="B8" s="29">
+      <c r="B8" s="28">
         <f>B6/G4</f>
         <v>6.671372102696459E-3</v>
       </c>
@@ -6221,24 +5948,24 @@
       <c r="J9"/>
     </row>
     <row r="10" spans="1:10" ht="18" thickBot="1">
-      <c r="A10" s="48" t="s">
-        <v>99</v>
+      <c r="A10" s="47" t="s">
+        <v>97</v>
       </c>
       <c r="J10"/>
     </row>
     <row r="11" spans="1:10" ht="16.5" thickTop="1">
       <c r="B11" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="B12" s="23">
+      <c r="B12" s="22">
         <v>960</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="23">
         <f>(C14*B14)/1000</f>
         <v>0.29543542033151998</v>
       </c>
@@ -6251,26 +5978,26 @@
         <v>22</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G13"/>
     </row>
     <row r="14" spans="1:10">
-      <c r="B14" s="19">
+      <c r="B14" s="18">
         <f>B12*G7</f>
         <v>9414.384</v>
       </c>
-      <c r="C14" s="60">
+      <c r="C14" s="59">
         <f>E14/D14</f>
         <v>3.1381279999999998E-2</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="22">
         <v>2824315200</v>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="18">
         <f>IFERROR((B14^2),0)</f>
         <v>88630626.099455997</v>
       </c>
@@ -6285,32 +6012,32 @@
       <c r="G15"/>
     </row>
     <row r="16" spans="1:10">
-      <c r="B16" s="63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="63"/>
+      <c r="B16" s="62" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="62"/>
       <c r="G16"/>
     </row>
     <row r="17" spans="1:8">
       <c r="B17" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G17"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="B18" s="21">
-        <v>1</v>
-      </c>
-      <c r="C18" s="21">
+      <c r="B18" s="20">
+        <v>1</v>
+      </c>
+      <c r="C18" s="20">
         <v>0</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="19">
         <f>C12/(B18*G7)</f>
         <v>3.0126028799999999E-2</v>
       </c>
@@ -6322,53 +6049,53 @@
       <c r="H19"/>
     </row>
     <row r="21" spans="1:8" ht="18" thickBot="1">
-      <c r="A21" s="48" t="s">
-        <v>94</v>
+      <c r="A21" s="47" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16.5" thickTop="1">
       <c r="B22" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:8">
-      <c r="B23" s="28">
+      <c r="B23" s="27">
         <v>1000000000</v>
       </c>
-      <c r="C23" s="54">
+      <c r="C23" s="53">
         <f>(B23/G4/1000)</f>
         <v>3.3356409519815205E-3</v>
       </c>
-      <c r="D23" s="51">
+      <c r="D23" s="50">
         <f>B23/1000</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="18" thickBot="1">
-      <c r="A26" s="48" t="s">
-        <v>101</v>
+      <c r="A26" s="47" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="16.5" thickTop="1">
       <c r="B27" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:8">
-      <c r="B28" s="27">
+      <c r="B28" s="26">
         <f>B30/G7</f>
         <v>749335.32127174258</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="20">
         <v>3800</v>
       </c>
     </row>
@@ -6380,195 +6107,195 @@
         <v>22</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <f>(2*E30)^0.5</f>
         <v>7348469.2283495339</v>
       </c>
-      <c r="C30" s="60">
+      <c r="C30" s="59">
         <f>IFERROR(C28*1000/B30,0)</f>
         <v>0.51711450125422653</v>
       </c>
-      <c r="D30" s="27">
+      <c r="D30" s="26">
         <f>C28*1000*B30</f>
         <v>27924183067728.23</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E30" s="25">
         <v>27000000000000</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="B31" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="B32" s="29">
+      <c r="B32" s="28">
         <f>B30/G4</f>
         <v>2.4511854892458749E-2</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="18" thickBot="1">
-      <c r="A35" s="48" t="s">
-        <v>115</v>
+      <c r="A35" s="47" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="16.5" thickTop="1">
-      <c r="A36" s="56"/>
+      <c r="A36" s="55"/>
       <c r="G36"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="B37" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" s="34">
+      <c r="B37" s="37" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="33">
         <v>2130</v>
       </c>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
       <c r="F37"/>
       <c r="G37"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="B38" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="C38" s="35">
+      <c r="B38" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" s="34">
         <v>8.3144621000000001</v>
       </c>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
       <c r="F38"/>
     </row>
     <row r="39" spans="1:9" ht="16.5" thickBot="1">
-      <c r="B39" s="38" t="s">
-        <v>113</v>
+      <c r="B39" s="37" t="s">
+        <v>111</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="39">
+        <v>28</v>
+      </c>
+      <c r="D39" s="38">
         <f>IFERROR(VLOOKUP(C39,Database!$G$2:$J$59,4,FALSE),"-")</f>
         <v>2.02</v>
       </c>
-      <c r="E39" s="40">
+      <c r="E39" s="39">
         <f>D39/1000</f>
         <v>2.0200000000000001E-3</v>
       </c>
       <c r="F39"/>
     </row>
     <row r="40" spans="1:9" ht="17.25" thickTop="1" thickBot="1">
-      <c r="B40" s="38"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D40" s="39">
+        <v>75</v>
+      </c>
+      <c r="D40" s="38">
         <f>IFERROR(VLOOKUP(C40,Database!$G$2:$J$59,4,FALSE),"-")</f>
         <v>18.02</v>
       </c>
-      <c r="E40" s="40">
+      <c r="E40" s="39">
         <f>D40/1000</f>
         <v>1.8020000000000001E-2</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="16.5" thickTop="1">
-      <c r="B41" s="38" t="s">
-        <v>205</v>
+      <c r="B41" s="37" t="s">
+        <v>203</v>
       </c>
       <c r="C41" s="14">
         <v>1.3979999999999999</v>
       </c>
       <c r="D41"/>
-      <c r="E41" s="30"/>
+      <c r="E41" s="29"/>
     </row>
     <row r="42" spans="1:9" ht="16.5" thickBot="1">
-      <c r="B42" s="38" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" s="36">
+      <c r="B42" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="35">
         <v>0</v>
       </c>
-      <c r="D42" s="55">
+      <c r="D42" s="54">
         <f>IFERROR(C42*101320,101.32)</f>
         <v>0</v>
       </c>
-      <c r="E42" s="30"/>
+      <c r="E42" s="29"/>
     </row>
     <row r="43" spans="1:9" ht="17.25" thickTop="1" thickBot="1">
-      <c r="B43" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="C43" s="36">
+      <c r="B43" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C43" s="35">
         <v>500</v>
       </c>
-      <c r="D43" s="55">
+      <c r="D43" s="54">
         <f>C43*101320</f>
         <v>50660000</v>
       </c>
-      <c r="E43" s="30"/>
+      <c r="E43" s="29"/>
     </row>
     <row r="44" spans="1:9" ht="16.5" thickTop="1">
-      <c r="B44" s="38"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="B45" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="C45" s="37">
+      <c r="B45" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="36">
         <f>(C37*C38)/E39</f>
         <v>8767229.8381188121</v>
       </c>
-      <c r="D45" s="30"/>
-      <c r="E45" s="37">
+      <c r="D45" s="29"/>
+      <c r="E45" s="36">
         <f>(C37*C38)/E40</f>
         <v>982786.03068812436</v>
       </c>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="B46" s="38" t="s">
-        <v>206</v>
-      </c>
-      <c r="C46" s="37">
+      <c r="B46" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" s="36">
         <f>(2*C41)/(C41-1)</f>
         <v>7.0251256281407048</v>
       </c>
-      <c r="D46" s="30"/>
+      <c r="D46" s="29"/>
       <c r="E46"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="B47" s="38" t="s">
-        <v>210</v>
-      </c>
-      <c r="C47" s="37">
+      <c r="B47" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="C47" s="36">
         <f>(C41-1)/C41</f>
         <v>0.284692417739628</v>
       </c>
-      <c r="D47" s="30"/>
+      <c r="D47" s="29"/>
       <c r="E47"/>
     </row>
     <row r="48" spans="1:9" customFormat="1">
       <c r="A48" s="5"/>
-      <c r="B48" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" s="37">
+      <c r="B48" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C48" s="36">
         <f>1-((D42/D43)^C47)</f>
         <v>1</v>
       </c>
-      <c r="D48" s="30"/>
+      <c r="D48" s="29"/>
       <c r="F48" s="5"/>
     </row>
     <row r="49" spans="1:7">
@@ -6580,350 +6307,350 @@
       <c r="F49"/>
     </row>
     <row r="50" spans="1:7" ht="16.5" thickBot="1">
-      <c r="B50" s="38"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="17" t="str">
         <f>C39</f>
         <v>LqdHydrogen</v>
       </c>
-      <c r="D50" s="30"/>
+      <c r="D50" s="29"/>
       <c r="E50" s="17" t="str">
         <f>C40</f>
         <v>Water (CRP)</v>
       </c>
-      <c r="G50" s="42"/>
+      <c r="G50" s="41"/>
     </row>
     <row r="51" spans="1:7" ht="16.5" thickTop="1">
-      <c r="B51" s="38" t="s">
+      <c r="B51" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C51" s="52">
+      <c r="C51" s="51">
         <f>(C45*C46*C48)^0.5</f>
         <v>7847.9864311534302</v>
       </c>
-      <c r="D51" s="30"/>
-      <c r="E51" s="52">
+      <c r="D51" s="29"/>
+      <c r="E51" s="51">
         <f>(E45*C46*C48)^0.5</f>
         <v>2627.5835536031618</v>
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="B52" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="C52" s="52">
+      <c r="B52" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="C52" s="51">
         <f>C51/9.80655</f>
         <v>800.28006089332439</v>
       </c>
-      <c r="D52" s="30"/>
-      <c r="E52" s="52">
+      <c r="D52" s="29"/>
+      <c r="E52" s="51">
         <f>E51/9.80655</f>
         <v>267.94168730115706</v>
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
+      <c r="E53" s="40"/>
+      <c r="F53" s="40"/>
     </row>
     <row r="54" spans="1:7">
-      <c r="E54" s="41"/>
+      <c r="E54" s="40"/>
     </row>
     <row r="55" spans="1:7" ht="18" thickBot="1">
-      <c r="A55" s="48" t="s">
-        <v>197</v>
+      <c r="A55" s="47" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="16.5" thickTop="1"/>
     <row r="57" spans="1:7">
       <c r="C57" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="D58" s="46">
+      <c r="D58" s="45">
         <v>60</v>
       </c>
-      <c r="E58" s="57">
+      <c r="E58" s="56">
         <v>0.75</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="B60" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="16.5" thickBot="1">
-      <c r="B61" s="44" t="s">
-        <v>196</v>
-      </c>
-      <c r="C61" s="59">
+      <c r="B61" s="43" t="s">
+        <v>194</v>
+      </c>
+      <c r="C61" s="58">
         <v>800</v>
       </c>
-      <c r="D61" s="58">
+      <c r="D61" s="57">
         <f>D58</f>
         <v>60</v>
       </c>
-      <c r="E61" s="47">
+      <c r="E61" s="46">
         <f t="shared" ref="E61:E67" si="0">($C$61/C61)^$E$58</f>
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="16.5" thickTop="1">
-      <c r="B62" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="C62" s="59">
+      <c r="B62" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="C62" s="58">
         <v>606</v>
       </c>
-      <c r="D62" s="53">
+      <c r="D62" s="52">
         <f t="shared" ref="D62:D67" si="1">$D$58*(($C$61/C62)^$E$58)</f>
         <v>73.894867118770051</v>
       </c>
-      <c r="E62" s="47">
+      <c r="E62" s="46">
         <f t="shared" si="0"/>
         <v>1.2315811186461676</v>
       </c>
     </row>
     <row r="63" spans="1:7">
-      <c r="B63" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="C63" s="59">
+      <c r="B63" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="58">
         <v>400</v>
       </c>
-      <c r="D63" s="53">
+      <c r="D63" s="52">
         <f t="shared" si="1"/>
         <v>100.90756983044574</v>
       </c>
-      <c r="E63" s="47">
+      <c r="E63" s="46">
         <f t="shared" si="0"/>
         <v>1.681792830507429</v>
       </c>
     </row>
     <row r="64" spans="1:7">
-      <c r="B64" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="C64" s="59">
+      <c r="B64" s="43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C64" s="58">
         <v>253</v>
       </c>
-      <c r="D64" s="53">
+      <c r="D64" s="52">
         <f t="shared" si="1"/>
         <v>142.27491989040757</v>
       </c>
-      <c r="E64" s="47">
+      <c r="E64" s="46">
         <f t="shared" si="0"/>
         <v>2.3712486648401261</v>
       </c>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="C65" s="59">
+      <c r="B65" s="42" t="s">
+        <v>189</v>
+      </c>
+      <c r="C65" s="58">
         <v>370</v>
       </c>
-      <c r="D65" s="53">
+      <c r="D65" s="52">
         <f t="shared" si="1"/>
         <v>106.98365906113423</v>
       </c>
-      <c r="E65" s="47">
+      <c r="E65" s="46">
         <f t="shared" si="0"/>
         <v>1.7830609843522371</v>
       </c>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="C66" s="59">
+      <c r="B66" s="42" t="s">
+        <v>124</v>
+      </c>
+      <c r="C66" s="58">
         <v>283</v>
       </c>
-      <c r="D66" s="53">
+      <c r="D66" s="52">
         <f t="shared" si="1"/>
         <v>130.80637609525397</v>
       </c>
-      <c r="E66" s="47">
+      <c r="E66" s="46">
         <f t="shared" si="0"/>
         <v>2.1801062682542329</v>
       </c>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="C67" s="59">
+      <c r="B67" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="C67" s="58">
         <v>253</v>
       </c>
-      <c r="D67" s="53">
+      <c r="D67" s="52">
         <f t="shared" si="1"/>
         <v>142.27491989040757</v>
       </c>
-      <c r="E67" s="47">
+      <c r="E67" s="46">
         <f t="shared" si="0"/>
         <v>2.3712486648401261</v>
       </c>
     </row>
     <row r="68" spans="2:5">
-      <c r="C68" s="59"/>
-      <c r="D68" s="41"/>
-      <c r="E68" s="45"/>
+      <c r="C68" s="58"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="44"/>
     </row>
     <row r="69" spans="2:5">
       <c r="B69" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C69" s="59"/>
-      <c r="D69" s="41"/>
-      <c r="E69" s="45"/>
+        <v>88</v>
+      </c>
+      <c r="C69" s="58"/>
+      <c r="D69" s="40"/>
+      <c r="E69" s="44"/>
     </row>
     <row r="70" spans="2:5" ht="16.5" thickBot="1">
-      <c r="B70" s="44" t="s">
-        <v>52</v>
-      </c>
-      <c r="C70" s="59">
+      <c r="B70" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C70" s="58">
         <v>800</v>
       </c>
-      <c r="D70" s="58">
+      <c r="D70" s="57">
         <f>D58</f>
         <v>60</v>
       </c>
-      <c r="E70" s="47">
+      <c r="E70" s="46">
         <f>($C$61/C70)^$E$58</f>
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="2:5" ht="16.5" thickTop="1">
-      <c r="B71" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C71" s="59">
+      <c r="B71" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C71" s="58">
         <v>606</v>
       </c>
-      <c r="D71" s="53">
+      <c r="D71" s="52">
         <f>$D$58*(($C$70/C71)^$E$58)</f>
         <v>73.894867118770051</v>
       </c>
-      <c r="E71" s="47">
+      <c r="E71" s="46">
         <f>($C$70/C71)^$E$58</f>
         <v>1.2315811186461676</v>
       </c>
     </row>
     <row r="72" spans="2:5">
-      <c r="B72" s="44" t="s">
-        <v>199</v>
-      </c>
-      <c r="C72" s="59">
+      <c r="B72" s="43" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="58">
         <v>253</v>
       </c>
-      <c r="D72" s="53">
+      <c r="D72" s="52">
         <f>$D$58*(($C$70/C72)^$E$58)</f>
         <v>142.27491989040757</v>
       </c>
-      <c r="E72" s="47">
+      <c r="E72" s="46">
         <f>($C$70/C72)^$E$58</f>
         <v>2.3712486648401261</v>
       </c>
     </row>
     <row r="73" spans="2:5">
-      <c r="B73" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="C73" s="59">
+      <c r="B73" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="C73" s="58">
         <v>370</v>
       </c>
-      <c r="D73" s="53">
+      <c r="D73" s="52">
         <f>$D$58*(($C$70/C73)^$E$58)</f>
         <v>106.98365906113423</v>
       </c>
-      <c r="E73" s="47">
+      <c r="E73" s="46">
         <f>($C$70/C73)^$E$58</f>
         <v>1.7830609843522371</v>
       </c>
     </row>
     <row r="74" spans="2:5">
-      <c r="B74" s="43" t="s">
-        <v>203</v>
-      </c>
-      <c r="C74" s="59">
+      <c r="B74" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C74" s="58">
         <v>283</v>
       </c>
-      <c r="D74" s="53">
+      <c r="D74" s="52">
         <f>$D$58*(($C$70/C74)^$E$58)</f>
         <v>130.80637609525397</v>
       </c>
-      <c r="E74" s="47">
+      <c r="E74" s="46">
         <f>($C$70/C74)^$E$58</f>
         <v>2.1801062682542329</v>
       </c>
     </row>
     <row r="75" spans="2:5">
-      <c r="B75" s="43" t="s">
-        <v>51</v>
-      </c>
-      <c r="C75" s="59">
+      <c r="B75" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75" s="58">
         <v>253</v>
       </c>
-      <c r="D75" s="53">
+      <c r="D75" s="52">
         <f>$D$58*(($C$70/C75)^$E$58)</f>
         <v>142.27491989040757</v>
       </c>
-      <c r="E75" s="47">
+      <c r="E75" s="46">
         <f>($C$70/C75)^$E$58</f>
         <v>2.3712486648401261</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="18" thickBot="1">
-      <c r="A81" s="48" t="s">
-        <v>220</v>
+      <c r="A81" s="47" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="16.5" thickTop="1">
       <c r="B82" t="s">
-        <v>216</v>
-      </c>
-      <c r="C82" s="61">
+        <v>214</v>
+      </c>
+      <c r="C82" s="60">
         <v>4000</v>
       </c>
     </row>
     <row r="83" spans="1:3">
       <c r="B83" t="s">
-        <v>218</v>
-      </c>
-      <c r="C83" s="34">
+        <v>216</v>
+      </c>
+      <c r="C83" s="33">
         <v>1600</v>
       </c>
     </row>
     <row r="84" spans="1:3">
       <c r="B84" t="s">
-        <v>217</v>
-      </c>
-      <c r="C84" s="34">
+        <v>215</v>
+      </c>
+      <c r="C84" s="33">
         <v>1000</v>
       </c>
     </row>
     <row r="85" spans="1:3">
       <c r="B85" t="s">
-        <v>215</v>
-      </c>
-      <c r="C85" s="62">
+        <v>213</v>
+      </c>
+      <c r="C85" s="61">
         <f>C82*(1-(C84/C83))</f>
         <v>1500</v>
       </c>
     </row>
     <row r="86" spans="1:3">
       <c r="B86" t="s">
-        <v>219</v>
-      </c>
-      <c r="C86" s="37">
+        <v>217</v>
+      </c>
+      <c r="C86" s="36">
         <f>C83/C84</f>
         <v>1.6</v>
       </c>

--- a/RR_fuelflow.xlsx
+++ b/RR_fuelflow.xlsx
@@ -946,7 +946,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="232">
   <si>
     <t>name</t>
   </si>
@@ -1668,6 +1668,12 @@
   </si>
   <si>
     <t>Mass flow (kg/s)</t>
+  </si>
+  <si>
+    <t>Antimatter (FFT)</t>
+  </si>
+  <si>
+    <t>AntiHydrogen</t>
   </si>
 </sst>
 </file>
@@ -2621,10 +2627,10 @@
         <v>65</v>
       </c>
       <c r="B7" s="21">
-        <v>549</v>
+        <v>1019000</v>
       </c>
       <c r="C7" s="21">
-        <v>1</v>
+        <v>350</v>
       </c>
       <c r="D7" s="77"/>
       <c r="E7" s="77"/>
@@ -2687,23 +2693,23 @@
       <c r="A9" s="1"/>
       <c r="B9" s="18">
         <f>B7*9.80665</f>
-        <v>5383.8508499999998</v>
+        <v>9992976.3499999996</v>
       </c>
       <c r="C9" s="66">
         <f>IFERROR(C7*1000/B9,0)</f>
-        <v>0.18574065810162629</v>
+        <v>3.5024600053216379E-2</v>
       </c>
       <c r="D9" s="18">
         <f>C7*1000*B9</f>
-        <v>5383850.8499999996</v>
+        <v>3497541722500</v>
       </c>
       <c r="E9" s="18">
         <f>IFERROR(D9/C9,0)</f>
-        <v>28985849.975045718</v>
+        <v>99859576331659.312</v>
       </c>
       <c r="G9" s="69">
         <f>SUM(B16:E16)</f>
-        <v>0.18574065810162632</v>
+        <v>3.5024600053216386E-2</v>
       </c>
       <c r="H9" s="65" t="str">
         <f>IF($C$9&gt;$G$9,"Input excesive",IF($C$9&lt;$G$9,"Output excessive","Equal"))</f>
@@ -2786,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="16"/>
@@ -2821,10 +2827,10 @@
         <v>63</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>228</v>
+        <v>28</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>51</v>
+        <v>231</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="63" t="s">
@@ -2863,15 +2869,15 @@
         <v>24</v>
       </c>
       <c r="B14" s="8">
-        <f>IFERROR(VLOOKUP(B13,Database!$A$2:$B$61,2,0),"-")</f>
-        <v>6.24</v>
+        <f>IFERROR(VLOOKUP(B13,Database!$A$2:$B$63,2,0),"-")</f>
+        <v>7.0849999999999996E-2</v>
       </c>
       <c r="C14" s="8">
-        <f>IFERROR(VLOOKUP(C13,Database!$A$2:$B$61,2,0),"-")</f>
-        <v>0.35399999999999998</v>
+        <f>IFERROR(VLOOKUP(C13,Database!$A$2:$B$63,2,0),"-")</f>
+        <v>8.6000000000000007E-2</v>
       </c>
       <c r="D14" s="8" t="str">
-        <f>IFERROR(VLOOKUP(D13,Database!$A$2:$B$61,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(D13,Database!$A$2:$B$63,2,0),"-")</f>
         <v>-</v>
       </c>
       <c r="E14" s="9">
@@ -2896,11 +2902,11 @@
       </c>
       <c r="B15" s="76">
         <f>IFERROR(C9*B12/SUM(B17:D17),"-")</f>
-        <v>2.3188596517056966E-2</v>
+        <v>0.22329996846169195</v>
       </c>
       <c r="C15" s="76">
         <f>IFERROR(C9*C12/SUM(B17:D17),"-")</f>
-        <v>0.11594298258528483</v>
+        <v>0.22329996846169195</v>
       </c>
       <c r="D15" s="69">
         <f>IFERROR(C9*D12/SUM(B17:D17),"-")</f>
@@ -2909,10 +2915,6 @@
       <c r="E15" s="69">
         <f>IFERROR(C9*E12/SUM(B17:D17),0)</f>
         <v>0</v>
-      </c>
-      <c r="G15" s="2">
-        <f>B15/C15</f>
-        <v>0.19999999999999998</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
@@ -2933,11 +2935,11 @@
       </c>
       <c r="B16" s="65">
         <f>IFERROR($B$14*$B$15,"-")</f>
-        <v>0.14469684226643548</v>
+        <v>1.5820802765510875E-2</v>
       </c>
       <c r="C16" s="65">
         <f t="shared" ref="C16:D16" si="0">IFERROR(C14*C15,"-")</f>
-        <v>4.1043815835190831E-2</v>
+        <v>1.920379728770551E-2</v>
       </c>
       <c r="D16" s="65" t="str">
         <f t="shared" si="0"/>
@@ -2946,10 +2948,6 @@
       <c r="E16" s="65">
         <f>E14*E15</f>
         <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <f>B16/C16</f>
-        <v>3.5254237288135597</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
@@ -2975,11 +2973,11 @@
       </c>
       <c r="B17" s="65">
         <f>IFERROR(B12*B14,"-")</f>
-        <v>6.24</v>
+        <v>7.0849999999999996E-2</v>
       </c>
       <c r="C17" s="65">
         <f t="shared" ref="C17:D17" si="1">IFERROR(C12*C14,"-")</f>
-        <v>1.77</v>
+        <v>8.6000000000000007E-2</v>
       </c>
       <c r="D17" s="65" t="str">
         <f t="shared" si="1"/>
@@ -3304,15 +3302,15 @@
         <v>24</v>
       </c>
       <c r="B29" s="8">
-        <f>IFERROR(VLOOKUP(B28,Database!$A$2:$B$61,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(B28,Database!$A$2:$B$63,2,0),"-")</f>
         <v>5.7050000000000001</v>
       </c>
       <c r="C29" s="8">
-        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$61,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(C28,Database!$A$2:$B$63,2,0),"-")</f>
         <v>0.35399999999999998</v>
       </c>
       <c r="D29" s="8" t="str">
-        <f>IFERROR(VLOOKUP(D28,Database!$A$2:$B$61,2,0),"-")</f>
+        <f>IFERROR(VLOOKUP(D28,Database!$A$2:$B$63,2,0),"-")</f>
         <v>-</v>
       </c>
       <c r="E29" s="9">
@@ -3340,10 +3338,6 @@
         <f>IFERROR(C24*E27/SUM(B32:D32),0)</f>
         <v>0.16728791716778338</v>
       </c>
-      <c r="G30" s="2">
-        <f>B30/C30</f>
-        <v>0.25</v>
-      </c>
       <c r="J30" s="64"/>
     </row>
     <row r="31" spans="1:28">
@@ -3365,10 +3359,6 @@
       <c r="E31" s="65">
         <f>E29*E30</f>
         <v>0</v>
-      </c>
-      <c r="G31" s="2">
-        <f>B31/C31</f>
-        <v>4.0289548022598876</v>
       </c>
       <c r="J31" s="64"/>
     </row>
@@ -3954,13 +3944,13 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$61</xm:f>
+            <xm:f>Database!$A$2:$A$63</xm:f>
           </x14:formula1>
           <xm:sqref>B13:D13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Database!$A$2:$A$61</xm:f>
+            <xm:f>Database!$A$2:$A$63</xm:f>
           </x14:formula1>
           <xm:sqref>B28:D28</xm:sqref>
         </x14:dataValidation>
@@ -4205,14 +4195,14 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>230</v>
       </c>
       <c r="B12" s="10">
-        <f t="shared" ref="B12:B13" si="0">C12*1000</f>
-        <v>1.784E-3</v>
+        <f>C12*1000</f>
+        <v>0.01</v>
       </c>
       <c r="C12" s="11">
-        <v>1.784E-6</v>
+        <v>1.0000000000000001E-5</v>
       </c>
       <c r="G12" s="30" t="s">
         <v>131</v>
@@ -4229,14 +4219,14 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="B13" s="10">
-        <f t="shared" si="0"/>
-        <v>0.9</v>
+        <f>C13*1000</f>
+        <v>8.6000000000000007E-2</v>
       </c>
       <c r="C13" s="11">
-        <v>8.9999999999999998E-4</v>
+        <v>8.6000000000000003E-5</v>
       </c>
       <c r="G13" s="30" t="s">
         <v>133</v>
@@ -4253,14 +4243,14 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>219</v>
+        <v>40</v>
       </c>
       <c r="B14" s="10">
-        <f t="shared" ref="B14" si="1">C14*1000</f>
-        <v>2.46</v>
+        <f>C14*1000</f>
+        <v>1.784E-3</v>
       </c>
       <c r="C14" s="11">
-        <v>2.4599999999999999E-3</v>
+        <v>1.784E-6</v>
       </c>
       <c r="G14" s="30" t="s">
         <v>38</v>
@@ -4277,14 +4267,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="B15" s="10">
-        <f t="shared" ref="B15:B23" si="2">C15*1000</f>
-        <v>10.97</v>
+        <f>C15*1000</f>
+        <v>0.9</v>
       </c>
       <c r="C15" s="11">
-        <v>1.0970000000000001E-2</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="G15" s="30" t="s">
         <v>102</v>
@@ -4301,14 +4291,14 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>102</v>
+        <v>219</v>
       </c>
       <c r="B16" s="10">
-        <f t="shared" si="2"/>
-        <v>0.78900000000000003</v>
+        <f t="shared" ref="B16" si="0">C16*1000</f>
+        <v>2.46</v>
       </c>
       <c r="C16" s="11">
-        <v>7.8899999999999999E-4</v>
+        <v>2.4599999999999999E-3</v>
       </c>
       <c r="G16" s="30" t="s">
         <v>103</v>
@@ -4325,14 +4315,14 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>103</v>
+        <v>38</v>
       </c>
       <c r="B17" s="10">
-        <f t="shared" si="2"/>
-        <v>0.84175</v>
+        <f t="shared" ref="B17:B25" si="1">C17*1000</f>
+        <v>10.97</v>
       </c>
       <c r="C17" s="11">
-        <v>8.4175000000000005E-4</v>
+        <v>1.0970000000000001E-2</v>
       </c>
       <c r="G17" s="30" t="s">
         <v>137</v>
@@ -4349,14 +4339,14 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="B18" s="10">
-        <f t="shared" si="2"/>
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0.78900000000000003</v>
       </c>
       <c r="C18" s="11">
-        <v>1E-3</v>
+        <v>7.8899999999999999E-4</v>
       </c>
       <c r="G18" s="30" t="s">
         <v>139</v>
@@ -4373,14 +4363,14 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="B19" s="10">
-        <f t="shared" si="2"/>
-        <v>0.216</v>
+        <f t="shared" si="1"/>
+        <v>0.84175</v>
       </c>
       <c r="C19" s="11">
-        <v>2.1599999999999999E-4</v>
+        <v>8.4175000000000005E-4</v>
       </c>
       <c r="G19" s="30" t="s">
         <v>74</v>
@@ -4398,14 +4388,14 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="B20" s="10">
-        <f t="shared" si="2"/>
-        <v>2.5</v>
+        <f t="shared" si="1"/>
+        <v>1</v>
       </c>
       <c r="C20" s="11">
-        <v>2.5000000000000001E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G20" s="30" t="s">
         <v>142</v>
@@ -4422,14 +4412,14 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B21" s="10">
-        <f t="shared" si="2"/>
-        <v>5.8</v>
+        <f t="shared" si="1"/>
+        <v>0.216</v>
       </c>
       <c r="C21" s="11">
-        <v>5.7999999999999996E-3</v>
+        <v>2.1599999999999999E-4</v>
       </c>
       <c r="G21" s="30" t="s">
         <v>144</v>
@@ -4446,14 +4436,14 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="B22" s="10">
-        <f t="shared" si="2"/>
-        <v>0.82</v>
+        <f t="shared" si="1"/>
+        <v>2.5</v>
       </c>
       <c r="C22" s="11">
-        <v>8.1999999999999998E-4</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G22" s="30" t="s">
         <v>146</v>
@@ -4470,14 +4460,14 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B23" s="10">
-        <f t="shared" si="2"/>
-        <v>0.53399999999999992</v>
+        <f t="shared" si="1"/>
+        <v>5.8</v>
       </c>
       <c r="C23" s="11">
-        <v>5.3399999999999997E-4</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="G23" s="30" t="s">
         <v>148</v>
@@ -4494,14 +4484,14 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>225</v>
+        <v>101</v>
       </c>
       <c r="B24" s="10">
-        <f t="shared" ref="B24" si="3">C24*1000</f>
-        <v>8.6964000000000006</v>
+        <f t="shared" si="1"/>
+        <v>0.82</v>
       </c>
       <c r="C24" s="11">
-        <v>8.6964E-3</v>
+        <v>8.1999999999999998E-4</v>
       </c>
       <c r="G24" s="30" t="s">
         <v>150</v>
@@ -4517,15 +4507,15 @@
       </c>
     </row>
     <row r="25" spans="1:10">
-      <c r="A25" s="5" t="s">
-        <v>44</v>
+      <c r="A25" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="B25" s="10">
-        <f>C25*1000</f>
-        <v>0.70209999999999995</v>
+        <f t="shared" si="1"/>
+        <v>0.53399999999999992</v>
       </c>
       <c r="C25" s="11">
-        <v>7.0209999999999999E-4</v>
+        <v>5.3399999999999997E-4</v>
       </c>
       <c r="G25" s="30" t="s">
         <v>152</v>
@@ -4542,14 +4532,14 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>159</v>
+        <v>225</v>
       </c>
       <c r="B26" s="10">
-        <f>C26*1000</f>
-        <v>0.79</v>
+        <f t="shared" ref="B26" si="2">C26*1000</f>
+        <v>8.6964000000000006</v>
       </c>
       <c r="C26" s="11">
-        <v>7.9000000000000001E-4</v>
+        <v>8.6964E-3</v>
       </c>
       <c r="G26" s="30" t="s">
         <v>154</v>
@@ -4566,15 +4556,15 @@
       </c>
     </row>
     <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>43</v>
+      <c r="A27" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="B27" s="10">
-        <f t="shared" ref="B27:B28" si="4">C27*1000</f>
-        <v>1.1732500000000001</v>
+        <f>C27*1000</f>
+        <v>0.70209999999999995</v>
       </c>
       <c r="C27" s="11">
-        <v>1.17325E-3</v>
+        <v>7.0209999999999999E-4</v>
       </c>
       <c r="G27" s="30" t="s">
         <v>105</v>
@@ -4591,14 +4581,14 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="B28" s="10">
-        <f t="shared" si="4"/>
-        <v>0.16239999999999999</v>
+        <f>C28*1000</f>
+        <v>0.79</v>
       </c>
       <c r="C28" s="11">
-        <v>1.6239999999999999E-4</v>
+        <v>7.9000000000000001E-4</v>
       </c>
       <c r="G28" s="30" t="s">
         <v>101</v>
@@ -4615,14 +4605,14 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>224</v>
+        <v>43</v>
       </c>
       <c r="B29" s="10">
-        <f t="shared" ref="B29" si="5">C29*1000</f>
-        <v>1.5050000000000001</v>
+        <f t="shared" ref="B29:B30" si="3">C29*1000</f>
+        <v>1.1732500000000001</v>
       </c>
       <c r="C29" s="11">
-        <v>1.505E-3</v>
+        <v>1.17325E-3</v>
       </c>
       <c r="G29" s="30" t="s">
         <v>37</v>
@@ -4639,14 +4629,14 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B30" s="10">
-        <f t="shared" ref="B30:B40" si="6">C30*1000</f>
-        <v>5.8999999999999997E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.16239999999999999</v>
       </c>
       <c r="C30" s="11">
-        <v>5.8999999999999998E-5</v>
+        <v>1.6239999999999999E-4</v>
       </c>
       <c r="G30" s="30" t="s">
         <v>44</v>
@@ -4663,14 +4653,14 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>28</v>
+        <v>224</v>
       </c>
       <c r="B31" s="10">
-        <f t="shared" si="6"/>
-        <v>7.0849999999999996E-2</v>
+        <f t="shared" ref="B31" si="4">C31*1000</f>
+        <v>1.5050000000000001</v>
       </c>
       <c r="C31" s="11">
-        <v>7.0850000000000001E-5</v>
+        <v>1.505E-3</v>
       </c>
       <c r="G31" s="30" t="s">
         <v>159</v>
@@ -4687,14 +4677,14 @@
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B32" s="10">
-        <f t="shared" si="6"/>
-        <v>0.42560999999999999</v>
+        <f t="shared" ref="B32:B42" si="5">C32*1000</f>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="C32" s="11">
-        <v>4.2560999999999999E-4</v>
+        <v>5.8999999999999998E-5</v>
       </c>
       <c r="G32" s="30" t="s">
         <v>43</v>
@@ -4711,14 +4701,14 @@
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="B33" s="10">
-        <f t="shared" si="6"/>
-        <v>1.141</v>
+        <f t="shared" si="5"/>
+        <v>7.0849999999999996E-2</v>
       </c>
       <c r="C33" s="11">
-        <v>1.1410000000000001E-3</v>
+        <v>7.0850000000000001E-5</v>
       </c>
       <c r="G33" s="30" t="s">
         <v>42</v>
@@ -4735,14 +4725,14 @@
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="B34" s="10">
-        <f t="shared" si="6"/>
-        <v>0.82490700000000006</v>
+        <f t="shared" si="5"/>
+        <v>0.42560999999999999</v>
       </c>
       <c r="C34" s="11">
-        <v>8.2490700000000005E-4</v>
+        <v>4.2560999999999999E-4</v>
       </c>
       <c r="G34" s="30" t="s">
         <v>45</v>
@@ -4759,14 +4749,14 @@
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="B35" s="10">
-        <f t="shared" si="6"/>
-        <v>7.8</v>
+        <f t="shared" si="5"/>
+        <v>1.141</v>
       </c>
       <c r="C35" s="11">
-        <v>7.7999999999999996E-3</v>
+        <v>1.1410000000000001E-3</v>
       </c>
       <c r="G35" s="30" t="s">
         <v>160</v>
@@ -4783,14 +4773,14 @@
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="B36" s="10">
-        <f t="shared" si="6"/>
-        <v>7.085</v>
+        <f t="shared" si="5"/>
+        <v>0.82490700000000006</v>
       </c>
       <c r="C36" s="11">
-        <v>7.0850000000000002E-3</v>
+        <v>8.2490700000000005E-4</v>
       </c>
       <c r="G36" s="30" t="s">
         <v>28</v>
@@ -4807,14 +4797,14 @@
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="B37" s="10">
-        <f t="shared" si="6"/>
-        <v>0.88</v>
+        <f t="shared" si="5"/>
+        <v>7.8</v>
       </c>
       <c r="C37" s="11">
-        <v>8.8000000000000003E-4</v>
+        <v>7.7999999999999996E-3</v>
       </c>
       <c r="G37" s="30" t="s">
         <v>29</v>
@@ -4831,14 +4821,14 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B38" s="10">
-        <f t="shared" si="6"/>
-        <v>1.45</v>
+        <f t="shared" si="5"/>
+        <v>7.085</v>
       </c>
       <c r="C38" s="11">
-        <v>1.4499999999999999E-3</v>
+        <v>7.0850000000000002E-3</v>
       </c>
       <c r="G38" s="30" t="s">
         <v>83</v>
@@ -4854,15 +4844,15 @@
       </c>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="5" t="s">
-        <v>78</v>
+      <c r="A39" s="2" t="s">
+        <v>80</v>
       </c>
       <c r="B39" s="10">
-        <f t="shared" si="6"/>
-        <v>1.05</v>
+        <f t="shared" si="5"/>
+        <v>0.88</v>
       </c>
       <c r="C39" s="11">
-        <v>1.0499999999999999E-3</v>
+        <v>8.8000000000000003E-4</v>
       </c>
       <c r="G39" s="30" t="s">
         <v>104</v>
@@ -4879,14 +4869,14 @@
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="B40" s="10">
-        <f t="shared" si="6"/>
-        <v>3.3103319999999998</v>
+        <f t="shared" si="5"/>
+        <v>1.45</v>
       </c>
       <c r="C40" s="11">
-        <v>3.310332E-3</v>
+        <v>1.4499999999999999E-3</v>
       </c>
       <c r="G40" s="30" t="s">
         <v>77</v>
@@ -4904,14 +4894,14 @@
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B41" s="10">
-        <f>C41*1000</f>
-        <v>0.79100000000000004</v>
+        <f t="shared" si="5"/>
+        <v>1.05</v>
       </c>
       <c r="C41" s="11">
-        <v>7.9100000000000004E-4</v>
+        <v>1.0499999999999999E-3</v>
       </c>
       <c r="G41" s="30" t="s">
         <v>164</v>
@@ -4927,15 +4917,15 @@
       </c>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="5" t="s">
-        <v>85</v>
+      <c r="A42" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="B42" s="10">
-        <f>C42*1000</f>
-        <v>0.82899999999999996</v>
+        <f t="shared" si="5"/>
+        <v>3.3103319999999998</v>
       </c>
       <c r="C42" s="11">
-        <v>8.2899999999999998E-4</v>
+        <v>3.310332E-3</v>
       </c>
       <c r="G42" s="30" t="s">
         <v>166</v>
@@ -4952,15 +4942,15 @@
       </c>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="2" t="s">
-        <v>75</v>
+      <c r="A43" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="B43" s="10">
         <f>C43*1000</f>
-        <v>1</v>
+        <v>0.79100000000000004</v>
       </c>
       <c r="C43" s="11">
-        <v>1E-3</v>
+        <v>7.9100000000000004E-4</v>
       </c>
       <c r="G43" s="30" t="s">
         <v>41</v>
@@ -4977,6 +4967,16 @@
       </c>
     </row>
     <row r="44" spans="1:10">
+      <c r="A44" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="10">
+        <f>C44*1000</f>
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="C44" s="11">
+        <v>8.2899999999999998E-4</v>
+      </c>
       <c r="G44" s="30" t="s">
         <v>168</v>
       </c>
@@ -4991,12 +4991,17 @@
         <v>16.052</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="18" thickBot="1">
-      <c r="A45" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B45"/>
-      <c r="C45" s="12"/>
+    <row r="45" spans="1:10">
+      <c r="A45" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" s="10">
+        <f>C45*1000</f>
+        <v>1</v>
+      </c>
+      <c r="C45" s="11">
+        <v>1E-3</v>
+      </c>
       <c r="G45" s="30" t="s">
         <v>169</v>
       </c>
@@ -5011,17 +5016,7 @@
         <v>88.171999999999997</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="19.5" thickTop="1">
-      <c r="A46" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B46" s="10">
-        <f t="shared" ref="B46:B50" si="7">C46*1000</f>
-        <v>5</v>
-      </c>
-      <c r="C46" s="11">
-        <v>5.0000000000000001E-3</v>
-      </c>
+    <row r="46" spans="1:10" ht="18.75">
       <c r="G46" s="30" t="s">
         <v>80</v>
       </c>
@@ -5035,17 +5030,12 @@
         <v>46.07</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="10">
-        <f t="shared" si="7"/>
-        <v>54.4</v>
-      </c>
-      <c r="C47" s="11">
-        <v>5.4399999999999997E-2</v>
-      </c>
+    <row r="47" spans="1:10" ht="18" thickBot="1">
+      <c r="A47" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47"/>
+      <c r="C47" s="12"/>
       <c r="G47" s="30" t="s">
         <v>172</v>
       </c>
@@ -5059,12 +5049,12 @@
         <v>233.88</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" ht="16.5" thickTop="1">
       <c r="A48" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B48" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="B48:B52" si="6">C48*1000</f>
         <v>5</v>
       </c>
       <c r="C48" s="11">
@@ -5086,14 +5076,14 @@
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B49" s="10">
-        <f t="shared" si="7"/>
-        <v>6.0000000000000005E-2</v>
+        <f t="shared" si="6"/>
+        <v>54.4</v>
       </c>
       <c r="C49" s="11">
-        <v>6.0000000000000002E-5</v>
+        <v>5.4399999999999997E-2</v>
       </c>
       <c r="G49" s="30" t="s">
         <v>81</v>
@@ -5110,14 +5100,14 @@
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B50" s="10">
-        <f t="shared" si="7"/>
-        <v>5.0108799999999993</v>
+        <f t="shared" si="6"/>
+        <v>5</v>
       </c>
       <c r="C50" s="11">
-        <v>5.0108799999999997E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G50" s="30" t="s">
         <v>176</v>
@@ -5134,14 +5124,14 @@
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="2" t="s">
-        <v>227</v>
+        <v>58</v>
       </c>
       <c r="B51" s="10">
-        <f t="shared" ref="B51" si="8">C51*1000</f>
-        <v>4.3499999999999996</v>
+        <f t="shared" si="6"/>
+        <v>6.0000000000000005E-2</v>
       </c>
       <c r="C51" s="11">
-        <v>4.3499999999999997E-3</v>
+        <v>6.0000000000000002E-5</v>
       </c>
       <c r="G51" s="30" t="s">
         <v>177</v>
@@ -5158,14 +5148,14 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="2" t="s">
-        <v>228</v>
+        <v>53</v>
       </c>
       <c r="B52" s="10">
-        <f t="shared" ref="B52" si="9">C52*1000</f>
-        <v>6.24</v>
+        <f t="shared" si="6"/>
+        <v>5.0108799999999993</v>
       </c>
       <c r="C52" s="11">
-        <v>6.2399999999999999E-3</v>
+        <v>5.0108799999999997E-3</v>
       </c>
       <c r="G52" s="30" t="s">
         <v>178</v>
@@ -5183,14 +5173,14 @@
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="2" t="s">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="B53" s="10">
-        <f t="shared" ref="B53:B61" si="10">C53*1000</f>
-        <v>5</v>
+        <f t="shared" ref="B53" si="7">C53*1000</f>
+        <v>4.3499999999999996</v>
       </c>
       <c r="C53" s="11">
-        <v>5.0000000000000001E-3</v>
+        <v>4.3499999999999997E-3</v>
       </c>
       <c r="G53" s="30" t="s">
         <v>180</v>
@@ -5207,14 +5197,14 @@
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="2" t="s">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="B54" s="10">
-        <f t="shared" si="10"/>
-        <v>8.6</v>
+        <f t="shared" ref="B54" si="8">C54*1000</f>
+        <v>6.24</v>
       </c>
       <c r="C54" s="11">
-        <v>8.6E-3</v>
+        <v>6.2399999999999999E-3</v>
       </c>
       <c r="G54" s="30" t="s">
         <v>181</v>
@@ -5231,14 +5221,14 @@
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B55" s="10">
-        <f t="shared" si="10"/>
-        <v>5.7050000000000001</v>
+        <f t="shared" ref="B55:B63" si="9">C55*1000</f>
+        <v>5</v>
       </c>
       <c r="C55" s="11">
-        <v>5.705E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G55" s="30" t="s">
         <v>183</v>
@@ -5255,14 +5245,14 @@
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B56" s="10">
-        <f t="shared" si="10"/>
-        <v>0.35399999999999998</v>
+        <f t="shared" si="9"/>
+        <v>8.6</v>
       </c>
       <c r="C56" s="11">
-        <v>3.5399999999999999E-4</v>
+        <v>8.6E-3</v>
       </c>
       <c r="G56" s="30" t="s">
         <v>185</v>
@@ -5279,14 +5269,14 @@
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B57" s="10">
-        <f t="shared" si="10"/>
-        <v>2.12805</v>
+        <f t="shared" si="9"/>
+        <v>5.7050000000000001</v>
       </c>
       <c r="C57" s="11">
-        <v>2.1280499999999998E-3</v>
+        <v>5.705E-3</v>
       </c>
       <c r="G57" s="30" t="s">
         <v>84</v>
@@ -5303,14 +5293,14 @@
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B58" s="10">
-        <f t="shared" si="10"/>
-        <v>4.1000000000000005</v>
+        <f t="shared" si="9"/>
+        <v>0.35399999999999998</v>
       </c>
       <c r="C58" s="11">
-        <v>4.1000000000000003E-3</v>
+        <v>3.5399999999999999E-4</v>
       </c>
       <c r="G58" s="30" t="s">
         <v>85</v>
@@ -5328,14 +5318,14 @@
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="B59" s="10">
-        <f t="shared" si="10"/>
-        <v>12.5</v>
+        <f t="shared" si="9"/>
+        <v>2.12805</v>
       </c>
       <c r="C59" s="11">
-        <v>1.2500000000000001E-2</v>
+        <v>2.1280499999999998E-3</v>
       </c>
       <c r="G59" s="30" t="s">
         <v>75</v>
@@ -5352,25 +5342,49 @@
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="10">
+        <f t="shared" si="9"/>
+        <v>4.1000000000000005</v>
+      </c>
+      <c r="C60" s="11">
+        <v>4.1000000000000003E-3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" s="10">
+        <f t="shared" si="9"/>
+        <v>12.5</v>
+      </c>
+      <c r="C61" s="11">
+        <v>1.2500000000000001E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B60" s="10">
-        <f t="shared" si="10"/>
+      <c r="B62" s="10">
+        <f t="shared" si="9"/>
         <v>7.5</v>
       </c>
-      <c r="C60" s="11">
+      <c r="C62" s="11">
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
-      <c r="A61" s="5" t="s">
+    <row r="63" spans="1:10">
+      <c r="A63" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B61" s="10">
-        <f t="shared" si="10"/>
+      <c r="B63" s="10">
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C63" s="11">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
@@ -5383,7 +5397,7 @@
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2">
-      <formula1>$A$11:$A$43</formula1>
+      <formula1>$A$11:$A$45</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="1" right="1" top="1.6666666666666667" bottom="1.6666666666666667" header="1" footer="1"/>
